--- a/UKMLA_Posts_Registry.xlsx
+++ b/UKMLA_Posts_Registry.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11446,6 +11446,1378 @@
         </is>
       </c>
     </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>how-to-become-a-doctor-in-uk-from-india</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>A step-by-step guide for Indian medical graduates on how to become a doctor in the UK from India — UKMLA eligibility, exam costs in rupees, GMC registration, and the MBBS-to-NHS timeline.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>IMG Pathway</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>IMG Pathway, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/registration-and-licensing/join-our-registers/registration-applications/application-guides/full-registration-for-international-medical-graduates</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in UK from India: 2026 Guide</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>How to become a doctor in UK from India: UKMLA eligibility, AKT/CPSA costs in rupees, GMC registration steps, and the full MBBS-to-NHS timeline.</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>how to become a doctor in UK from India</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;How to become a doctor in UK from India&lt;/strong&gt; is one of the most searched questions among Indian MBBS graduates, and for good reason — the route is well defined but has several stages that must be completed in the right order. An Indian MBBS degree does not automatically allow you to practise medicine in the United Kingdom. Instead, you must pass the &lt;strong&gt;UK Medical Licensing Assessment (UKMLA)&lt;/strong&gt;, have your qualifications verified through an international credentialing service, prove your English language ability, and then apply to the General Medical Council (GMC) for registration with a licence to practise. Once registered, you can apply for foundation or specialty training posts and begin working in the NHS.&lt;/p&gt;
+&lt;p&gt;This guide walks through the complete India-to-NHS pathway in the order you will actually experience it: eligibility rules for NMC-recognised Indian degrees, how to open a GMC Online account and complete primary source verification through EPIC, where you can sit the &lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test (AKT)&lt;/a&gt; inside India, why the clinical exam must be taken in Manchester, what the whole process costs in Indian rupees, and a realistic month-by-month timeline from graduation to your first NHS pay cheque. It also compares the UKMLA route to staying in India for NEET PG and to the alternative route via the USMLE, and closes with a set of frequently asked questions written the way Indian doctors actually search for them.&lt;/p&gt;
+&lt;p&gt;Every year, thousands of Indian medical graduates begin this process, and the majority of delays reported by candidates are avoidable — caused by document verification backlogs, English test certificates expiring before the registration application is submitted, or underestimating the cost of a Manchester exam trip. Understanding the full sequence in advance, before you spend money on any single step, is the single biggest factor in completing this route smoothly.&lt;/p&gt;
+&lt;h2&gt;The UKMLA Route From India: A Quick Overview&lt;/h2&gt;
+&lt;p&gt;Before going step by step, it helps to see the whole journey in one place. The table below summarises the major stages every Indian medical graduate must complete, from finishing MBBS to being registered with a licence to practise in the UK.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Stage&lt;/th&gt;&lt;th&gt;What Happens&lt;/th&gt;&lt;th&gt;Typical Timing&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;1. Confirm eligibility&lt;/td&gt;&lt;td&gt;Check your MBBS degree is NMC-recognised and listed on the World Directory of Medical Schools; open a GMC Online account&lt;/td&gt;&lt;td&gt;Can start in final year of MBBS&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;2. Primary source verification&lt;/td&gt;&lt;td&gt;Submit your degree and internship documents to EPIC for verification against your &lt;a href="/news#uk-medical-schools-ukmla-implementation"&gt;medical school&lt;/a&gt; and university&lt;/td&gt;&lt;td&gt;2–4 months, sometimes longer&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;3. English language evidence&lt;/td&gt;&lt;td&gt;Sit IELTS Academic or OET Medicine and achieve the GMC's minimum score in every domain&lt;/td&gt;&lt;td&gt;Can run in parallel with EPIC verification&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;4. Applied Knowledge Test (AKT)&lt;/td&gt;&lt;td&gt;Book and sit the AKT at a Pearson VUE centre — available in several Indian cities&lt;/td&gt;&lt;td&gt;After GMC Online account is set up; results in ~10 working days&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;5. &lt;a href="/exam-pattern/cpsa"&gt;Clinical and Professional Skills Assessment (CPSA)&lt;/a&gt;&lt;/td&gt;&lt;td&gt;Travel to the GMC's dedicated exam centre in Manchester to sit the practical OSCE-style clinical exam&lt;/td&gt;&lt;td&gt;Booked after passing AKT; must usually be sat within 24 months of the AKT pass&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;6. GMC registration application&lt;/td&gt;&lt;td&gt;Submit your registration application with all verified documents once AKT and CPSA are both passed&lt;/td&gt;&lt;td&gt;4–8 weeks for a decision&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;Once you are registered with a licence to practise, you can apply for a job — most Indian graduates start in Foundation Year 2 equivalent posts, Trust posts, or apply directly to specialty training depending on prior experience. Each of these six stages is explained in full detail below, including exact fees, the &lt;a href="/registration-guide"&gt;GMC registration process&lt;/a&gt;, and the &lt;a href="/key-dates"&gt;UKMLA key dates and sitting schedule&lt;/a&gt; you will need to plan around.&lt;/p&gt;
+&lt;h2&gt;Who Is Eligible? UKMLA Eligibility for Indian Doctors&lt;/h2&gt;
+&lt;p&gt;UKMLA eligibility for Indian doctors starts with your primary medical qualification. To be eligible for GMC registration as an international medical graduate, your MBBS degree must appear on the World Directory of Medical Schools (WDOMS), which almost all National Medical Commission (NMC)-recognised medical colleges in India do. If you graduated from a college recognised by the NMC (formerly the Medical Council of India, MCI), your degree is very likely to satisfy this requirement, but it is worth checking the WDOMS listing directly rather than assuming, because listings are tied to the specific medical school and sometimes to the year you graduated.&lt;/p&gt;
+&lt;h3&gt;NMC-Recognised Degrees and How They Map to GMC Requirements&lt;/h3&gt;
+&lt;p&gt;The GMC does not evaluate the content of your MBBS curriculum directly. Instead, it relies on two things: your degree being awarded by a WDOMS-listed institution, and independent verification that you actually hold that qualification. This is different from some other countries' systems, where regulators assess curriculum equivalence subject by subject. For Indian graduates this generally simplifies matters — if your college is NMC-recognised and WDOMS-listed, the degree itself is not usually the sticking point. The UKMLA (specifically the AKT and CPSA) is what actually tests whether your clinical knowledge and skills meet the UK standard, replacing any need for a separate curriculum comparison.&lt;/p&gt;
+&lt;p&gt;You will also need evidence of an internship or equivalent period of supervised clinical practice completed after your MBBS, since full GMC registration (as opposed to provisional registration) generally requires this. Compulsory rotating internship certificates from your medical college, along with your MBBS degree certificate and mark sheets, form the core document set you will submit for verification.&lt;/p&gt;
+&lt;h3&gt;Provisional Registration vs Full Registration&lt;/h3&gt;
+&lt;p&gt;It is worth understanding the distinction between provisional and full registration early, because it affects how you sequence your internship documentation. Provisional registration is a limited category, historically used by UK medical graduates who had passed their degree but not yet completed the foundation year needed for full registration; it is not the route most Indian IMGs use. Indian graduates who have already completed their compulsory rotating internship in India, and who pass both components of the UKMLA, generally apply directly for &lt;strong&gt;full registration with a licence to practise&lt;/strong&gt;. This matters because it means your Indian internship certificate is not a formality — it is a required piece of evidence that your supervised clinical practice period is already complete, and its absence or an incomplete internship record is a common reason applications stall at the document-checking stage.&lt;/p&gt;
+&lt;h3&gt;Primary Source Verification Through EPIC&lt;/h3&gt;
+&lt;p&gt;A central and sometimes underappreciated step is primary source verification through EPIC — the Education Commission for Foreign Medical Graduates' EPIC service. EPIC is an independent verification system that contacts your medical school and university directly to confirm that the degree certificate you hold was genuinely issued by them. The GMC requires this verification for international medical graduates as part of the registration application, and it cannot be skipped or substituted with notarised copies of your documents.&lt;/p&gt;
+&lt;p&gt;In practice, this means creating an EPIC account, uploading your primary medical qualification and internship documents, and paying the EPIC verification fee. EPIC then writes to your medical college and university (and sometimes the NMC) to confirm authenticity. Response times from Indian institutions vary considerably — some colleges respond within a few weeks, others take several months, particularly if the college has changed administration, merged, or if records from your graduation year were kept on paper rather than digitally. Starting this step early, ideally as soon as you have your final degree certificate in hand, is one of the most effective things you can do to avoid delays later. Full details on who is allowed to sit the assessment and how eligibility is assessed are covered in the GMC's own eligibility material, alongside the site's page on &lt;a href="/eligibility"&gt;UKMLA eligibility requirements&lt;/a&gt; and the news update on &lt;a href="/news#ukmla-eligibility-who-can-sit"&gt;who can sit the UKMLA&lt;/a&gt;.&lt;/p&gt;
+&lt;h3&gt;What EPIC Verification Actually Checks&lt;/h3&gt;
+&lt;p&gt;Candidates sometimes assume EPIC verification is a paperwork formality similar to notarisation, but it is a substantive investigation. EPIC verifies four things independently with the issuing institution: that you were enrolled as a student at the medical school in the years claimed; that you were awarded the specific primary medical qualification stated, on the date stated; that the qualification is a recognised medical degree conferring eligibility to practise medicine in India; and, separately, that any internship or postgraduate training documents you submit are genuine and match the institution's own records. Because this process relies on the responsiveness of Indian medical colleges and universities — many of which do not have a dedicated international verification desk — building in slack time for this stage, rather than assuming a fixed number of weeks, is the more realistic approach. If your college has since changed its name, merged with another institution, or moved affiliation between universities, mention this proactively in your EPIC application, since it is a common cause of verification mismatches for older graduates.&lt;/p&gt;
+&lt;h3&gt;Registering With the Medical Council and Keeping Your Indian Licence&lt;/h3&gt;
+&lt;p&gt;Most Indian doctors pursuing the UK route keep their Indian State Medical Council or NMC registration active in parallel, rather than surrendering it. There is no requirement to give up your Indian medical registration in order to register with the GMC — the two are independent regulatory relationships. Many candidates find it useful to maintain Indian registration and continue some clinical work or a residency-track post in India while working through EPIC verification and exam preparation, since the process realistically takes the better part of a year and having clinical income and hands-on practice during that period benefits both your finances and your CPSA performance.&lt;/p&gt;
+&lt;h2&gt;How to Apply for the UKMLA From India: Step by Step&lt;/h2&gt;
+&lt;p&gt;Knowing how to apply for UKMLA from India means working through a specific sequence of administrative steps before you can book either exam. Doing these in the wrong order is one of the most common causes of avoidable delay, so treat this as a checklist rather than a set of options.&lt;/p&gt;
+&lt;h3&gt;Step 1: Create a GMC Online Account&lt;/h3&gt;
+&lt;p&gt;Everything starts with a GMC Online account, created on the GMC's website using your passport details and an email address you will keep for the duration of the process. This account becomes your hub for booking exams, uploading documents, tracking your EPIC verification status, and eventually submitting your registration application. Use your name exactly as it appears on your passport, since discrepancies between your passport, MBBS certificate, and EPIC documents are a common source of administrative back-and-forth.&lt;/p&gt;
+&lt;h3&gt;Step 2: Begin EPIC Primary Source Verification&lt;/h3&gt;
+&lt;p&gt;As soon as your GMC Online account is active, start your EPIC application in parallel. You will need scanned copies of your MBBS degree certificate, internship completion certificate, and passport. EPIC verification is not free and is paid separately from GMC and Pearson VUE exam fees — factor this into your total budget alongside &lt;a href="/fees"&gt;the full UKMLA fee schedule&lt;/a&gt;.&lt;/p&gt;
+&lt;h3&gt;Step 3: Gather English Language Evidence&lt;/h3&gt;
+&lt;p&gt;While EPIC verification is progressing (which can take months), sit your English language test. Booking this in parallel rather than waiting for EPIC to finish saves significant time overall, but be careful about test validity windows — most English test results are only accepted by the GMC if they were taken within two years of your registration application, so timing this too early can mean &lt;a href="/appeals-and-resits"&gt;re-sit&lt;/a&gt;ting the test later.&lt;/p&gt;
+&lt;h3&gt;Step 4: Book and Sit the AKT&lt;/h3&gt;
+&lt;p&gt;Once your GMC Online account is set up, you can book the Applied Knowledge Test through Pearson VUE. Indian candidates can sit this computer-based exam inside India, which is covered in detail in the next section. AKT results are typically released within about ten working days of your sitting.&lt;/p&gt;
+&lt;h3&gt;Step 5: Book and Sit the CPSA&lt;/h3&gt;
+&lt;p&gt;After passing the AKT, you become eligible to book the Clinical and Professional Skills Assessment. Unlike the AKT, the CPSA cannot currently be sat in India — it must be taken at the GMC's dedicated exam centre in Manchester, which has significant cost and logistical implications covered below.&lt;/p&gt;
+&lt;h3&gt;Step 6: Submit Your GMC Registration Application&lt;/h3&gt;
+&lt;p&gt;Once you have passed both the AKT and the CPSA, and your EPIC verification and English language evidence are complete and current, you submit your formal application for registration with a licence to practise. The GMC reviews the full document set — verified qualification, internship evidence, English language certificate, both exam pass certificates, and identity documents — before granting registration. The &lt;a href="/registration-guide"&gt;GMC registration process&lt;/a&gt; page on this site walks through the document checklist in more detail, and the GMC's own guidance is authoritative: consult &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/registration-applications/application-guides/full-registration-for-international-medical-graduates"&gt;the GMC's full registration guide for international medical graduates&lt;/a&gt; before submitting anything.&lt;/p&gt;
+&lt;h3&gt;Step 7: Apply for NHS Posts and Obtain a Certificate of Sponsorship&lt;/h3&gt;
+&lt;p&gt;Registration with the GMC gives you the legal right to practise medicine in the UK, but it does not by itself give you the right to live and work in the UK if you are not a UK or Irish citizen — that requires a visa. Most Indian doctors enter on a &lt;strong&gt;Health and Care Worker visa&lt;/strong&gt;, which requires a job offer from an NHS employer (or an approved healthcare provider) accompanied by a Certificate of Sponsorship. In practice this means the realistic sequence is: pass AKT and CPSA, obtain GMC registration, then apply for NHS vacancies (Trust posts, Foundation Year 2 equivalent posts, or specialty training via the national recruitment rounds depending on your experience level), and only once you have a confirmed offer do you apply for the visa itself. Many candidates start browsing and applying to vacancies in the final weeks before their registration is confirmed, since NHS recruitment cycles run on fixed rounds throughout the year and timing your application to coincide with a live round shortens the overall gap between registration and your first pay cheque.&lt;/p&gt;
+&lt;h2&gt;Can You Take the UKMLA AKT in India? Test Centres Explained&lt;/h2&gt;
+&lt;p&gt;Yes — the Applied Knowledge Test is delivered through Pearson VUE, which operates test centres across India, meaning most candidates never need to leave the country for this part of the exam. Can I take UKMLA AKT in India is one of the most common questions Indian candidates ask, and the practical answer is that AKT sittings are typically available in major metropolitan cities including &lt;strong&gt;Mumbai, Delhi, Bangalore, Chennai, and Hyderabad&lt;/strong&gt;, subject to seat availability during each sitting window. Exact centre locations and available dates change between sittings, so always confirm current options directly through the Pearson VUE booking portal linked from your GMC Online account rather than relying on a fixed list.&lt;/p&gt;
+&lt;p&gt;The AKT is a computer-based, multiple-choice examination, which is why it can be delivered at standard Pearson VUE test centres worldwide rather than requiring a dedicated facility. It tests applied medical knowledge across the breadth of UK clinical practice — presentations, investigations, management, and professional/ethical scenarios — in a format broadly similar to other single-best-answer medical licensing exams, though calibrated specifically to UK clinical guidelines and the NHS context. Because seats fill up quickly around popular &lt;a href="/news#ukmla-key-dates-sitting-schedule"&gt;sitting dates&lt;/a&gt;, especially in Delhi and Mumbai, book as early as your booking window allows, and check &lt;a href="/key-dates"&gt;UKMLA key dates and sitting schedule&lt;/a&gt; to plan around the GMC's published sitting calendar for the year.&lt;/p&gt;
+&lt;h3&gt;What to Expect at an Indian AKT Test Centre&lt;/h3&gt;
+&lt;p&gt;The AKT experience at an Indian Pearson VUE centre is procedurally identical to sitting the exam anywhere else in the world — the same secure testing environment, the same identity checks against your passport, and the same computer-delivered question format. Arrive with your passport as the primary form of identification (the name on it must match your GMC Online account exactly), expect airport-style security procedures including a metal detector and pocket check before entering the test room, and expect all personal items, including phones and watches, to be stored in a locker for the duration of the exam. Because Indian metros can have unpredictable traffic, most candidates travelling from outside the test centre's city budget an overnight stay nearby rather than a same-day journey, to avoid the stress of a delayed arrival jeopardising the sitting.&lt;/p&gt;
+&lt;h3&gt;Booking Windows and Seat Availability&lt;/h3&gt;
+&lt;p&gt;Pearson VUE releases AKT seats in blocks tied to each GMC sitting window, and Indian centres are shared with candidates sitting other Pearson VUE-administered exams, which means seat availability at popular centres can be tighter than in some other countries. Delhi and Mumbai typically see the highest demand and are the first to fill for convenient time slots. If your preferred city and date combination is unavailable, the practical alternatives are booking a different city within India (many candidates travel between metros for the exam day, treating it similarly to a domestic postgraduate entrance exam), or selecting a different date within the same sitting window. Because rebooking or cancelling close to your date can incur a fee, finalise your target sitting only once your preparation timeline is realistic, not provisionally.&lt;/p&gt;
+&lt;h3&gt;Why the CPSA Must Be Sat in Manchester&lt;/h3&gt;
+&lt;p&gt;Unlike the AKT, the Clinical and Professional Skills Assessment cannot be sat in India. The CPSA is an OSCE-style practical exam involving live actors playing standardised patients, physical examination stations, and real-time assessment by trained examiners — this requires a dedicated, purpose-built clinical assessment centre, which the GMC currently operates only in Manchester, UK. This means every candidate, regardless of home country, must travel to the UK for this stage. For Indian candidates this is the single biggest practical and &lt;a href="/news#ukmla-fees-explained"&gt;financial planning&lt;/a&gt; point in the whole process: flights, UK visitor visa arrangements, Manchester accommodation for the days around your exam slot, and the exam fee itself all need to be budgeted together, not treated as an afterthought once you have already passed the AKT. Many candidates use the weeks after passing AKT to prepare specifically for CPSA format using structured resources — see the news guide on &lt;a href="/news#plab-2-preparation-guide"&gt;preparing for the PLAB 2 clinical assessment&lt;/a&gt;, which covers the same clinical and communication skill set now assessed in the CPSA.&lt;/p&gt;
+&lt;h2&gt;UKMLA Exam Cost in India: Fees in Indian Rupees&lt;/h2&gt;
+&lt;p&gt;UKMLA exam cost in India is a frequent concern, and it is worth separating out clearly because there are several distinct fees involved, not one lump sum. All GMC and Pearson VUE fees are set and charged in pounds sterling, so the INR figures below are approximate conversions and will move with the exchange rate — always check the live figure on the GMC's website before budgeting precisely.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Fee Item&lt;/th&gt;&lt;th&gt;Amount in GBP&lt;/th&gt;&lt;th&gt;Approximate INR*&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;AKT exam fee&lt;/td&gt;&lt;td&gt;&lt;strong&gt;£283&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;≈ ₹29,700&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA exam fee&lt;/td&gt;&lt;td&gt;&lt;strong&gt;£1,036&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;≈ ₹1,08,800&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC registration fee&lt;/td&gt;&lt;td&gt;&lt;strong&gt;£481&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;≈ ₹50,500&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Annual retention fee (yearly, to keep your licence active)&lt;/td&gt;&lt;td&gt;&lt;strong&gt;£431&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;≈ ₹45,300&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;*INR conversions are approximate, calculated at broadly prevailing GBP-to-INR exchange rates, and are provided for planning purposes only. Exchange rates fluctuate regularly, and the GMC and Pearson VUE charge in GBP at the time of payment, so the rupee amount you actually pay will depend on your bank's or card provider's conversion rate on the day. The GMC reviews its requirements periodically; always verify current rules on the &lt;a href="/official-resources"&gt;GMC website&lt;/a&gt; before applying.&lt;/p&gt;
+&lt;p&gt;These four fees are the core exam and registration costs, but they are not the full picture of what the route costs an Indian candidate. On top of them, budget separately for: the EPIC primary source verification fee (paid in USD, separate from GMC fees); your English language test fee (IELTS or OET, both charged in INR at Indian test centres); and, most significantly, the cost of travelling to Manchester for the CPSA — flights from India, UK visitor visa fees, and several nights of accommodation, which for many candidates ends up being a larger real-world cost than the CPSA exam fee itself. For a complete breakdown including these ancillary costs, see &lt;a href="/news#ukmla-fees-for-img-2026"&gt;the full IMG fee breakdown&lt;/a&gt; alongside the site's general &lt;a href="/fees"&gt;UKMLA fee schedule&lt;/a&gt;.&lt;/p&gt;
+&lt;h2&gt;English Language Requirements for Indian Doctors&lt;/h2&gt;
+&lt;p&gt;Every international medical graduate applying for GMC registration must provide evidence of English language proficiency, and Indian doctors are not exempt from this even though much of Indian medical education is delivered in English. The GMC currently accepts two test routes, and you only need to pass one of them.&lt;/p&gt;
+&lt;p&gt;The first option is &lt;strong&gt;IELTS Academic&lt;/strong&gt;, where the GMC's current minimum requirement is a score of &lt;strong&gt;7.0 in each of the four domains&lt;/strong&gt; — listening, reading, writing, and speaking — with an overall score that reflects this. A high score in three domains does not compensate for falling below 7.0 in the fourth; the GMC applies the minimum per-domain, not just as an average. The second option is the &lt;strong&gt;Occupational English Test (OET), Medicine version&lt;/strong&gt;, where the GMC's current minimum is &lt;strong&gt;Grade B in each of the four sub-tests&lt;/strong&gt;. OET is designed specifically around healthcare communication scenarios, which some Indian candidates find more directly relevant to clinical practice than the general academic format of IELTS, though both are equally accepted.&lt;/p&gt;
+&lt;p&gt;Whichever test you choose, results are only valid for a limited period from the test date — plan your test sitting so that the certificate will still be within its validity window when you eventually submit your GMC registration application, not just when you sit the AKT. Because English test requirements, minimum scores, and accepted exceptions are reviewed periodically, treat any figure here as a starting point and confirm against &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/before-you-apply-guide-for-doctors/evidence-of-your-knowledge-of-english"&gt;the GMC's English language evidence requirements&lt;/a&gt; before booking a test.&lt;/p&gt;
+&lt;h2&gt;UKMLA vs Other Routes for Indian Doctors&lt;/h2&gt;
+&lt;p&gt;Most Indian MBBS graduates weighing up the UK route are also considering two alternatives: staying in India and preparing for NEET PG, or pursuing the USMLE route to practise in the United States. Each is a substantial decision in its own right, so this section gives only a brief comparison — the detailed analysis lives in two dedicated posts on this site.&lt;/p&gt;
+&lt;p&gt;Compared with the domestic route, the UKMLA pathway generally has a shorter and more predictable timeline to independent practice than the highly competitive NEET PG postgraduate seat allocation process in India, but it requires upfront investment in exam fees, English testing, and international travel that the domestic route does not. For a full side-by-side comparison of costs, timelines, and career outcomes, see &lt;a href="/news#ukmla-vs-neet-pg"&gt;how the UKMLA route compares to NEET PG&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Compared with the USMLE route into US residency, the UKMLA is often seen by Indian candidates as having a more linear, single-exam-body process (everything runs through the GMC and Pearson VUE) versus the multi-step USMLE Step 1/Step 2 CK/Match process governed by the ECFMG and NRMP. Both routes involve significant cost and a mandatory in-country practical or interview stage. A detailed breakdown of exam structure, cost, and residency/training-post competitiveness for each route is covered separately in &lt;a href="/news#ukmla-vs-usmle-comparison"&gt;how UKMLA compares to the USMLE&lt;/a&gt; — read that alongside this guide if you are still deciding between the two countries.&lt;/p&gt;
+&lt;p&gt;A few high-level factors tend to drive the decision for most Indian candidates. Total cost to reach independent practice is generally lower for the UKMLA route than for USMLE plus Match, largely because the CPSA is a single practical exam rather than a separate clinical skills exam and a lengthy residency Match cycle with its own application fees. Time to a working, paid clinical post also tends to be shorter via the UKMLA route for candidates who complete EPIC and both exams efficiently, since GMC registration itself confers eligibility to work, whereas US Match results are only released once a year and unmatched candidates must wait for the next cycle. On the other hand, candidates targeting long-term settlement, higher subspecialty training capacity, or specific research-heavy fellowships sometimes still find the US route more attractive despite the longer and more competitive pathway. Neither route is objectively "better" — the right choice depends on your specialty interest, risk tolerance for a competitive Match process, and how quickly you need to start earning as a doctor.&lt;/p&gt;
+&lt;h2&gt;Timeline: From MBBS Graduation to NHS Registration&lt;/h2&gt;
+&lt;p&gt;The realistic timeline for how to become a doctor in UK from India varies by candidate, largely depending on how quickly EPIC verification completes and how far in advance you can book exam and travel slots, but a typical sequence looks like this.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Stage&lt;/th&gt;&lt;th&gt;Approximate Timing&lt;/th&gt;&lt;th&gt;Notes&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;MBBS graduation + internship completion&lt;/td&gt;&lt;td&gt;Month 0&lt;/td&gt;&lt;td&gt;Ensure internship certificate is issued promptly by your college&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC Online account + EPIC application opened&lt;/td&gt;&lt;td&gt;Month 0–1&lt;/td&gt;&lt;td&gt;Start EPIC as early as possible — this is usually the longest-running step&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;English language test sat&lt;/td&gt;&lt;td&gt;Month 1–3&lt;/td&gt;&lt;td&gt;Run in parallel with EPIC, but mind the 2-year validity window&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;EPIC verification completes&lt;/td&gt;&lt;td&gt;Month 3–7&lt;/td&gt;&lt;td&gt;Highly variable; some colleges respond faster than others&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;AKT booked and sat in India&lt;/td&gt;&lt;td&gt;Month 4–8&lt;/td&gt;&lt;td&gt;Can be booked once GMC Online account is active; does not need to wait for EPIC to fully complete in all cases&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;AKT result released&lt;/td&gt;&lt;td&gt;~10 working days after sitting&lt;/td&gt;&lt;td&gt;&amp;nbsp;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA booked&lt;/td&gt;&lt;td&gt;Month 6–10&lt;/td&gt;&lt;td&gt;Book Manchester travel and visa well ahead of the exam date&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA sat in Manchester&lt;/td&gt;&lt;td&gt;Month 8–12&lt;/td&gt;&lt;td&gt;Must generally be within 24 months of AKT pass&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC registration application submitted&lt;/td&gt;&lt;td&gt;Month 9–13&lt;/td&gt;&lt;td&gt;Requires all documents current and verified&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC registration granted&lt;/td&gt;&lt;td&gt;Month 10–15&lt;/td&gt;&lt;td&gt;4–8 weeks after a complete application&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Apply for NHS posts / training programmes&lt;/td&gt;&lt;td&gt;Month 11 onward&lt;/td&gt;&lt;td&gt;Can start applying once registration is imminent or confirmed, depending on the vacancy cycle&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;Candidates who plan efficiently — starting EPIC immediately after graduation and sitting the AKT as soon as realistically prepared — sometimes complete the whole route from graduation to registration in around &lt;strong&gt;10 to 12 months&lt;/strong&gt;. Candidates who wait to start EPIC until after passing the AKT, or who need to re-sit an exam, commonly see the process extend to &lt;strong&gt;18 months or more&lt;/strong&gt;. This is why sequencing matters more than raw exam preparation time for most candidates.&lt;/p&gt;
+&lt;h2&gt;Common Mistakes Indian Doctors Make on This Route&lt;/h2&gt;
+&lt;p&gt;Several mistakes recur often enough among Indian candidates that they are worth flagging explicitly, since each one is avoidable with earlier planning.&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Starting EPIC verification too late.&lt;/strong&gt; Because EPIC has to contact your medical college and university directly, and Indian institutions vary widely in how quickly they respond to verification requests, this step should begin the moment you have your final degree and internship certificates — not after you have already passed the AKT.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Letting English test results expire.&lt;/strong&gt; IELTS and OET certificates are valid for a limited window from the test date. Candidates who sit the test very early, then take 18–24 months to complete EPIC and both exams, sometimes find their certificate has expired by the time they submit their registration application, forcing an expensive re-sit.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Underestimating CPSA travel costs.&lt;/strong&gt; The CPSA exam fee itself is a fixed, known cost, but flights to Manchester, UK visitor visa fees, accommodation for several nights around the exam date, and the possibility of needing a second attempt if the first is unsuccessful can multiply the real cost of this stage well beyond the headline fee. Budget for this as a discrete, larger line item rather than an add-on.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Booking AKT before adequate preparation.&lt;/strong&gt; Because Indian test centres and sitting windows can fill up, some candidates book a slot opportunistically and then find they have insufficient preparation time. Choosing &lt;a href="/news#ukmla-question-bank-and-mock-tests"&gt;a good AKT question bank&lt;/a&gt; and setting a realistic study timeline before booking avoids a costly re-sit.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Assuming NMC recognition automatically means WDOMS listing.&lt;/strong&gt; The two are closely linked but not identical administratively — always verify your specific medical school's current WDOMS entry rather than assuming based on general NMC recognition.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Mismatched name spellings across documents.&lt;/strong&gt; Minor discrepancies between your passport, MBBS certificate, and EPIC submission (a missing middle name, different transliteration) can stall verification and the eventual registration application. Check every document for consistency before submitting anything.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Not using a structured, UK-specific preparation plan.&lt;/strong&gt; The AKT and CPSA test UK clinical guidelines and NHS-specific scenarios, which differ in emphasis from Indian postgraduate entrance exams. Candidates who prepare using India-focused postgraduate material alone, without adapting to UK guidelines, often underperform relative to their underlying clinical knowledge. A &lt;a href="/news#ukmla-preparation-for-imgs"&gt;tailored IMG preparation guide&lt;/a&gt; addresses this gap directly.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Leaving visa and job applications until after registration is granted.&lt;/strong&gt; Because a Health and Care Worker visa requires a confirmed job offer and Certificate of Sponsorship, candidates who wait until GMC registration is fully granted before even browsing NHS vacancies add unnecessary weeks to their timeline.</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>doctor from India UK route</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>/images/how-to-become-a-doctor-in-uk-from-india-featured.webp</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>How to become a doctor in UK from India - Indian medical graduate reviewing UKMLA and GMC registration documents</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>5640</v>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Everything Pakistani medical graduates need to know about the UKMLA for Pakistani doctors — eligibility, PMDC-to-GMC recognition, AKT test centres, and fees in PKR.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>IMG Pathway</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>IMG Pathway, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/registration-and-licensing/join-our-registers/registration-applications/application-guides/provisional-registration-for-international-medical-graduates</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility &amp; Fees</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani doctors: eligibility, GMC registration, AKT test centres in Pakistan, and exam fees in PKR for 2026 — the complete route guide.</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;UKMLA for Pakistani doctors&lt;/strong&gt; is one of the most searched topics among MBBS graduates from Pakistan Medical and Dental Council (PMDC)-recognised universities who want to practise medicine in the National Health Service. Pakistan sends one of the largest cohorts of international medical graduates (IMGs) to the UK every year, and the route — from a Karachi, Lahore, or Islamabad medical degree through to full General Medical Council (GMC) registration — is well trodden but far from simple. Understanding exactly which exams to sit, in what order, at what cost, and with what documentation is the single biggest factor separating candidates who register within two years from those who stall for four or five.&lt;/p&gt;
+&lt;p&gt;This guide sets out the complete pathway for Pakistani doctors: how a PMDC-recognised primary medical qualification maps onto GMC eligibility, the step-by-step application process from a GMC Online account through to registration, where the &lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test (AKT)&lt;/a&gt; can be sat inside Pakistan, what the &lt;a href="/exam-pattern/cpsa"&gt;Clinical and Professional Skills Assessment (CPSA)&lt;/a&gt; requires in Manchester, and a full fee breakdown converted into Pakistani rupees. It also covers English language requirements, a realistic timeline from graduation to your first NHS post, and the mistakes that repeatedly delay Pakistani candidates on this route.&lt;/p&gt;
+&lt;p&gt;Throughout, the aim is precision rather than reassurance. Figures for fees, English language scores, and timelines are stated as exactly as current GMC guidance allows, with clear notes on where candidates must verify the latest numbers directly with the GMC before committing money or time.&lt;/p&gt;
+&lt;h2&gt;The UKMLA Route From Pakistan: A Quick Overview&lt;/h2&gt;
+&lt;p&gt;Before going step by step, it helps to see the whole route from MBBS graduation to working as a doctor in the NHS in outline. For a Pakistani doctor, the process generally runs as follows:&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;&lt;strong&gt;Complete your MBBS&lt;/strong&gt; at a PMDC-recognised medical school and complete your House Job (internship) year, since the GMC requires evidence of a period of supervised clinical practice.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Verify your primary medical qualification&lt;/strong&gt; through EPIC (the Electronic Portfolio of International Credentials, operated via ECFMG/Intealth), which the GMC requires before it will accept an application.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Meet the English language requirement&lt;/strong&gt; with IELTS Academic or OET Medicine at the GMC's minimum scores.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Create a GMC Online account&lt;/strong&gt; and begin your registration application, which opens a &lt;a href="/news#three-months-ukmla-akt-countdown"&gt;90-day&lt;/a&gt; window to complete supporting steps.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Sit the UKMLA AKT&lt;/strong&gt; (the &lt;a href="/ukmla-vs-plab"&gt;PLAB 1&lt;/a&gt; equivalent) at a Pearson VUE centre — this can be done from inside Pakistan.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Sit the UKMLA CPSA&lt;/strong&gt; (the PLAB 2 equivalent) — this must be done in person in Manchester, UK.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Apply for full GMC registration with a licence to practise&lt;/strong&gt; once both UKMLA components and all other eligibility criteria are satisfied.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Apply for NHS posts&lt;/strong&gt; — typically Foundation-equivalent or clinical fellow roles for doctors without prior UK experience, moving into structured training thereafter.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Each of these steps has its own paperwork, cost, and waiting period, and several can be run in parallel to save time. The sections below break down each stage in detail, including exactly how the process differs for someone applying from Pakistan compared with a UK medical graduate.&lt;/p&gt;
+&lt;h2&gt;PMDC Recognition and UKMLA Eligibility for Pakistani Doctors&lt;/h2&gt;
+&lt;p&gt;The starting point for any discussion of &lt;strong&gt;UKMLA for Pakistani doctors&lt;/strong&gt; is degree recognition. The GMC does not maintain a simple "approved list" of overseas medical schools in the way some other regulators do. Instead, it relies on independent, internationally recognised verification of your primary medical qualification, combined with confirmation that your medical school and qualification are listed in the World Directory of Medical Schools (WDOMS).&lt;/p&gt;
+&lt;p&gt;For a PMDC-recognised Pakistani medical degree, this generally works as follows. Your medical school must appear in the WDOMS with your specific qualification (usually MBBS) listed as awarded. Almost all PMDC-recognised public and private medical colleges — including those affiliated with major universities in Punjab, Sindh, Khyber Pakhtunkhwa, and Balochistan — are listed. If your college is a newer or smaller institution, it is worth checking the WDOMS entry early, since an unlisted qualification will block your GMC application regardless of how strong your exam results are.&lt;/p&gt;
+&lt;p&gt;Beyond degree recognition, the GMC's &lt;a href="/eligibility"&gt;UKMLA eligibility requirements&lt;/a&gt; for IMGs generally require:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;A primary medical qualification that is acceptable to the GMC and listed in WDOMS.&lt;/li&gt;
+&lt;li&gt;Successful primary source verification of that qualification via EPIC.&lt;/li&gt;
+&lt;li&gt;Evidence of the required period of supervised clinical practice (in Pakistan, typically your House Job/internship year, or equivalent postgraduate clinical experience).&lt;/li&gt;
+&lt;li&gt;Evidence of knowledge of English at the GMC's required standard.&lt;/li&gt;
+&lt;li&gt;A pass in both the UKMLA AKT and UKMLA CPSA (or their PLAB 1/PLAB 2 equivalents, which IMGs continue to book through the same GMC systems).&lt;/li&gt;
+&lt;li&gt;No unresolved fitness-to-practise concerns that would prevent registration.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;Primary source verification through EPIC deserves particular attention because it is frequently the slowest step in the entire pathway. EPIC contacts your medical school directly to confirm your degree, graduation date, and academic record, rather than accepting documents you submit yourself. Response times from Pakistani medical schools vary considerably: some of the larger, more established institutions with dedicated registrar offices respond within four to six weeks, while others — particularly if your request arrives during university holidays or a change of administrative staff — can take two to four months. Starting your EPIC verification as early as possible, ideally as soon as you have finished your House Job, is the single most effective way to avoid the pathway stalling before it has really begun.&lt;/p&gt;
+&lt;p&gt;It is worth being clear about what the GMC actually checks at this stage, because candidates sometimes conflate degree recognition with clinical competence assessment — the two are entirely separate. EPIC and WDOMS verification only confirm that your qualification is genuine and was awarded by a legitimately recognised institution; they say nothing about your clinical knowledge or skill, which is assessed entirely separately by the AKT and CPSA. A doctor with an impeccably verified degree from a top Pakistani medical college still has to pass both UKMLA components on their own clinical merit — recognition of your degree is a gateway requirement, not a substitute for exam preparation.&lt;/p&gt;
+&lt;p&gt;Postgraduate qualifications add a further layer of nuance. Pakistani doctors who have completed FCPS training, a diploma, or other postgraduate qualifications through the College of Physicians and Surgeons Pakistan (CPSP) sometimes assume this automatically strengthens their GMC application or reduces the amount of supervised practice they must evidence. In most cases it does not change the core UKMLA requirement — you still need to pass the AKT and CPSA regardless of postgraduate specialisation — though relevant postgraduate experience can strengthen your CV when you later apply for NHS posts or specialty training, and some postgraduate qualifications may support applications for GMC specialist registration further down the line, which is a separate process from initial UKMLA-based registration.&lt;/p&gt;
+&lt;p&gt;The GMC reviews its requirements periodically; always verify current rules on the &lt;a href="/official-resources"&gt;GMC website&lt;/a&gt; before applying, since eligibility criteria, WDOMS listings, and accepted verification routes can change with limited notice.&lt;/p&gt;
+&lt;h2&gt;How to Apply for the UKMLA From Pakistan: Step by Step&lt;/h2&gt;
+&lt;p&gt;Once you understand the eligibility landscape, the practical application process for &lt;strong&gt;UKMLA Pakistan&lt;/strong&gt; candidates follows a defined sequence. Each step below can, in most cases, be started from Pakistan without travelling to the UK — with the single exception of the CPSA itself.&lt;/p&gt;
+&lt;h3&gt;Step 1: Create a GMC Online Account&lt;/h3&gt;
+&lt;p&gt;Your first formal step is registering for a GMC Online account at gmc-uk.org. This account becomes the single hub for your entire application: booking exams, uploading documents, tracking your EPIC verification status, and eventually submitting your registration application. Use a personal email address you will retain long-term, not a university or hospital email that may be deactivated after you leave a post. Double-check that your name is entered exactly as it appears on your passport, since mismatches between your passport, MBBS certificate, and other documents are a recurring source of delay for Pakistani applicants (a name recorded with different spellings or a missing middle name on different documents is extremely common and worth resolving via affidavit before it becomes a problem).&lt;/p&gt;
+&lt;h3&gt;Step 2: Begin EPIC Verification&lt;/h3&gt;
+&lt;p&gt;With your GMC Online account active, start your EPIC application (accessed via the Intealth/ECFMG EPIC portal, which the GMC links to directly from its registration guidance). You will need scanned copies of your MBBS degree certificate, academic transcripts, and House Job/internship completion certificate. EPIC will then contact your medical school to confirm these documents independently — you cannot accelerate this by submitting more paperwork yourself, but you can accelerate it by contacting your medical school's registrar office in advance to let them know a verification request is coming and to confirm who should handle it.&lt;/p&gt;
+&lt;p&gt;Pakistani doctors should be aware that some medical colleges charge an internal administrative fee to process EPIC verification requests, separate from the EPIC service fee itself. Ask your college's examination or academic affairs department about this directly, since it is not always advertised.&lt;/p&gt;
+&lt;h3&gt;Step 3: Gather English Language Evidence&lt;/h3&gt;
+&lt;p&gt;In parallel with EPIC verification — not after it — begin preparing for and sitting your English language test, either IELTS Academic or OET Medicine. Running your English test preparation alongside EPIC verification, rather than waiting for one to finish before starting the other, is one of the most effective time-saving strategies available to Pakistani candidates, since both processes can easily take two to four months independently. Full requirements are covered in the dedicated section below; consult &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/before-you-apply-guide-for-doctors/evidence-of-your-knowledge-of-english"&gt;the GMC's English language evidence requirements&lt;/a&gt; for the authoritative and most current version of the rules.&lt;/p&gt;
+&lt;h3&gt;Step 4: Submit Your GMC Registration Application and Open the 90-Day Window&lt;/h3&gt;
+&lt;p&gt;Once your EPIC verification is complete and your English language evidence is in hand, you formally submit your GMC registration application through GMC Online. This triggers a 90-day window within which you must complete the remaining steps of your application — including submitting any outstanding documents. Missing this window generally means restarting parts of the process, so do not open your application until you are confident you can move quickly through the remaining stages. Full detail on this stage is in our &lt;a href="/registration-guide"&gt;GMC registration process&lt;/a&gt; guide.&lt;/p&gt;
+&lt;h3&gt;Step 5: Book and Sit the UKMLA AKT&lt;/h3&gt;
+&lt;p&gt;With your application in progress, you can book your UKMLA AKT (the exam Pakistani IMGs continue to access via the PLAB 1 route) through Pearson VUE. Bookings typically open several months ahead of &lt;a href="/news#ukmla-key-dates-sitting-schedule"&gt;sitting dates&lt;/a&gt;, and slots at popular centres and dates fill quickly — check the current &lt;a href="/key-dates"&gt;UKMLA sitting schedule&lt;/a&gt; as soon as you are eligible to book so you can plan preparation time around a confirmed date rather than guessing. For candidates who want a refresher on the mechanics of booking specifically through the PLAB 1 route, see our guide on &lt;a href="/news#how-to-register-plab-1"&gt;registering for PLAB 1&lt;/a&gt;.&lt;/p&gt;
+&lt;h3&gt;Step 6: Book and Sit the UKMLA CPSA in Manchester&lt;/h3&gt;
+&lt;p&gt;Once you have passed the AKT, you become eligible to book the UKMLA CPSA — the practical OSCE-style clinical and communication assessment accessed via the PLAB 2 route. Unlike the AKT, this cannot be sat inside Pakistan; it takes place exclusively at the GMC's Clinical Assessment Centre in Manchester. This means budgeting for international travel, UK accommodation, and typically one to two weeks in the country for final preparation and the exam itself. Our detailed guide on &lt;a href="/news#plab-2-preparation-guide"&gt;preparing for the PLAB 2 clinical assessment&lt;/a&gt; covers station types, common pitfalls, and how to structure your final weeks of practice.&lt;/p&gt;
+&lt;h3&gt;Step 7: Submit Your Full Registration Application&lt;/h3&gt;
+&lt;p&gt;After passing both the AKT and CPSA, and with your English language evidence, EPIC verification, and supervised practice documentation all confirmed, you submit your full application for registration with a licence to practise. The GMC reviews the complete file and, assuming no outstanding fitness-to-practise concerns, grants registration — at which point you are legally entitled to work as a doctor in the UK. Processing typically takes four to eight weeks from a complete, correctly documented submission, though incomplete files can extend this considerably.&lt;/p&gt;
+&lt;p&gt;Most Pakistani IMGs apply first for provisional registration if they have not yet completed a recognised internship equivalent to a UK &lt;a href="/what-is-ukmla"&gt;Foundation Year 1&lt;/a&gt;, or full registration with a licence to practise if their House Job satisfies the GMC's supervised practice requirement. The distinction matters because it determines what kind of post you are legally permitted to start in. &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/registration-applications/application-guides/provisional-registration-for-international-medical-graduates"&gt;The GMC's provisional registration guide for international medical graduates&lt;/a&gt; sets out exactly which category applies to your circumstances and what additional supervision requirements, if any, follow from provisional rather than full registration. Reading this guide before you submit your application avoids the common error of applying for the wrong registration type and having to resubmit.&lt;/p&gt;
+&lt;h2&gt;UKMLA AKT Test Centres in Pakistan&lt;/h2&gt;
+&lt;p&gt;One of the most practically useful facts for Pakistani candidates is that the AKT does not require travel to the UK. The AKT is delivered through the Pearson VUE global network, which operates authorised test centres within Pakistan itself. &lt;strong&gt;UKMLA AKT test centres in Pakistan&lt;/strong&gt; are typically available in major cities — Karachi, Lahore, and Islamabad are the most commonly used locations, reflecting Pearson VUE's broader network of professional and academic testing centres in these cities. Availability at any given centre depends on Pearson VUE's current contracted locations and can change, so always confirm the live list of centres and open dates directly through the official GMC/Pearson VUE booking portal at the time you are ready to book, rather than relying on where a friend or colleague sat previously.&lt;/p&gt;
+&lt;p&gt;Because the AKT can be sat locally, most Pakistani candidates avoid the cost and disruption of international travel for this component entirely — a significant financial and logistical advantage over the CPSA. Popular test dates and centres, particularly in Karachi and Lahore, can fill up several weeks or months in advance around peak booking periods, so treat "I'll book closer to the date" as a risk rather than a plan. Check the current &lt;a href="/key-dates"&gt;UKMLA sitting schedule&lt;/a&gt; and book as soon as your eligibility and preparation timeline allow.&lt;/p&gt;
+&lt;p&gt;The CPSA, by contrast, has no equivalent local option. Every candidate worldwide — regardless of where they trained or sat the AKT — must travel to Manchester, UK, to sit the CPSA in person. There is currently no Pakistan-based or remote alternative for this practical component, since it requires physical interaction with simulated patients and in-person examiner assessment that cannot be replicated remotely. Pakistani candidates should treat the Manchester trip as a fixed, non-negotiable part of the pathway and budget accordingly — flights, a UK visa if required, accommodation for the exam period, and often a short period of local acclimatisation and final practice before the assessment itself.&lt;/p&gt;
+&lt;h2&gt;UKMLA Exam Fees in Pakistan: Costs in PKR&lt;/h2&gt;
+&lt;p&gt;Cost is consistently one of the first questions Pakistani doctors ask about this pathway, and &lt;strong&gt;UKMLA &lt;a href="/fees"&gt;exam fees&lt;/a&gt; in Pakistan&lt;/strong&gt; need to be understood in both GBP (the currency the GMC actually charges in) and approximate PKR, since most candidates are budgeting and saving in rupees. As of 2026, the headline GMC fees are &lt;strong&gt;£283 for the AKT&lt;/strong&gt; (PLAB 1), &lt;strong&gt;£1,036 for the CPSA&lt;/strong&gt; (PLAB 2), &lt;strong&gt;£481 for initial GMC registration&lt;/strong&gt;, and &lt;strong&gt;£431 per year for annual retention&lt;/strong&gt; once registered.&lt;/p&gt;
+&lt;p&gt;The table below converts these into approximate Pakistani rupees using indicative exchange rates. These figures move with the GBP/PKR exchange rate on any given day, so treat them as planning estimates rather than fixed amounts.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Fee Item&lt;/th&gt;&lt;th&gt;Amount (GBP)&lt;/th&gt;&lt;th&gt;Approximate Amount (PKR)&lt;/th&gt;&lt;th&gt;When Payable&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;UKMLA AKT (PLAB 1)&lt;/td&gt;&lt;td&gt;£283&lt;/td&gt;&lt;td&gt;~PKR 104,000&lt;/td&gt;&lt;td&gt;At booking, before sitting&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;UKMLA CPSA (PLAB 2)&lt;/td&gt;&lt;td&gt;£1,036&lt;/td&gt;&lt;td&gt;~PKR 381,000&lt;/td&gt;&lt;td&gt;At booking, after passing AKT&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC initial registration&lt;/td&gt;&lt;td&gt;£481&lt;/td&gt;&lt;td&gt;~PKR 177,000&lt;/td&gt;&lt;td&gt;On submitting your full application&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Annual retention fee&lt;/td&gt;&lt;td&gt;£431&lt;/td&gt;&lt;td&gt;~PKR 158,000&lt;/td&gt;&lt;td&gt;Every January once registered&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Total core fees (first attempt only)&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;~£1,800&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;~PKR 662,000&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Across the full pathway&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;These core fees do not represent the full financial picture. Pakistani candidates should additionally budget for the English language test (IELTS Academic typically costs the equivalent of roughly PKR 65,000–75,000 in Pakistan; OET is broadly comparable), EPIC verification fees (payable in USD, generally equivalent to PKR 100,000–140,000 depending on the number of credentials verified), &lt;a href="/preparation"&gt;question bank&lt;/a&gt; subscriptions, and — the largest additional variable — flights, accommodation, and living costs for the Manchester CPSA trip, which for most Pakistani candidates adds a further PKR 250,000–500,000 depending on how far in advance flights are booked and how long the UK stay is.&lt;/p&gt;
+&lt;p&gt;The GMC reviews its requirements periodically; always verify current rules on the GMC website before applying, and treat the PKR figures above as indicative only — check the live GBP/PKR exchange rate and the GMC's current published fee schedule before transferring money or committing to a booking date.&lt;/p&gt;
+&lt;p&gt;It is also worth understanding how Pakistan's costs compare with those facing IMGs from other countries, since the GMC fees themselves are identical worldwide — the variation comes entirely from currency conversion, travel distance to Manchester, and local test preparation pricing. For a full breakdown of every fee item across every IMG route, including how UK medical students' costs differ from those paid by overseas graduates, see &lt;a href="/news#ukmla-fees-for-img-2026"&gt;the full IMG fee breakdown across every route&lt;/a&gt;. Candidates who compare their total budget against this wider picture are generally better prepared for the cash-flow reality of paying several large fees at different, unpredictable points over eighteen months to three years, rather than in one predictable lump sum.&lt;/p&gt;
+&lt;p&gt;A practical budgeting tip specific to Pakistani candidates: because the AKT, CPSA, and registration fees fall at different and sometimes unpredictable points in your timeline, avoid converting your entire savings into GBP at once. Exchange rate movements between PKR and GBP over an eighteen-month to three-year pathway can be substantial, and converting funds in stages closer to each actual payment date, rather than early in a lump sum, generally reduces your exposure to adverse currency swings.&lt;/p&gt;
+&lt;h2&gt;English Language Requirements for Pakistani Doctors&lt;/h2&gt;
+&lt;p&gt;Even though English is widely used as the medium of instruction throughout Pakistani medical education, the GMC requires independent, standardised evidence of English language proficiency from all IMGs, including Pakistani graduates. There is no exemption for candidates whose MBBS was taught in English. Two tests are accepted:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;IELTS Academic:&lt;/strong&gt; the GMC requires an overall score of &lt;strong&gt;7.0&lt;/strong&gt;, with a minimum of &lt;strong&gt;7.0 in each of the four domains&lt;/strong&gt; — Listening, Reading, Writing, and Speaking. Some guidance historically referenced a higher overall figure, so always confirm the exact current threshold on the GMC website before booking, since minor revisions to required bands do occur.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;OET (Occupational English Test), Medicine version:&lt;/strong&gt; the GMC requires a minimum of &lt;strong&gt;Grade B&lt;/strong&gt; in all four sub-tests (Listening, Reading, Writing, Speaking). OET's healthcare-specific scenarios are often more intuitive for practising or recently graduated doctors than IELTS's general academic content, since the material mirrors real clinical communication rather than abstract academic topics.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;Both tests are available at multiple centres within Pakistan, so this step — like the AKT — does not require travel abroad. Karachi, Lahore, Islamabad, and several other cities host regular IELTS and OET sittings throughout the year. Full official detail, including any recent changes to accepted scores or accepted test variants, is set out in &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/before-you-apply-guide-for-doctors/evidence-of-your-knowledge-of-english"&gt;the GMC's English language evidence requirements&lt;/a&gt;, which should always be checked directly rather than relied upon from secondhand summaries.&lt;/p&gt;
+&lt;p&gt;A critical detail Pakistani candidates frequently overlook: English language test results are only valid for a limited period — generally &lt;strong&gt;two years&lt;/strong&gt; from the test date — for the purposes of GMC registration. If your pathway (EPIC verification, AKT, CPSA, and final registration submission) takes longer than this window, your English test may expire before you reach the registration stage, forcing a costly and time-consuming retake. Sitting your English test too early, before your other pathway steps are realistically on track to finish within two years, is a common and avoidable mistake.&lt;/p&gt;
+&lt;h2&gt;Life and Career for Pakistani Doctors in the NHS After Registration&lt;/h2&gt;
+&lt;p&gt;Once GMC registration with a licence to practise is granted, Pakistani doctors are legally entitled to work in any NHS post they are qualified and appointed to. For most newly registered IMGs without prior UK clinical experience, the realistic entry points are Foundation-equivalent posts or clinical fellow positions, rather than direct entry into specialty training.&lt;/p&gt;
+&lt;p&gt;Clinical fellow posts are advertised individually by NHS trusts, sit outside the formal &lt;a href="/news#foundation-programme-after-ukmla"&gt;Foundation Programme&lt;/a&gt; structure, and carry responsibilities broadly comparable to a Foundation Year 2 or Core Trainee doctor. These posts are a common and realistic entry route for Pakistani IMGs, since they do not require the same competitive national application process as Foundation Programme places reserved primarily for &lt;a href="/news#uk-medical-schools-ukmla-implementation"&gt;UK medical school&lt;/a&gt; graduates. Search NHS Jobs (jobs.nhs.uk) and individual trust career pages directly, and expect competition to be higher for popular specialties (such as &lt;a href="/news#cardiology-ukmla-akt-revision"&gt;cardiology&lt;/a&gt;, &lt;a href="/news#dermatology-ukmla-revision"&gt;dermatology&lt;/a&gt;, or &lt;a href="/news#emergency-medicine-ukmla-revision"&gt;emergency medicine&lt;/a&gt;) and desirable geographic locations (London, the South East, and major teaching hospital cities).&lt;/p&gt;
+&lt;p&gt;From a clinical fellow or equivalent post, the standard route into structured training is applying for Core Training (CT1) or Specialty Training (ST1) posts through the national recruitment rounds once you have accrued sufficient UK clinical experience and, where relevant, passed any required specialty entrance examinations (such as MRCP or MRCS parts). Many Pakistani doctors use their first one to two years in an NHS clinical fellow role specifically to build the UK-specific clinical experience, references, and familiarity with NHS systems that make a subsequent training application competitive. Career progression from there follows the same structured pathway available to any doctor on the UK register — through core and higher specialty training toward consultant grade, or via the GP training route toward general practice.&lt;/p&gt;
+&lt;p&gt;Salary and working conditions for these grades are set nationally under the NHS terms and conditions for doctors and dentists in training, meaning pay scales, banding supplements for out-of-hours work, and annual leave entitlements are broadly consistent across trusts, though cost of living — particularly housing — varies considerably by region, with London and the South East being notably more expensive than the Midlands, North of England, Scotland, Wales, or Northern Ireland.&lt;/p&gt;
+&lt;p&gt;Many Pakistani doctors also weigh up geography deliberately rather than accepting the first available post. Trusts in the North West, North East, Scotland, and parts of Wales often advertise more clinical fellow vacancies relative to the number of applicants than London and the South East, simply because fewer doctors actively seek posts there, which can mean a faster route into employment and a materially lower cost of living, even though headline salaries are nationally banded and do not vary by region in the same way. Pakistani doctors already established in these regions frequently form informal networks — through mosques, Pakistani medical associations, and hospital-based community groups — that help newly arrived colleagues find accommodation, understand local schooling options for families, and settle into life outside the exam process itself. Family relocation, visa sponsorship under the Health and Care Worker visa route, and registering with a GP and dentist are practical steps that are easy to overlook amid exam preparation but become urgent the moment a job offer is confirmed, so it is worth researching them in outline before you reach this stage rather than starting from zero once you have a start date.&lt;/p&gt;
+&lt;h2&gt;Timeline: From Graduation in Pakistan to NHS Registration&lt;/h2&gt;
+&lt;p&gt;Pakistani doctors consistently underestimate how long the full pathway takes when every step is accounted for. A realistic timeline, assuming reasonably efficient progress and no major setbacks, looks like this:&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Stage&lt;/th&gt;&lt;th&gt;Realistic Duration&lt;/th&gt;&lt;th&gt;Key Variable&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;Completing MBBS and House Job/internship&lt;/td&gt;&lt;td&gt;Fixed by your degree programme&lt;/td&gt;&lt;td&gt;Not compressible&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;EPIC verification of primary qualification&lt;/td&gt;&lt;td&gt;1 to 4 months&lt;/td&gt;&lt;td&gt;Speed of your medical school's response&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;English language test preparation and sitting&lt;/td&gt;&lt;td&gt;1 to 4 months (can run in parallel with EPIC)&lt;/td&gt;&lt;td&gt;Baseline English proficiency&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC application submission and 90-day window&lt;/td&gt;&lt;td&gt;Up to 90 days once opened&lt;/td&gt;&lt;td&gt;Must not be allowed to lapse&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;AKT booking and preparation&lt;/td&gt;&lt;td&gt;2 to 6 months preparation; booking 3-6 months ahead&lt;/td&gt;&lt;td&gt;Local test centre availability in Karachi, Lahore, Islamabad&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA preparation, travel, and sitting in Manchester&lt;/td&gt;&lt;td&gt;2 to 4 months preparation; limited yearly sittings&lt;/td&gt;&lt;td&gt;Availability of Manchester slots; visa processing if required&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Full GMC registration processing&lt;/td&gt;&lt;td&gt;4 to 8 weeks after complete submission&lt;/td&gt;&lt;td&gt;Document completeness&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;NHS job search and start date&lt;/td&gt;&lt;td&gt;1 to 3 months from registration&lt;/td&gt;&lt;td&gt;NHS recruitment cycles and specialty competition&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;Adding these stages together, most Pakistani doctors who progress efficiently and without major delays should expect a total timeline of &lt;strong&gt;eighteen months to three years&lt;/strong&gt; from finishing their House Job to starting their first NHS post. Candidates who run EPIC verification and English testing in parallel, prepare thoroughly enough to pass the AKT and CPSA on the first attempt, and book exam dates as early as they become eligible consistently land toward the shorter end of this range. Those who wait for one step to fully finish before starting the next, or who need &lt;a href="/appeals-and-resits"&gt;resit&lt;/a&gt;s, often find themselves at three years or beyond.&lt;/p&gt;
+&lt;h2&gt;Common Mistakes Pakistani Doctors Make on This Route&lt;/h2&gt;
+&lt;p&gt;Several recurring errors slow down or derail otherwise well-qualified Pakistani candidates. Being aware of them in advance is one of the cheapest ways to protect your timeline and budget.&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Starting EPIC verification late.&lt;/strong&gt; Because EPIC depends on your medical school's response time rather than your own effort, delaying the start of this step by even a few months can add months to your overall timeline. Begin EPIC as soon as your House Job is complete, even before you have fully decided on your English test or AKT date.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Underestimating the true cost of the Manchester trip for the CPSA.&lt;/strong&gt; Candidates budget the £1,036 exam fee itself but frequently underestimate flights, UK accommodation for a week or two, local transport, and the cost of any final in-person or online preparation course. A realistic Manchester trip budget is significantly higher than the headline exam fee alone.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Letting English language test results expire.&lt;/strong&gt; IELTS and OET results are valid for a limited period — generally two years — for GMC registration purposes. Sitting the test too early relative to your realistic overall timeline risks the result expiring before you reach the final registration stage, forcing an expensive and entirely avoidable retake.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Name mismatches across documents.&lt;/strong&gt; Differences between the name on your MBBS certificate, your CNIC, and your passport (common due to transliteration variations or omitted middle names) can stall both EPIC verification and GMC registration. Resolve these with a notarised affidavit early, rather than when a document is rejected mid-application.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Sitting the AKT without a structured question bank strategy.&lt;/strong&gt; Some candidates read broadly around clinical topics without doing enough &lt;a href="/news#mock-exams-ukmla-preparation"&gt;timed practice&lt;/a&gt; questions in the actual UKMLA &lt;a href="/news#ukmla-akt-format-preparation"&gt;AKT format&lt;/a&gt;. Investing time in &lt;a href="/news#ukmla-question-bank-and-mock-tests"&gt;choosing a good AKT question bank&lt;/a&gt; and working through it systematically, rather than passively reading textbooks, is strongly associated with first-attempt passes.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Not understanding the resit rules before attempting the exam under-prepared.&lt;/strong&gt; Treating a first AKT or CPSA attempt as a "trial run" is an expensive strategy given the fees involved. Review &lt;a href="/news#ukmla-resits-rules-limits"&gt;the resit rules if you don't pass first time&lt;/a&gt; before your first sitting so you know exactly what a failed attempt costs you in both money and ti</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Pakistani doctor UKMLA route</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>/images/ukmla-for-pakistani-doctors-featured.webp</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani doctors - medical graduate from Pakistan preparing GMC registration and AKT exam documents</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>5321</v>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>A complete route guide for Nigerian medical graduates covering UKMLA eligibility, MDCN-to-GMC recognition, exam costs in naira, and GMC registration.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>IMG Pathway</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>IMG Pathway, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/registration-and-licensing/join-our-registers/before-you-apply-guide-for-doctors/primary-source-verification-for-international-medical-graduates</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility &amp; Fees</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian doctors: eligibility, MDCN-to-GMC recognition, AKT and CPSA costs in naira, and the full GMC registration process for 2026.</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;UKMLA for Nigerian doctors&lt;/strong&gt; represents one of the most well-travelled international pathways to UK medical registration, reflecting the large and long-established community of Nigerian-trained doctors already working within the NHS. For graduates holding a medical degree recognised by the Medical and Dental Council of Nigeria (MDCN), the route to sitting the UKMLA and ultimately gaining full GMC registration follows a defined sequence of credential verification, English language testing, two structured examinations, and a formal registration application. None of these steps is individually complicated, but together they involve a level of administrative detail, cost, and patience that catches many first-time applicants off guard.&lt;/p&gt;
+&lt;p&gt;This guide walks through the entire journey specifically as it applies to doctors trained in Nigeria — from confirming that an MBBS or MBBCh degree from a Nigerian &lt;a href="/news#uk-medical-schools-ukmla-implementation"&gt;medical school&lt;/a&gt; satisfies GMC eligibility rules, through primary source verification, booking exams, and budgeting in naira for a pathway priced in pounds sterling. It also covers where Nigerian candidates can sit the &lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test (AKT)&lt;/a&gt; locally, why the &lt;a href="/exam-pattern/cpsa"&gt;Clinical and Professional Skills Assessment (CPSA)&lt;/a&gt; must be taken in Manchester, and the realistic timeline and common pitfalls that shape how long the whole process actually takes.&lt;/p&gt;
+&lt;p&gt;Nigerian doctors are not newcomers to the UK medical workforce. Nigerian-trained physicians have practised within the NHS for decades, and this established diaspora means that much of the practical, on-the-ground knowledge about how the process really works — rather than how it looks on paper — is already available through community networks. This guide sets out the formal requirements and pairs them with the practical detail that matters for planning a successful application.&lt;/p&gt;
+&lt;h2&gt;The UKMLA Route From Nigeria: A Quick Overview&lt;/h2&gt;
+&lt;p&gt;Before diving into each stage in detail, it helps to see the whole pathway from MDCN registration to NHS practice at a glance. The route for a Nigerian-trained doctor generally runs as follows:&lt;/p&gt;
+&lt;ol&gt;
+&lt;li&gt;&lt;strong&gt;Confirm eligibility:&lt;/strong&gt; Verify that your MBBS/MBBCh degree from an MDCN-recognised Nigerian medical school is accepted by the GMC, and that you hold full, unrestricted MDCN registration following your housemanship (internship) year.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Create a GMC Online account&lt;/strong&gt; and begin primary source verification of your medical qualification through EPIC (Electronic Portfolio of International Credentials).&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Sit and pass an approved English language test&lt;/strong&gt; — IELTS Academic or OET Medicine — unless you hold an accepted exemption.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Book and pass the UKMLA AKT&lt;/strong&gt; (the &lt;a href="/ukmla-vs-plab"&gt;PLAB 1&lt;/a&gt; equivalent for IMGs), sat at a Pearson VUE test centre, including in Nigeria.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Book and pass the UKMLA CPSA&lt;/strong&gt; (the PLAB 2 equivalent), which can only be sat in person at the GMC's Clinical Assessment Centre in Manchester.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Apply for GMC registration with a licence to practise&lt;/strong&gt; once both assessments are passed and all supporting documents are verified.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Apply for NHS posts&lt;/strong&gt; — typically clinical fellow roles, trust-grade positions, or Foundation Year 2-equivalent posts — and begin practising in the UK.&lt;/li&gt;
+&lt;/ol&gt;
+&lt;p&gt;Each of these stages has its own processing time, cost, and set of common delays, which are covered in the sections below. Understanding the full sequence early prevents the single most common planning mistake: assuming that passing the exams is the hard part, when in practice credential verification and document logistics often take longer than exam preparation itself. Many Nigerian candidates who have already sat postgraduate exams in Nigeria, or who are used to the relatively self-contained structure of MDCN processes, are surprised by how much of the UKMLA pathway depends on external parties responding promptly — medical school registrars, the MDCN head office, and GMC caseworkers — rather than on their own study effort alone. Treating the administrative track and the exam preparation track as two separate projects, run in parallel rather than one after the other, is the single biggest determinant of how quickly a Nigerian candidate reaches registration.&lt;/p&gt;
+&lt;h2&gt;MDCN Recognition and UKMLA Eligibility for Nigerian Doctors&lt;/h2&gt;
+&lt;p&gt;The starting point for any Nigerian doctor considering the UKMLA route is confirming basic eligibility. The GMC requires that your primary medical qualification comes from a medical school that is listed on the World Directory of Medical Schools and that your degree is recognised by the relevant national regulator — in Nigeria's case, the &lt;strong&gt;Medical and Dental Council of Nigeria (MDCN)&lt;/strong&gt;. Graduates of MDCN-accredited institutions such as the University of Ibadan, University of Lagos (CMUL), University of Nigeria Nsukka, Ahmadu Bello University, Obafemi Awolowo University, and other MDCN-recognised medical schools generally satisfy this first eligibility hurdle without difficulty, provided the school was accredited at the time of your graduation.&lt;/p&gt;
+&lt;p&gt;Beyond the medical school itself, the GMC also expects evidence that you have completed the mandatory housemanship (internship) year required by the MDCN and that you hold full, unrestricted registration with the MDCN rather than provisional or temporary registration. A Certificate of Good Standing confirming your registration status and disciplinary history is typically required as part of your application, and this must be requested directly from the MDCN — a step many candidates leave too late, given that Nigerian regulatory bodies can take several weeks to process such requests.&lt;/p&gt;
+&lt;p&gt;Full details of who is permitted to sit the exam, including specific rules for degrees awarded outside standard timeframes or through non-standard routes, are set out in the GMC's guidance on &lt;a href="/news#ukmla-eligibility-who-can-sit"&gt;confirming who can sit the exam&lt;/a&gt;. It is worth reading this in full before committing time and money to the process, since eligibility is assessed on a case-by-case basis for some qualification types. For a broader view of the requirements that apply across all international medical graduates, see the site's guide to &lt;a href="/eligibility"&gt;UKMLA eligibility requirements&lt;/a&gt;.&lt;/p&gt;
+&lt;h3&gt;Primary Source Verification via EPIC&lt;/h3&gt;
+&lt;p&gt;Once basic eligibility is confirmed, the GMC requires primary source verification of your Nigerian medical degree — meaning your qualification is confirmed directly with your medical school rather than accepted on the strength of a certificate alone. This is handled through EPIC (Electronic Portfolio of International Credentials), the platform used globally for this purpose. Nigerian medical schools vary considerably in how quickly they respond to EPIC verification requests; well-established schools with dedicated international relations or academic affairs offices tend to respond within four to eight weeks, while others can take three months or longer, particularly during examination periods or academic holidays.&lt;/p&gt;
+&lt;p&gt;Full detail on how primary source verification works, what documents are required, and how the GMC uses the resulting evidence is available directly from the regulator: see &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/before-you-apply-guide-for-doctors/primary-source-verification-for-international-medical-graduates"&gt;the GMC's primary source verification requirements for international medical graduates&lt;/a&gt;. Candidates are strongly advised to read this guidance before initiating their EPIC application, as incomplete submissions are one of the most common causes of delay.&lt;/p&gt;
+&lt;h3&gt;What Counts as MDCN Recognition in Practice&lt;/h3&gt;
+&lt;p&gt;It is worth being precise about what "MDCN-recognised" actually means for GMC purposes, because the two regulators are assessing slightly different things. The MDCN license to practise in Nigeria confirms that you are entitled to work as a doctor within the Nigerian health system; it does not, on its own, transfer any rights or recognition in the UK. The GMC instead looks at three separate elements: whether your medical school appears on the World Directory of Medical Schools for the relevant graduation year, whether the degree programme itself met minimum duration and curriculum standards, and whether you can produce primary evidence — degree certificate, full transcripts, and internship completion documentation — that stands up to independent verification. A doctor can hold perfectly valid MDCN registration and still face delays at the GMC stage if, for example, their medical school's WDOMS listing lapsed for a period, or if academic transcripts are incomplete. Checking your medical school's current WDOMS status before you begin is a five-minute task that can save weeks of confusion later.&lt;/p&gt;
+&lt;h3&gt;Documents Nigerian Candidates Should Gather Early&lt;/h3&gt;
+&lt;p&gt;Beyond the primary degree certificate itself, most Nigerian applicants need a consistent set of supporting documents, and gathering them in parallel rather than sequentially saves considerable time:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;MBBS/MBBCh degree certificate&lt;/strong&gt; and full academic transcripts, year by year, from your medical school.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Housemanship (internship) completion certificate&lt;/strong&gt; confirming you completed the mandatory MDCN-supervised internship year.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;MDCN Certificate of Good Standing&lt;/strong&gt;, confirming your registration status and disciplinary record, requested directly from the MDCN head office in Abuja.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;International passport&lt;/strong&gt;, valid well beyond your expected registration date.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Evidence of any name changes&lt;/strong&gt; — marriage certificates or statutory declarations — where your degree name and passport name differ, which is a common source of query for Nigerian applicants with traditional and Western name variants.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Certified translations&lt;/strong&gt; of any document not already issued in English, from a recognised professional translation service.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;Requesting the MDCN Certificate of Good Standing early is particularly important, since this document is issued by a separate national body from your medical school and follows its own, often slower, administrative timeline.&lt;/p&gt;
+&lt;h2&gt;How to Apply for the UKMLA From Nigeria: Step by Step&lt;/h2&gt;
+&lt;p&gt;With eligibility confirmed, the practical application process for a Nigerian doctor follows six sequential steps. Each is described below in the order it should typically be actioned.&lt;/p&gt;
+&lt;h3&gt;Step 1: Create Your GMC Online Account&lt;/h3&gt;
+&lt;p&gt;Registration begins with creating a GMC Online account at the GMC's official website. This account becomes your central hub for the entire process — you will use it to track your EPIC verification status, book both the AKT and CPSA, submit your English language evidence, and eventually complete your registration application. Use a personal email address you will retain long-term, not a university or hospital email that may be deactivated after you leave a post, since GMC Online correspondence can span well over a year for most Nigerian candidates.&lt;/p&gt;
+&lt;h3&gt;Step 2: Begin EPIC Verification Early&lt;/h3&gt;
+&lt;p&gt;As covered above, EPIC verification of your MBBS/MBBCh degree is usually the single longest step in the entire pathway. Start this as early as possible — ideally before you have finalised your English test date or exam bookings — because it runs in parallel with other preparation and does not require your active involvement once submitted, beyond following up with your medical school if there are delays. Keep a written record of every communication with your medical school's registrar, as this becomes useful evidence if you need to escalate a delayed response.&lt;/p&gt;
+&lt;h3&gt;Step 3: Gather and Submit English Language Evidence&lt;/h3&gt;
+&lt;p&gt;In parallel with EPIC verification, sit your English language test (IELTS Academic or OET Medicine — full detail in the dedicated section below) and upload your certificate to GMC Online once results are issued. Many Nigerian candidates assume that because their medical education was conducted in English, this requirement can be waived; in practice, formal evidence is still required in almost all cases, so it is worth booking a test slot early rather than waiting to find out whether an exemption applies.&lt;/p&gt;
+&lt;h3&gt;Step 4: Book and Prepare for the AKT&lt;/h3&gt;
+&lt;p&gt;Once your GMC Online account is active, you can book the AKT through the Pearson VUE booking system linked from your account. Booking windows typically open several months ahead of each testing period, and popular Nigerian test centre dates fill quickly, so book as soon as a suitable slot appears rather than waiting until the last moment. Preparation should draw on &lt;a href="/news#mla-content-map-explained"&gt;the official MLA content map&lt;/a&gt;, which defines exactly what conditions, presentations, and professional knowledge areas are examinable, and a structured &lt;a href="/preparation"&gt;question bank&lt;/a&gt; — see the guidance on &lt;a href="/news#ukmla-question-bank-and-mock-tests"&gt;choosing a good AKT question bank&lt;/a&gt; for a comparison of the main options available to Nigerian candidates.&lt;/p&gt;
+&lt;h3&gt;Step 5: Book and Prepare for the CPSA&lt;/h3&gt;
+&lt;p&gt;The CPSA can only be booked once you have passed the AKT. Because the CPSA is only available in Manchester, Nigerian candidates need to plan a UK trip around this stage, factoring in visa arrangements, flights, and several days of accommodation for preparation immediately before the assessment. Many candidates combine the trip with a short period of UK clinical observation or shadowing beforehand, which helps with the specific communication and consultation style the CPSA examines.&lt;/p&gt;
+&lt;h3&gt;Step 6: Submit Your GMC Registration Application&lt;/h3&gt;
+&lt;p&gt;Once both the AKT and CPSA are passed, and your EPIC verification, English language evidence, and any outstanding documents (Certificate of Good Standing, internship completion certificate, identity documents) are all confirmed, you can submit your full application for GMC registration with a licence to practise. Full step-by-step detail on this final stage is available in the site's &lt;a href="/registration-guide"&gt;GMC registration process&lt;/a&gt; guide, which covers document checklists, processing times, and what to do if your application is queried.&lt;/p&gt;
+&lt;h2&gt;UKMLA AKT Test Centres in Nigeria&lt;/h2&gt;
+&lt;p&gt;One of the most practical advantages of the UKMLA/PLAB 1 route for Nigerian candidates is that the AKT can be sat locally rather than requiring international travel. The AKT is delivered through the Pearson VUE global network of test centres, which includes locations in major Nigerian cities. &lt;strong&gt;Lagos and Abuja&lt;/strong&gt; are the most commonly used Nigerian test centres for the AKT, with availability that fluctuates by testing window — candidates should check the live list of centres and open dates directly through their GMC Online account or the Pearson VUE booking portal, as centre availability in Nigeria can change between sitting periods.&lt;/p&gt;
+&lt;p&gt;This is a significant contrast with the CPSA. Unlike the AKT, the &lt;strong&gt;CPSA cannot be sat anywhere in Nigeria, or indeed anywhere outside the UK&lt;/strong&gt; — it is held exclusively at the GMC's purpose-built Clinical Assessment Centre in Manchester, with occasional additional London dates in periods of high demand. This means every Nigerian candidate must, at minimum, make one trip to the UK to complete their UKMLA pathway, even if the AKT is passed entirely from Lagos or Abuja without leaving Nigeria. Budgeting for this single mandatory UK trip — flights, a UK visitor visa if required, accommodation, and living costs for the preparation and exam period — should be built into &lt;a href="/news#ukmla-fees-explained"&gt;financial planning&lt;/a&gt; from the very start of the process, not left until after the AKT is passed.&lt;/p&gt;
+&lt;h2&gt;UKMLA Exam Cost in Nigeria: Fees in Naira&lt;/h2&gt;
+&lt;p&gt;Cost is consistently one of the biggest practical concerns for Nigerian doctors evaluating the UKMLA pathway, both because the fees themselves are substantial in absolute terms and because the naira has experienced significant and sustained volatility against the pound in recent years. The table below sets out the core GMC and Pearson VUE fees in pounds sterling alongside an approximate naira equivalent, so Nigerian candidates can budget realistically. For &lt;a href="/fees"&gt;the full UKMLA fee schedule&lt;/a&gt; covering every fee across the pathway, including &lt;a href="/appeals-and-resits"&gt;re-sit&lt;/a&gt; charges, see the dedicated fees guide.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Fee Item&lt;/th&gt;&lt;th&gt;Amount (GBP)&lt;/th&gt;&lt;th&gt;Approximate Amount (NGN)&lt;/th&gt;&lt;th&gt;When Payable&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;AKT / PLAB 1 exam fee&lt;/td&gt;&lt;td&gt;£283&lt;/td&gt;&lt;td&gt;~₦620,000&lt;/td&gt;&lt;td&gt;At booking&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA / PLAB 2 exam fee&lt;/td&gt;&lt;td&gt;£1,036&lt;/td&gt;&lt;td&gt;~₦2,270,000&lt;/td&gt;&lt;td&gt;At booking&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC initial registration fee&lt;/td&gt;&lt;td&gt;£481&lt;/td&gt;&lt;td&gt;~₦1,055,000&lt;/td&gt;&lt;td&gt;On application, after both exams passed&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Annual retention fee&lt;/td&gt;&lt;td&gt;£431&lt;/td&gt;&lt;td&gt;~₦945,000&lt;/td&gt;&lt;td&gt;Annually in January, once registered&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Total core fees (first attempt)&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;£1,800&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;~₦3,945,000&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Across the full pathway to registration&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;These naira figures are indicative and calculated at a broadly representative exchange rate; they will shift with market movements between the time this guide is written and the time you make a payment. &lt;strong&gt;Exchange rates for the naira have fluctuated significantly in recent years&lt;/strong&gt;, and a gap of even a few months between budgeting and paying can materially change the naira cost of a given fee. The GMC reviews its requirements periodically; always verify current rules and current fee amounts on the &lt;a href="/official-resources"&gt;GMC website&lt;/a&gt; before applying, and check live exchange rates at the time you actually transfer funds rather than relying on figures calculated months in advance.&lt;/p&gt;
+&lt;p&gt;Beyond these core fees, Nigerian candidates should budget separately for EPIC verification charges, English language test fees, flights and accommodation for the mandatory Manchester CPSA trip, UK visitor visa costs if applicable, and study materials. Together these additional costs commonly add £1,500–£3,000 on top of the core GMC fees, so a realistic total budget for a first-attempt pass across the whole pathway is closer to £3,300–£4,800 once every cost is included.&lt;/p&gt;
+&lt;p&gt;Because so much of this budget is denominated in pounds while income and savings are typically held in naira, many Nigerian candidates choose to build their fund gradually over several months rather than attempting a single large currency purchase close to a payment deadline. Spreading currency purchases over time, using a specialist international transfer provider rather than a standard bank counter rate, and tracking the mid-market rate rather than relying on a single bureau de change quotation are all practical ways to reduce the effective cost of converting naira to pounds across the pathway. Some candidates also time larger purchases around periods of relative naira stability rather than during periods of sharp depreciation, though this requires ongoing attention to the foreign exchange market rather than a one-off decision.&lt;/p&gt;
+&lt;h2&gt;English Language Requirements for Nigerian Doctors&lt;/h2&gt;
+&lt;p&gt;English is the language of instruction throughout Nigerian medical education, which leads many Nigerian doctors to assume that formal English testing will not apply to them. In practice, the GMC requires documentary evidence of English language proficiency from the great majority of international medical graduates regardless of the language of their medical training, and Nigerian degrees are not automatically exempt. Candidates should plan for formal testing as a standard part of the pathway rather than hoping for a waiver.&lt;/p&gt;
+&lt;p&gt;Two tests are accepted: &lt;strong&gt;IELTS Academic&lt;/strong&gt;, where the GMC requires an overall score of &lt;strong&gt;7.0, with no individual component (Listening, Reading, Writing, Speaking) below 7.0&lt;/strong&gt;, and &lt;strong&gt;OET (Occupational English Test), Medicine version&lt;/strong&gt;, where the GMC requires a minimum of &lt;strong&gt;Grade B in all four sub-tests&lt;/strong&gt;. OET is often more intuitive for practising doctors because its scenarios are built entirely around healthcare communication — referral letters, doctor-patient consultations, and clinical case notes — rather than general academic topics. IELTS Academic, by contrast, draws on a broader range of subject matter and has more widely available preparation material in Nigeria.&lt;/p&gt;
+&lt;p&gt;Both test certificates have a defined validity period from the date of the test, so timing matters: sitting the test too early relative to your overall pathway risks the certificate expiring before you submit your registration application, which would require a costly and time-consuming re-sit. Full detail on accepted scores, accepted test providers, and how evidence is submitted is available directly from the regulator at &lt;a href="https://www.gmc-uk.org/registration-and-licensing/join-our-registers/before-you-apply-guide-for-doctors/evidence-of-your-knowledge-of-english"&gt;the GMC's English language evidence requirements&lt;/a&gt;. It is worth reading this page in full, since the specific evidentiary requirements are updated from time to time and always take precedence over general summaries.&lt;/p&gt;
+&lt;h2&gt;Life and Career for Nigerian Doctors in the NHS After Registration&lt;/h2&gt;
+&lt;p&gt;Once GMC registration is secured, Nigerian doctors join a well-established diaspora community within the NHS. Nigerian-trained doctors have practised in the UK for decades, and Nigeria remains consistently among the largest source countries for internationally trained doctors on the UK medical register. This means new arrivals typically find peer networks, informal mentorship, and professional associations — including Nigerian doctor associations active in most major NHS regions — already in place to help with the practical realities of settling into UK practice.&lt;/p&gt;
+&lt;p&gt;Career progression after registration generally follows one of several routes: a trust-grade or clinical fellow post (the most common entry point for newly registered IMGs, offering FY2-equivalent clinical responsibility without requiring a &lt;a href="/news#foundation-programme-after-ukmla"&gt;Foundation Programme&lt;/a&gt; place), a Specialty Training application once sufficient UK experience and portfolio evidence are in place, or locum work through NHS staff banks and agencies for those who want flexibility while building their UK clinical track record. Many Nigerian doctors who enter through clinical fellow posts subsequently progress into core or specialty training within two to three years, particularly in specialties experiencing significant workforce shortages such as general internal medicine, &lt;a href="/news#psychiatry-communication-cpsa-stations"&gt;psychiatry&lt;/a&gt;, and &lt;a href="/news#emergency-medicine-ukmla-revision"&gt;emergency medicine&lt;/a&gt;, where competition ratios for IMG applicants tend to be more favourable.&lt;/p&gt;
+&lt;p&gt;It is worth noting that the broad shape of this journey — degree recognition, credential verification, English testing, a knowledge exam, a clinical skills exam, then registration — mirrors &lt;a href="/news#how-to-become-a-doctor-in-uk-from-india"&gt;the equivalent route for doctors coming from India&lt;/a&gt;, another country with a very large diaspora presence in the NHS, even though the specific verification bodies and typical processing times differ between the two countries.&lt;/p&gt;
+&lt;p&gt;Day-to-day life for newly registered Nigerian doctors in the NHS typically involves an adjustment period covering both clinical and cultural dimensions. Clinically, the biggest early adjustments tend to be around NHS documentation standards (structured handover formats such as SBAR), a strong institutional emphasis on multidisciplinary team working, and a more codified approach to consent and capacity than many candidates are accustomed to from Nigerian practice. Socially, Nigerian doctors moving to the UK are joining one of the more established migrant professional communities in the NHS, with active Nigerian doctor associations, church and community networks, and informal mentorship arrangements in most major cities, particularly London, Manchester, Birmingham, and other regions with substantial Nigerian populations. Salary progression follows the standard NHS pay scale for the relevant grade, and while it can take time to reach specialty training, most Nigerian doctors who remain committed to the pathway report that the structured nature of UK training — clear competency frameworks, protected training time, and defined progression points — compares favourably with less standardised systems elsewhere.&lt;/p&gt;
+&lt;h2&gt;Timeline: From Graduation in Nigeria to NHS Registration&lt;/h2&gt;
+&lt;p&gt;Nigerian candidates consistently underestimate how long the full pathway takes, largely because exam preparation time is easy to plan for while administrative processing time is not. The table below sets out a realistic stage-by-stage timeline based on typical current processing periods.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Stage&lt;/th&gt;&lt;th&gt;Typical Duration&lt;/th&gt;&lt;th&gt;Key Variable&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;MDCN Certificate of Good Standing request&lt;/td&gt;&lt;td&gt;2 to 8 weeks&lt;/td&gt;&lt;td&gt;MDCN processing backlog&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;EPIC primary source verification&lt;/td&gt;&lt;td&gt;4 weeks to 4 months&lt;/td&gt;&lt;td&gt;Speed of your medical school's response&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;English language test preparation and sitting&lt;/td&gt;&lt;td&gt;1 to 4 months&lt;/td&gt;&lt;td&gt;Baseline English proficiency&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;AKT preparation&lt;/td&gt;&lt;td&gt;3 to 6 months&lt;/td&gt;&lt;td&gt;Study intensity, prior NHS knowledge&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;AKT booking to sitting (Lagos/Abuja)&lt;/td&gt;&lt;td&gt;4 to 12 weeks&lt;/td&gt;&lt;td&gt;Test centre date availability&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA preparation, including UK travel planning&lt;/td&gt;&lt;td&gt;2 to 4 months&lt;/td&gt;&lt;td&gt;Visa processing, budget readiness&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA booking to sitting (Manchester)&lt;/td&gt;&lt;td&gt;2 to 6 months&lt;/td&gt;&lt;td&gt;Limited sitting capacity&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC registration application processing&lt;/td&gt;&lt;td&gt;4 to 8 weeks&lt;/td&gt;&lt;td&gt;Document completeness&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;NHS job search and start date&lt;/td&gt;&lt;td&gt;1 to 3 months&lt;/td&gt;&lt;td&gt;NHS recruitment cycles, specialty demand&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;Adding these stages together, most Nigerian candidates should plan for a realistic total timeline of &lt;strong&gt;18 to 30 months&lt;/strong&gt; from beginning EPIC verification to starting their first NHS post, assuming first-attempt passes at both the AKT and CPSA. Candidates who fail either assessment on their first attempt, or who face delays at the MDCN or EPIC stage, should expect this to extend further. Planning around the longer end of this range from the outset avoids the financial and psychological strain of a timeline that assumes everything goes smoothly.&lt;/p&gt;
+&lt;h2&gt;Common Mistakes Nigerian Doctors Make on This Route&lt;/h2&gt;
+&lt;p&gt;Several avoidable errors recur consistently among Nigerian candidates pursuing the UKMLA pathway. Most of these mistakes are not clinical — they are planning and administrative errors that have nothing to do with medical knowledge, yet they are responsible for a disproportionate share of the delays and extra costs Nigerian candidates experience. Being aware of them in advance, before you have committed money to a specific exam date or travel booking, can save months of delay and hundreds of pounds in wasted fees.&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Starting EPIC verification too late.&lt;/strong&gt; Because EPIC processing time depends heavily on your medical school's administrative speed rather than your own effort, this step should be initiated before — not after — you begin AKT preparation. Candidates who wait until they are ready to book the AKT before starting EPIC often lose two to three months they could have used productively.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Underestimating the true cost of the Manchester CPSA trip.&lt;/strong&gt; The £1,036 exam fee itself is only part of the cost. Flights from Lagos or Abuja, several nights of Manchester accommodation, local transport, food, and — for many candidates — a short UK preparation course before the exam, can together add £1,000–£2,000 on top of the fee. Candidates who budget only for the headline fee frequently find themselves scrambling for additional funds close to their exam date.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Not accounting for naira exchange rate volatility.&lt;/strong&gt; Because all UKMLA and GMC fees are charged in pounds sterling, a Nigerian candidate who calculates their naira budget many months before actually paying can find the real cost has risen substantially by the time payment is due. Build a buffer of at least 15–20% above your initial naira budget calculation, and monitor exchange rates in the weeks leading up to each payment rather than assuming an old estimate still holds.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Letting English test certificates expire.&lt;/strong&gt; Both IELTS and OET certificates are valid for a defined period from the test date. Candidates who sit their English test early in the process — before EPIC verification or AKT preparation is complete — sometimes find their certificate has expired by the time they are ready to submit their full registration application, forcing a costly re-sit. Sequence your English test so its validity period comfortably covers your expected registration application date.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Treating document translation and certification casually.&lt;/strong&gt; Any document not already in English requires a certified professional translation, not an informal translation from a bilingual colleague. Underestimating the time this takes, or submitting translations that do not meet the GMC's certification standard, is a common cause of application delay.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Assuming AKT and CPSA preparation can be compressed into the final weeks.&lt;/strong&gt; Both assessments draw on a specific, defined content base — &lt;a href="/news#mla-content-map-explained"&gt;the official MLA content map&lt;/a&gt; for the AKT and a structured OSCE circuit for the CPSA — and candidates who begin serious preparation only a few weeks before their booked date typically underperform relative to their actual clinical knowledge.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2&gt;Frequently Asked Questions&lt;/h2&gt;
+&lt;h3&gt;Can Nigerian doctors sit the UKMLA AKT without travelling outside Nigeria?&lt;/h3&gt;
+&lt;p&gt;Yes. The AKT is delivered through Pearson VUE test centres, and Nigeria has centres in &lt;strong&gt;Lagos and Abuja&lt;/strong&gt; where the AKT can be sat without international travel. Candidates should confirm current centre availability through their GMC Online account or the Pearson VUE booking portal, as available dates and locations can vary between testing windows.&lt;/p&gt;
+&lt;h3&gt;Do I have to travel to the UK for the CPSA?&lt;/h3&gt;
+&lt;p&gt;Yes, this step cannot be avoided. The CPSA is held exclusively at the GMC's Clinical Assessment Centre in &lt;strong&gt;Manchester&lt;/strong&gt;, with occasional additional London dates during periods of high demand. There is no option to sit the CPSA remotely or anywhere within Nigeria, so every Nigerian candidate must budget for at least one trip to the UK to complete their UKMLA pathway.&lt;/p&gt;
+&lt;h3&gt;Is a Nigerian MBBS or MBBCh degree automatically accepted by the GMC?&lt;/h3&gt;
+&lt;p&gt;Degrees from MDCN-accredited Nigerian medical schools generally satisfy the GMC's basic eligibility requirement, provided the school was properly accredited at the time you graduated and your qualification is listed on the World Directory of Medical Schools. However, acceptance also depends on completing primary source verification through EPIC and holding full, unrestricted MDCN registration following your housemanship year. Always confirm your specific situation against the current guidance on &lt;a href="/news#ukmla-eligibility-who-can-sit"&gt;confirming who can sit the exam&lt;/a&gt; rather than assuming eligibility automatically.&lt;/p&gt;
+&lt;h3&gt;How much does the whole UKMLA process cost in naira?&lt;/h3&gt;
+&lt;p&gt;The core GMC and exam fees — AKT, CPSA, and initial registration — total approximately £1,800, which converts to roughly ₦3.9 million at broadly representative exchange rates, though this figure moves with the market. Once English testing, EPIC verification, Manchester travel and accommodation, and study materi</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Nigerian doctor UKMLA route</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>/images/ukmla-for-nigerian-doctors-featured.webp</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian doctors - medical graduate from Nigeria reviewing GMC registration and UKMLA exam requirements</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>5083</v>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>A detailed, evidence-based comparison of UKMLA vs USMLE covering cost, difficulty, exam format, and career pathways for IMGs choosing between the UK and US routes.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Exam Comparisons</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Exam Comparisons, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/education/medical-licensing-assessment/plab-and-the-mla</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Should You Take?</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE compared: cost, difficulty, format, career outcomes and which route gets IMGs into practice faster in 2026.</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;UKMLA vs USMLE&lt;/strong&gt; is one of the defining decisions facing medical graduates who want to practise in an English-speaking healthcare system but did not train in the UK or the United States. Every year, thousands of doctors from India, Pakistan, Nigeria, Egypt, and across the Middle East reach the same fork in the road: commit to the UK's Medical Licensing Assessment and the &lt;a href="/registration-guide"&gt;GMC registration&lt;/a&gt; pathway, or commit to the United States Medical Licensing Examination and the long road through ECFMG certification to a US residency Match. Both are legitimate, respected routes into world-class healthcare systems. Both are expensive, time-consuming, and unforgiving of poor planning. Neither is inherently "better" — but they are very different in structure, cost, timeline, and the kind of candidate they suit.&lt;/p&gt;
+&lt;p&gt;This decision is rarely made with full information. Candidates hear fragments — that the USMLE is "more theoretical," that the UKMLA is "cheaper," that the US Match is "impossible without a US rotation," that the UK route is "faster" — and these fragments are sometimes true, sometimes outdated, and often missing the context that would make them useful. The reality is that UKMLA and USMLE are built on different philosophies of assessment and different models of how a &lt;a href="/what-is-ukmla"&gt;newly qualified doctor&lt;/a&gt; enters supervised practice, and comparing them fairly means looking past headline claims to the actual exam structures, the actual fees, and the actual employment outcomes each route leads to.&lt;/p&gt;
+&lt;p&gt;This guide lays out the full comparison: exam format, cost, difficulty, career outcomes, and the practical question of whether a candidate can — or should — attempt both routes at once. Wherever a claim cannot be verified against official sources, that is stated plainly rather than glossed over, because an honest "we don't know" is more useful to a candidate planning a multi-year, multi-thousand-pound or multi-thousand-dollar commitment than a confident-sounding guess.&lt;/p&gt;
+&lt;p&gt;It is also worth stating upfront why this decision has become more urgent for many candidates in recent years. The UK's move from the older PLAB system to the unified Medical Licensing Assessment framework, completed in August 2024, changed the practical shape of the UK pathway considerably, and candidates researching older forum posts or outdated blog content may be working from information that no longer reflects current fees, format, or &lt;a href="/news#ukmla-eligibility-who-can-sit"&gt;eligibility rules&lt;/a&gt;. On the US side, the retirement of Step 2 Clinical Skills in 2021 and the move to pass/fail scoring for Step 1 in 2022 similarly changed what the USMLE sequence actually demands of a candidate compared to a decade ago. Anyone comparing UKMLA and USMLE using pre-2021 information is, in effect, comparing two exams that no longer exist in their described form — which is precisely why this guide anchors every comparison point to current, verifiable figures rather than received wisdom passed between candidates.&lt;/p&gt;
+&lt;h2&gt;UKMLA vs USMLE at a Glance&lt;/h2&gt;
+&lt;p&gt;Before going into the detail of each exam, the table below summarises the core structural differences between the two pathways. It compares the number of exam stages, the total cost, the format of assessment, where each exam can be sat, the licensing body responsible, the realistic time to practise, and whether a competitive placement process (like the US Match) stands between passing the exam and starting supervised clinical work.&lt;/p&gt;
+&lt;table class="post-table"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th&gt;Feature&lt;/th&gt;&lt;th&gt;UKMLA Route&lt;/th&gt;&lt;th&gt;USMLE Route&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;Number of exam stages&lt;/td&gt;&lt;td&gt;2 (AKT + CPSA)&lt;/td&gt;&lt;td&gt;3 (Step 1, Step 2 CK, Step 3)&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Core exam cost (IMG)&lt;/td&gt;&lt;td&gt;~&lt;strong&gt;£1,800&lt;/strong&gt; (AKT + CPSA + registration)&lt;/td&gt;&lt;td&gt;~&lt;strong&gt;$3,465–$3,665&lt;/strong&gt; (Steps 1–3 + ECFMG)&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Format&lt;/td&gt;&lt;td&gt;Computer-based single-best-answer test (AKT) + in-person 18-station OSCE (CPSA)&lt;/td&gt;&lt;td&gt;Computer-based multiple-choice/case-based tests (Steps 1, 2 CK) + computer-based case simulations (Step 3)&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Where you can sit it&lt;/td&gt;&lt;td&gt;AKT: Pearson VUE centres worldwide. CPSA: Manchester only&lt;/td&gt;&lt;td&gt;Steps 1, 2 CK and most of Step 3: Prometric centres worldwide. Some Step 3 components/US clinical exposure often needed for competitiveness&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Licensing/certifying body&lt;/td&gt;&lt;td&gt;General Medical Council (GMC)&lt;/td&gt;&lt;td&gt;ECFMG (certification) + individual US State Medical Boards (licensure)&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Realistic time to practise (IMG)&lt;/td&gt;&lt;td&gt;12–24 months from first booking to working in the NHS&lt;/td&gt;&lt;td&gt;3–6+ years from first Step attempt to starting residency, due to Match competitiveness&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Competitive placement process&lt;/td&gt;&lt;td&gt;IMG placement via NHS trust job applications; no centralised Match&lt;/td&gt;&lt;td&gt;Mandatory NRMP Match — highly competitive for IMGs, especially in ROL-sensitive specialties&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;&lt;/table&gt;
+&lt;p&gt;The single biggest structural difference is not the exams themselves but what happens after passing them. The UKMLA route ends in GMC registration, after which an IMG applies directly for NHS trust jobs like any other job-seeker. The USMLE route ends in ECFMG certification, which only makes a candidate &lt;em&gt;eligible&lt;/em&gt; to enter the NRMP Match — a separate, highly competitive national process that determines whether, when, and where a candidate actually starts residency. This difference in what comes after the exams is often more decisive for candidates than the exams themselves, and it is explored fully in the careers section below.&lt;/p&gt;
+&lt;h2&gt;Exam Format Compared: AKT/CPSA vs USMLE Steps 1, 2 CK and 3&lt;/h2&gt;
+&lt;p&gt;The UKMLA and USMLE are built around different assessment philosophies. The UKMLA is a two-part, entry-level licensing exam sat close to the point of registration. The USMLE is a three-step sequence that spans a much longer period — from a candidate's basic sciences years through to the start of independent practice — and each step tests a distinct stage of clinical development.&lt;/p&gt;
+&lt;h3&gt;UKMLA: Applied Knowledge Test (AKT) + CPSA&lt;/h3&gt;
+&lt;p&gt;The UKMLA has exactly two components. The &lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test (AKT)&lt;/a&gt; is a single sitting of &lt;strong&gt;200 single-best-answer (SBA) questions&lt;/strong&gt; delivered over roughly three hours at a Pearson VUE computer-based test centre. It assesses applied clinical knowledge against the &lt;a href="/syllabus"&gt;MLA Content Map&lt;/a&gt; — the presentations, conditions, and clinical actions a newly qualified UK doctor is expected to recognise and manage safely. For IMGs, the AKT is accessed through the PLAB 1 route, which — as explained in &lt;a href="/ukmla-vs-plab"&gt;how UKMLA compares to the older PLAB system&lt;/a&gt; — has been fully aligned with the MLA standard since August 2024. Understanding &lt;a href="/news#ukmla-akt-format-preparation"&gt;the AKT's format and question types&lt;/a&gt; in detail is a critical first step for anyone weighing this route, because unlike the USMLE's Step 1, the AKT does not test pure basic sciences in isolation — every question is written as an applied clinical scenario.&lt;/p&gt;
+&lt;p&gt;The second component, the &lt;a href="/exam-pattern/cpsa"&gt;Clinical and Professional Skills Assessment (CPSA)&lt;/a&gt;, is an 18-station objective structured &lt;a href="/news#clinical-examination-cpsa-guide"&gt;clinical examination&lt;/a&gt; (OSCE) sat in person at the GMC's Clinical Assessment Centre in Manchester. It tests history-taking, examination, communication, clinical and procedural skills, and professional judgement against simulated patients and trained examiners. For IMGs, this is accessed through the PLAB 2 route. Both AKT and CPSA are marked against a pass mark set using a formal standard-setting process — worth understanding through &lt;a href="/news#angoff-standard-setting-explained"&gt;how the UKMLA pass mark is set using the Angoff method&lt;/a&gt; — rather than a fixed percentage, which means the "pass mark" moves slightly from sitting to sitting depending on the assessed difficulty of that specific paper.&lt;/p&gt;
+&lt;h3&gt;USMLE: Step 1, Step 2 CK and Step 3&lt;/h3&gt;
+&lt;p&gt;The USMLE, by contrast, is a three-step sequence, each administered as a separate computer-based exam through Prometric test centres, with content and eligibility rules set out in &lt;a href="https://www.usmle.org/step-exams"&gt;the official USMLE Step Exams overview&lt;/a&gt;. &lt;strong&gt;Step 1&lt;/strong&gt; tests foundational basic sciences — anatomy, physiology, biochemistry, pharmacology, pathology, &lt;a href="/news#infection-microbiology-ukmla-revision"&gt;microbiology&lt;/a&gt;, and behavioural sciences — applied to clinical scenarios. Since January 2022, Step 1 has been scored on a pass/fail basis only, a significant change from its previous three-digit numeric score, which has shifted its role in residency applications: it remains a mandatory hurdle but no longer functions as a fine-grained ranking tool for competitive specialties.&lt;/p&gt;
+&lt;p&gt;Step 1 is typically taken after a candidate has completed their basic sciences training, which for most international &lt;a href="/news#uk-medical-schools-ukmla-implementation"&gt;medical school&lt;/a&gt;s falls somewhere in years two to four of a five- or six-year programme. The exam itself is delivered as a single-day, multi-block session of multiple-choice items, and candidates are permitted a defined eligibility period from ECFMG in which to sit it — unlike the AKT, which any eligible IMG can book once English language and primary qualification requirements are met, Step 1 eligibility runs through ECFMG's own application and verification process, which itself takes several weeks to complete before a candidate can even schedule a test date. This upfront administrative step is often underestimated by first-time USMLE candidates and should be factored into overall timeline planning well before the first exam booking.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Step 2 Clinical Knowledge (Step 2 CK)&lt;/strong&gt; tests the application of clinical knowledge, diagnosis, and management across the major specialties, and — unlike Step 1 — retains a three-digit numeric score that residency programmes weigh heavily, since it is now the primary quantitative knowledge benchmark used to filter Match applicants. It is worth noting that the USMLE previously included a separate practical skills exam, Step 2 Clinical Skills (Step 2 CS), which required candidates to travel to a small number of US test centres to be assessed with standardised patients. Step 2 CS was suspended in 2020 during the COVID-19 pandemic and formally discontinued in January 2021; there is currently no in-person clinical skills component in the USMLE sequence for IMGs, which is a materially different position from the UK's CPSA, which remains a mandatory in-person OSCE.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Step 3&lt;/strong&gt; is the final step, combining multiple-choice questions with computer-based case simulations that test independent clinical decision-making. Step 3 is typically taken after a candidate has started US residency (for US-trained candidates) or, for many IMGs, before applying to residency in order to strengthen an ECFMG certification file — though its exact timing varies by candidate and by state licensing requirements. Together, the three steps span years rather than months, in contrast to the UKMLA's two-component structure, which most candidates complete within a single 12-month cycle. Candidates preparing for the AKT specifically often benefit from structured revision timing, such as &lt;a href="/news#three-months-ukmla-akt-countdown"&gt;a final three-month AKT preparation countdown&lt;/a&gt;, which has no direct equivalent in USMLE preparation culture given the longer runway most Step exams are prepared over.&lt;/p&gt;
+&lt;h2&gt;UKMLA vs USMLE Cost and Difficulty&lt;/h2&gt;
+&lt;p&gt;Cost is one of the most concrete, comparable data points between the two routes, and candidates deserve exact figures rather than vague ranges.&lt;/p&gt;
+&lt;p&gt;The UKMLA core pathway for an IMG totals approximately &lt;strong&gt;£1,800&lt;/strong&gt;: &lt;strong&gt;£283&lt;/strong&gt; for the AKT, &lt;strong&gt;£1,036&lt;/strong&gt; for the CPSA, and &lt;strong&gt;£481&lt;/strong&gt; for initial GMC registration. A full breakdown, including &lt;a href="/appeals-and-resits"&gt;re-sit&lt;/a&gt; costs, currency conversions, and hidden costs like travel to Manchester, is available in &lt;a href="/news#ukmla-fees-for-img-2026"&gt;the full UKMLA fee breakdown for IMGs&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;The USMLE core pathway costs considerably more in absolute terms. Step 1 costs approximately &lt;strong&gt;$985&lt;/strong&gt;, Step 2 CK costs approximately &lt;strong&gt;$985&lt;/strong&gt;, and Step 3 costs approximately &lt;strong&gt;$955–$1,295&lt;/strong&gt; depending on the jurisdiction issuing the licence (Step 3 fees are set by individual state medical boards via the Federation of State Medical Boards, so they vary). On top of the three Steps, IMGs must also pay for ECFMG certification, which costs approximately &lt;strong&gt;$200&lt;/strong&gt; for the application plus separate fees for primary source verification of medical school credentials. Taken together, the three Steps plus ECFMG certification bring the core USMLE pathway to roughly &lt;strong&gt;$3,500–$4,000&lt;/strong&gt;, before any consideration of visa costs, travel to the US for away rotations (commonly called "electives" or "sub-internships," which many IMGs pursue specifically to strengthen their Match application), or the cost of applying to residency programmes through ERAS, which itself charges per-programme fees that escalate steeply once a candidate applies to more than ten programmes.&lt;/p&gt;
+&lt;table class="post-table"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th&gt;Cost Item&lt;/th&gt;&lt;th&gt;UKMLA (IMG)&lt;/th&gt;&lt;th&gt;USMLE (IMG)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;Stage 1 fee&lt;/td&gt;&lt;td&gt;AKT: £283&lt;/td&gt;&lt;td&gt;Step 1: ~$985&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Stage 2 fee&lt;/td&gt;&lt;td&gt;CPSA: £1,036&lt;/td&gt;&lt;td&gt;Step 2 CK: ~$985&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Stage 3 fee&lt;/td&gt;&lt;td&gt;—&lt;/td&gt;&lt;td&gt;Step 3: ~$955–$1,295&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Certification/&lt;a href="/fees"&gt;registration fee&lt;/a&gt;&lt;/td&gt;&lt;td&gt;GMC registration: £481&lt;/td&gt;&lt;td&gt;ECFMG certification: ~$200 + verification fees&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Approximate core total&lt;/td&gt;&lt;td&gt;&lt;strong&gt;~£1,800&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;~$3,500–$4,000+&lt;/strong&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Typical major add-on cost&lt;/td&gt;&lt;td&gt;Travel/accommodation for CPSA in Manchester&lt;/td&gt;&lt;td&gt;US electives/away rotations, ERAS application fees per programme&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;&lt;/table&gt;
+&lt;p&gt;On difficulty, candidates should be wary of any source that claims a definitive cross-exam ranking — no independent, peer-reviewed study or official body has published a validated comparison of UKMLA and USMLE difficulty, because the two exams test different content domains using different psychometric models and different pass-mark methods, which makes a single "which is harder" number essentially unverifiable. What can be stated with confidence, because it is publicly reported, is that pass rates differ by candidate group on each exam: first-attempt pass rates for UK medical students on the AKT and CPSA are consistently higher than first-attempt pass rates for IMGs sitting the same assessments via PLAB, a pattern explained more by preparation context and familiarity with UK clinical guidelines than by any difference in exam standard, and the same dynamic applies to Step 1 and Step 2 CK, where first-attempt pass rates for US/Canadian medical students are reported by the USMLE programme as higher than those for IMGs. Neither programme publishes a difficulty score that is comparable to the other's, so any claim that "USMLE Step 1 is objectively harder than the UKMLA AKT" (or vice versa) should be treated as opinion, not fact.&lt;/p&gt;
+&lt;p&gt;Retake policy is a more concrete point of comparison. The UKMLA's AKT and CPSA have no official cap on the number of attempts for IMGs, though each re-sit incurs the full fee again. The USMLE permits a maximum of &lt;strong&gt;six attempts&lt;/strong&gt; at each Step, and most US state licensing boards and residency programmes apply increasing scrutiny — and in some cases automatic filtering — to applicants with multiple failed attempts on any Step, which functions as a de facto stricter ceiling than the raw attempt limit suggests. This is a meaningful practical difference: a UKMLA candidate who needs several attempts faces a cost and time penalty but not necessarily a structural barrier to eventual registration, whereas a USMLE candidate with multiple failed attempts may find their competitiveness for the Match materially and permanently reduced even if they eventually pass.&lt;/p&gt;
+&lt;p&gt;Waiting periods between attempts also differ in ways that affect how quickly a candidate can recover from a failed sitting. &lt;a href="/news#ukmla-preparation-for-imgs"&gt;IMGs who&lt;/a&gt; fail the AKT can typically re-book within a matter of weeks, subject to test centre availability, and there is no mandatory cooling-off period imposed by the GMC beyond practical scheduling constraints. USMLE candidates who fail a Step must generally wait a minimum period — historically around 60 days for a first re-attempt, extending further for candidates who have already failed multiple times — before they are eligible to sit that Step again, and eligibility periods issued by ECFMG can also constrain how many attempts are practically possible within a given certification window. Candidates budgeting a realistic timeline should build these enforced gaps into their planning rather than assuming a failed attempt simply costs money with no time penalty attached.&lt;/p&gt;
+&lt;h2&gt;UKMLA vs USMLE: Which Is Easier?&lt;/h2&gt;
+&lt;p&gt;There is no single honest answer to "UKMLA vs USMLE which is easier" — it depends heavily on the individual candidate's academic background, training language, and clinical exposure, and any source offering a flat one-line answer is oversimplifying a genuinely candidate-specific question. What can be done fairly is to break the comparison down by the kind of background a candidate brings to each exam.&lt;/p&gt;
+&lt;p&gt;Candidates with a strong basic-sciences foundation — those who excelled in preclinical years, are comfortable with biochemistry, physiology, and pharmacology at a mechanistic level, and enjoy exam formats that reward deep theoretical recall — often find USMLE Step 1 preparation aligns well with their existing strengths, even though it is now pass/fail. These candidates may also adapt comfortably to Step 2 CK's emphasis on management algorithms once they build clinical vignette practice. Conversely, candidates whose medical schools emphasised bedside clinical teaching, structured history-taking, and OSCE-style formative assessment throughout their degree — common in many UK-affiliated and Commonwealth curricula — often find the CPSA's station format less unfamiliar than it might first appear, because the skills it tests (systematic history-taking, examination technique, safety-netting, communication under time pressure) map closely onto training they have already received, even if the specific UK clinical guidelines are new to them.&lt;/p&gt;
+&lt;p&gt;English-medium training is a major differentiator on both routes, but it bites differently. On the USMLE, English proficiency mostly affects reading speed and precision on long, densely worded clinical vignettes under strict per-question time limits across all three Steps. On the UKMLA, English proficiency affects both the AKT (similar vignette-reading demands) and, more acutely, the CPSA, where real-time spoken communication with a simulated patient and examiner — including picking up conversational cues, explaining diagnoses in lay language, and responding to unscripted patient concerns — places a premium on spoken fluency that a purely computer-based exam does not test in the same way. Candidates from non-English-medium training backgrounds who are confident readers but less confident in spontaneous spoken English may find the AKT more approachable than the CPSA, while the reverse is rare, since the CPSA's live spoken component has no analogue in the current USMLE sequence following the discontinuation of Step 2 CS.&lt;/p&gt;
+&lt;p&gt;Time pressure is another dimension candidates often overlook when judging "difficulty" purely on content. The AKT allocates roughly three hours to 200 questions, which works out to under a minute per item once time is set aside for flagged-question review — a pace that rewards fast pattern recognition over slow, deliberate reasoning. USMLE Step 1 and Step 2 CK are longer overall (delivered across multiple blocks in a full-day session) but allow more time per individual question, which suits candidates who prefer to reason through vignettes methodically rather than answer on instinct. Candidates who perform well on rapid-fire question formats, such as those common in many South Asian and Middle Eastern undergraduate medical curricula, may find the AKT's pace more natural, while candidates trained in curricula that emphasise slower, case-based discussion may adapt more readily to the Step exams' pacing. Neither pacing style is inherently easier — they simply reward different exam-taking habits, which is one more reason a flat "which is easier" answer misses the point.&lt;/p&gt;
+&lt;p&gt;Candidates weighing this question in detail are well served by reading &lt;a href="/preparation"&gt;a full UKMLA preparation guide&lt;/a&gt; alongside official USMLE content outlines before committing, since the honest answer to "which is easier" is really "which is easier for you," and that can only be assessed against your own transcript, clinical exposure, and language comfort — not against a generic ranking.&lt;/p&gt;
+&lt;h2&gt;Career Outcomes: NHS vs US Residency&lt;/h2&gt;
+&lt;p&gt;The practical outcome after passing each exam sequence is arguably the most consequential difference between the two routes, and it is where the UKMLA and USMLE diverge most sharply.&lt;/p&gt;
+&lt;p&gt;In the UK, once an IMG passes the AKT and CPSA, meets the English language requirement, and completes GMC registration, they become directly eligible to apply for NHS jobs — there is no centralised matching algorithm standing between registration and employment. IMGs typically apply for Foundation Year 2-equivalent posts, Specialty/Trust doctor grade posts, or in some cases enter the &lt;a href="/news#foundation-programme-after-ukmla"&gt;Foundation Programme&lt;/a&gt; itself if eligible, applying through NHS Jobs and individual trust recruitment processes much like any other job-seeker, with interviews and offers happening on the same timeline as any advertised NHS post. Understanding &lt;a href="/news#how-to-become-a-doctor-in-uk-from-india"&gt;the India-to-UK route&lt;/a&gt; in practical terms is a useful starting point for candidates from South Asia specifically weighing timelines, since the process of turning GMC registration into an actual NHS job offer typically takes a matter of weeks to a few months once registration is secured, though it depends heavily on specialty competitiveness, location flexibility, and CV strength.&lt;/p&gt;
+&lt;p&gt;In the United States, ECFMG certification — which requires passing Step 1, Step 2 CK, and meeting medical education credentialing requirements — only makes a candidate &lt;em&gt;eligible&lt;/em&gt; to apply for residency positions. Actually securing a residency position requires successfully navigating the National Resident Matching Program (NRMP) Match, a centralised, once-yearly algorithmic process in which candidates rank programmes, programmes rank candidates, and a computer algorithm produces binding placements. The NRMP publishes its own Match statistics annually, and these consistently show that IMGs match at meaningfully lower rates than US MD and DO seniors, particularly for competitive specialties such as &lt;a href="/news#dermatology-ukmla-revision"&gt;dermatology&lt;/a&gt;, orthopaedic &lt;a href="/news#surgical-presentations-ukmla-revision"&gt;surgery&lt;/a&gt;, and plastic surgery, and particularly for IMGs without US clinical experience (USCE) on their CV. Many IMGs spend a year or more after finishing their Steps completing unpaid or low-paid US clinical observerships, externships, or research positions specifically to build a US-facing CV before entering the Match, and even then, a substantial proportion of IMG applicants do not match in their first Match cycle and must reapply in a subsequent year.&lt;/p&gt;
+&lt;p&gt;This structural difference has a direct effect on realistic timelines. An IMG pursuing the UK route who prepares well can realistically expect to move from first AKT booking to working in the NHS within roughly &lt;strong&gt;12 to 24 months&lt;/strong&gt;, assuming no major delays in visa processing or exam scheduling. An IMG pursuing the US route should realistically budget &lt;strong&gt;3 to 6 years or more&lt;/strong&gt; from first Step attempt to starting residency, once Step preparation time, USCE-building, ERAS application cycles, interview season, and the possibility of an unsuccessful first Match attempt are factored in. This is not a claim that the US route is inferior — US residency training and subsequent attending physician compensation are highly regarded globally, and many candidates judge the extended timeline a worthwhile trade-off — but it is a timeline difference that should be weighed honestly against personal, financial, and family circumstances rather than assumed away.&lt;/p&gt;
+&lt;p&gt;Visa and immigration pathways add a further layer that candidates frequently underweight when comparing the two systems. In the UK, IMGs typically enter under a Health and Care Worker visa once they have secured an NHS job offer, a route with a comparatively predictable application process, reduced visa fees, and no annual quota that a candidate might miss out on. In the US, IMGs who match into residency generally require either a J-1 exchange visitor visa, sponsored through ECFMG itself, or an H-1B visa sponsored by the employing institution — and H-1B sponsorship is subject to an annual lottery-based cap that is fully independent of the Match outcome, meaning a candidate can match into a residency position and still face visa uncertainty depending on the sponsoring programme's visa policy and the lottery result in a given year. The J-1 route avoids the lottery but carries its own complication: most J-1 physicians are subject to a two-year home-country physical presence requirement after training unless they obtain a waiver, commonly through the Conrad 30 programme, which requires committing to work in an underserved US area for a further period. Candidates should research their specific programme's visa sponsorship practices directly, since this varies considerably by institution and specialty, and it is a factor that sits entirely outside the exam comparison itself but materially affects how "complete" either pathway feels in practice.&lt;/p&gt;
+&lt;h2&gt;Which Countries Are Better Suited to the UK Route vs the US Route?&lt;/h2&gt;
+&lt;p&gt;Broad, evidence-based generalisations about candidate priorities — not stereotypes about ability — can help frame this decision, while recognising that individual circumstances always override national trends.&lt;/p&gt;
+&lt;p&gt;Candidates from countries with strong historical and Commonwealth ties to the UK — India, Pakistan, Nigeria, and several other Commonwealth nations — often find the UK route practically smoother for reasons unrelated to exam difficulty: familiarity with British English conventions and idiom, medical curricula that were historically modelled on UK undergraduate medical education, existing diaspora and professional networks within the NHS, and in many cases, existing family or community ties in the UK that ease the transition. The UK's absence of a centralised Match also appeals to candidates who prioritise a shorter, more predictable timeline to first employment over the specialty-matching precision the NRMP process offers.&lt;/p&gt;
+&lt;p&gt;Candidates from the Middle East and Gulf states sometimes weigh both routes evenly, given strong educational and economic ties to both the UK and the US, and the decision more often comes down to individual specialty ambitions (some competitive US specialties offer training and subsequent compensation structures not directly replicated in the NHS) or family preference for one country's lifestyle and long-term immigration pathway over the other. Candidates prioritising the highest achievable long-term specialist compensation, or a specific competitive specialty with a strong US training reputation, more frequently gravitate toward the USMLE route despite its longer and costlier pathway, while candidates prioritising a faster, lower-cost route into stable clinical employment with a clear structured training ladder (Foundation Programme, core training, specialty training) more frequently choose the UK route. Neither preference is right or wrong — they reflect genuinely different priorities that are worth naming explicitly rather than assuming one route is universally superior.&lt;/p&gt;
+&lt;h2&gt;Can You Do Both? Sitting UKMLA and USMLE&lt;/h2&gt;
+&lt;p&gt;A meaningful minority of candidates choose to pursue both routes in parallel as a deliberate hedge, keeping options open in case one country's job market, visa policy, or Match outcome proves less favourable than expected. This is logistically possible — nothing in either the GMC's or the USMLE programme's eligibility rules prevents a candidate from holding both a valid AKT/CPSA pass and USMLE Step passes simultaneously — but it comes with a real and often underestimated cost and time burden that should be planned for explicitly rather than treated as a low-risk add-on.&lt;/p&gt;
+&lt;p&gt;Financially, pursuing both routes roughly doubles the direct exam cost: a candidate attempting both pathways should budget for the full ~£1,800 UKMLA core cost and the full ~$3,500–$4,000 USMLE core cost, which at current exchange rates means a combined spend in the region of £4,500–£5,000 or more once currency conversion, travel for the CPSA (Manchester) and any US-based rotations, and preparation materials for both exams are included. Time is the scarcer resource in practice: preparing properly for the AKT's UK-guideline-specific content and the CPSA's OSCE stations draws on a different body of knowledge and skill than preparing for Step 1's basic-sciences depth and Step 2 CK's US-guideline-based management algorithms, and most candidates find they cannot productively prepare for both simultaneously at full intensity — the more common and more sustainable pattern is to sequence the two pathways, completing one exam sequence substantially before beginning serious preparation for the other, rather than interleaving study for both from day one.&lt;/p&gt;
+&lt;p&gt;Candidates considering this dual-track approach should be realistic about opportunity cost: building &lt;a href="/news#ukmla-question-bank-and-mock-tests"&gt;an effective AKT practice routine&lt;/a&gt; alongside a full USMLE Step 1 or Step 2 CK question bank rotation is achievable for strong, highly organised candidates with substantial dedicated study time, but it is not a lighter workload than either exam alone — it is closer to two full preparation cycles run back-to-back or in a tightly managed overlap, and candidates already working clinically while preparing should weigh whether the diversification benefit justifies the additional months or years of dual-track effort against simply committing fully to the single route that best fits their background and priorities.&lt;/p&gt;
+&lt;h2&gt;Frequently Asked Questions&lt;/h2&gt;
+&lt;h3&gt;Is UKMLA easier than USMLE?&lt;/h3&gt;
+&lt;p&gt;There is no independently verified, official ranking of UKMLA versus USMLE difficulty — the two exams test different content using different formats and different pass-mark methods, so no single "easier" answer applies to all candidates. What can be said is that a candidate's own academic background, clinical training style, and English fluency (spoken versus written) will make one route feel more approachable than the other on an individual basis, which is different from either exam being objectively harder.&lt;/p&gt;
+&lt;h3&gt;Which is cheaper, UKMLA or USMLE?&lt;/h3&gt;
+&lt;p&gt;The UKMLA core pathway for an IMG costs approximately &lt;strong&gt;£1,800&lt;/strong&gt; (AKT £283, CPSA £1,036, GMC registration £481). The USMLE core pathway costs approximately &lt;strong&gt;$3,500–$4,000&lt;/strong&gt; (Step 1 ~$985, Step 2 CK ~$985, Step 3 ~$955–$1,295, ECFMG certification ~$200 plus verification fees). On core exam and registration costs alone, the UKMLA route is meaningfully cheaper, though both routes carry substantial additional costs for travel, preparation materials, and — for the US route particularly — unpaid clinical experience-building before the Match.&lt;/p&gt;
+&lt;h3&gt;Can an IMG sit both UKMLA and USMLE?&lt;/h3&gt;
+&lt;p&gt;Yes. There is no rule preventing a candidate from pursuing both pathways, and some candidates do so as a deliberate hedge. However, this roughly doubles total cost and significantly increases the time and preparation burden, since the two exams draw on differ</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE comparison</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>/images/ukmla-vs-usmle-comparison-featured.webp</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE Comparison</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE comparison - side-by-side exam route decision for international medical graduates</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>5299</v>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Indian medical graduates often face a choice between NEET PG and the UKMLA route to the UK. This guide compares cost, competition, timelines and long-term career outcomes.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Exam Comparisons</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Exam Comparisons, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/education/medical-licensing-assessment</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Is Right for You?</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG compared: cost, competition, timelines and career outcomes to help Indian medical graduates choose the right path in 2026.</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;UKMLA vs NEET PG&lt;/strong&gt; is one of the most consequential decisions an Indian MBBS graduate will make, and unlike most exam-comparison questions, it is not really about which test is "harder" — it is about which country, which career shape, and which kind of postgraduate life you want. Every year, thousands of final-year and recently graduated MBBS students in India reach the same fork in the road: prepare for NEET PG (National Eligibility cum Entrance Test for Postgraduates) and compete for a limited number of MD/MS seats at home, or prepare for the UKMLA and PLAB route to register with the General Medical Council (GMC) and build a career inside the NHS. Both are legitimate, respected pathways followed by tens of thousands of doctors before you, and both demand serious, sustained preparation — but the exams themselves are built on entirely different logic.&lt;/p&gt;
+&lt;p&gt;This guide sets out the practical, evidence-based differences between the two routes: what each exam actually measures, how competitive each one really is, what each will cost you in money and time, what career and lifestyle outcomes typically follow, and — for the many candidates who don't want to close either door too early — whether it is realistic to prepare for both at once. Nothing here is designed to talk you into one path or the other. The aim is to give you the same clear-eyed comparison a careers counsellor with knowledge of both systems would give you, so that your decision is based on facts rather than rumour or peer pressure.&lt;/p&gt;
+&lt;p&gt;Throughout, we will also touch on &lt;strong&gt;UKMLA vs PLAB for Indian doctors&lt;/strong&gt;, since for most Indian MBBS graduates considering the UK route, PLAB registration and the UKMLA are now the same underlying pathway, and understanding that relationship matters before you compare it against NEET PG. If you are already leaning towards the UK and want the deeper mechanics of that specific comparison, &lt;a href="/ukmla-vs-plab"&gt;the full UKMLA vs PLAB comparison&lt;/a&gt; covers it in detail. Here, our focus is the bigger decision that comes before that: India or the UK, NEET PG or UKMLA.&lt;/p&gt;
+&lt;h2&gt;UKMLA vs NEET PG at a Glance&lt;/h2&gt;
+&lt;p&gt;Before going into the detail of each exam, it helps to see the two pathways side by side. The table below summarises the core structural differences that drive almost everything else in this comparison — from how you prepare to what your life looks like three years after you pass.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Feature&lt;/th&gt;&lt;th&gt;UKMLA Route (UK)&lt;/th&gt;&lt;th&gt;NEET PG Route (India)&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;Purpose of the exam&lt;/td&gt;&lt;td&gt;Confirms you meet the minimum competency standard for safe independent practice as a doctor in the UK (pass/fail against a fixed standard)&lt;/td&gt;&lt;td&gt;Ranks candidates competitively to allocate a fixed, limited number of MD/MS postgraduate seats in India&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Competition level&lt;/td&gt;&lt;td&gt;Not a ranking exam — you compete against a fixed standard, not against other candidates&lt;/td&gt;&lt;td&gt;Extremely competitive; a very large national applicant pool competes for a comparatively small number of seats in sought-after specialties and colleges&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Cost (exam only)&lt;/td&gt;&lt;td&gt;Approximately &lt;strong&gt;£1,800&lt;/strong&gt; total (AKT + CPSA + GMC registration) — roughly &lt;strong&gt;₹1,90,000–₹2,00,000&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;NEET PG exam fee is comparatively low (a few thousand rupees), but realistic total cost including coaching and repeat attempts is often far higher&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Format&lt;/td&gt;&lt;td&gt;Two components: a computer-based knowledge test (AKT) and a practical clinical skills assessment (CPSA)&lt;/td&gt;&lt;td&gt;Single-day computer-based objective test (MCQ-based) covering the full MBBS curriculum&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Outcome if you pass&lt;/td&gt;&lt;td&gt;Eligible for &lt;a href="/registration-guide"&gt;GMC registration&lt;/a&gt; and entry into UK &lt;a href="/news#foundation-programme-after-ukmla"&gt;Foundation Programme&lt;/a&gt; / IMG NHS placement pathways&lt;/td&gt;&lt;td&gt;Eligible to participate in centralised/state counselling for MD/MS or PG diploma seat allocation, subject to your rank&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Typical timeline&lt;/td&gt;&lt;td&gt;Several months of structured preparation, exam booking, and GMC registration processing before starting clinical work in the UK&lt;/td&gt;&lt;td&gt;Often 1–2+ years of intensive preparation, frequently including a coaching-supported "drop year," before securing a seat&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;The single most important row in that table is the second one. NEET PG is a zero-sum ranking exam: your score only matters relative to everyone else's score, because the number of seats is fixed and does not expand to meet demand. The UKMLA, by contrast, is a threshold exam: if you meet the required standard, you pass, regardless of how many other candidates also passed that sitting. This distinction shapes almost every other difference discussed below, so it is worth returning to before making any final decision.&lt;/p&gt;
+&lt;h2&gt;What Each Exam Actually Tests&lt;/h2&gt;
+&lt;p&gt;Although both exams are ultimately rooted in the same MBBS-level clinical knowledge base, they are built for different purposes, and that shows up clearly in what they actually test and how they score you. It also shows up in how each exam is administered day to day: NEET PG is a single, high-stakes national sitting held once a year on a fixed date, whereas the UKMLA's components — accessed by Indian IMGs via the PLAB route — are offered across multiple sittings throughout the year at testing centres around the world, giving candidates considerably more flexibility over when they sit and how they pace their preparation.&lt;/p&gt;
+&lt;h3&gt;UKMLA: AKT and CPSA as a Readiness Check&lt;/h3&gt;
+&lt;p&gt;The UKMLA is formally the Medical Licensing Assessment administered by the GMC — &lt;a href="https://www.gmc-uk.org/education/medical-licensing-assessment"&gt;the GMC's official Medical Licensing Assessment overview&lt;/a&gt; sets out the full assessment framework — and it has two components. The &lt;strong&gt;&lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test (AKT)&lt;/a&gt;&lt;/strong&gt; is a 200-question single-best-answer computer-based exam, sat over roughly three hours, that tests whether a candidate can apply clinical knowledge safely — not simply recall facts, but reason through applied clinical scenarios the way a newly qualified UK doctor would need to. Every question maps to &lt;a href="/news#mla-content-map-explained"&gt;the official content map behind every AKT question&lt;/a&gt;, which defines the presentations, conditions, and clinical actions a safe &lt;a href="/what-is-ukmla"&gt;Foundation Year 1&lt;/a&gt; doctor in the UK must be able to handle.&lt;/p&gt;
+&lt;p&gt;The second component, the &lt;strong&gt;&lt;a href="/exam-pattern/cpsa"&gt;Clinical and Professional Skills Assessment (CPSA)&lt;/a&gt;&lt;/strong&gt;, is a practical OSCE-style exam with 18 stations covering history-taking, physical examination, clinical communication, &lt;a href="/news#blood-tests-data-interpretation-akt"&gt;data interpretation&lt;/a&gt;, and practical procedures. Both components are graded against a fixed, pre-determined standard — set using recognised standard-setting methodology — rather than curved against how other candidates performed. In other words, the UKMLA asks one question: "does this doctor meet the minimum bar for safe independent practice in the UK?" It does not ask "how does this doctor compare to everyone else who sat the exam this year?"
+For candidates coming from the PLAB route specifically, it helps to understand &lt;a href="/news#ukmla-vs-plab-difference"&gt;how the older PLAB numbering maps onto today's UKMLA&lt;/a&gt; — PLAB 1 and PLAB 2 have effectively become the IMG delivery mechanism for the AKT and CPSA respectively.&lt;/p&gt;
+&lt;h3&gt;NEET PG: A Competitive Ranking Exam for Limited Seats&lt;/h3&gt;
+&lt;p&gt;NEET PG, conducted by &lt;a href="https://natboard.edu.in/"&gt;the National Board of Examinations in Medical Sciences, which conducts NEET PG&lt;/a&gt; (NBEMS), is structurally different. It is a single computer-based objective test covering pre-clinical, para-clinical, and clinical subjects from the full MBBS curriculum, and it produces a percentile-based score and an all-India rank. That rank — not a pass/fail threshold — is what determines whether, and where, you get a postgraduate seat. Two candidates can both comfortably clear the qualifying percentile and still end up with entirely different postgraduate outcomes, because seat allocation in the subsequent counselling rounds depends on relative rank, category, domicile status, and seat availability in a given specialty and institution, not on an absolute knowledge threshold.&lt;/p&gt;
+&lt;p&gt;This means NEET PG tests two things simultaneously: whether you know the MBBS curriculum well enough to practise safely (a threshold concern, broadly similar in spirit to the UKMLA), and how you perform relative to every other MBBS graduate sitting that year (a ranking concern, which the UKMLA does not have at all). It is this second layer — the ranking mechanism — that defines the NEET PG experience for most candidates and drives the intensity of preparation culture around it in India.&lt;/p&gt;
+&lt;p&gt;There is also a practical difference in how the two exams treat clinical skills. NEET PG is a single written paper — it does not include any face-to-face clinical or communication component, so a candidate's ability to take a history, examine a patient, or communicate with a distressed family is not directly assessed at the postgraduate entrance stage; those skills are instead developed and assessed later, during the MD/MS residency itself. The UKMLA route builds that assessment in far earlier, through the CPSA, precisely because the GMC's remit is to confirm a doctor is safe to practise independently in front of real patients from day one of employment, not simply that they hold sufficient theoretical knowledge to begin structured training. Neither approach is wrong — they reflect the different point in a doctor's career at which each exam sits — but it is a genuine difference in what a pass certificate actually verifies.&lt;/p&gt;
+&lt;h2&gt;Competition and Realistic Odds&lt;/h2&gt;
+&lt;p&gt;The single biggest structural difference between these two exams is this: &lt;strong&gt;NEET PG is a competitive ranking exam with a very large applicant pool competing for a limited number of MD/MS seats, while the UKMLA is a competency threshold exam that you pass or fail against a fixed standard — not against other candidates.&lt;/strong&gt; Understanding this distinction properly is more useful than any single statistic, because it explains why the lived experience of preparing for each exam feels so different.&lt;/p&gt;
+&lt;p&gt;Every year, a very large number of MBBS graduates across India sit NEET PG, while the number of MD/MS seats — particularly in high-demand clinical specialties at well-regarded government and deemed university colleges — remains comparatively limited. This is a structural feature of Indian medical education, not a temporary bottleneck, and it means that even highly capable, hard-working graduates can spend one or more additional years attempting to improve their rank enough to secure a seat in their preferred specialty. Competition is heaviest for clinical specialties such as &lt;a href="/news#radiology-imaging-akt-ukmla"&gt;radiology&lt;/a&gt;, &lt;a href="/news#dermatology-ukmla-revision"&gt;dermatology&lt;/a&gt;, and general &lt;a href="/news#surgical-presentations-ukmla-revision"&gt;surgery&lt;/a&gt; at reputed institutes, and comparatively lighter for less sought-after specialties, para-clinical subjects, or seats in private colleges with higher fees. We deliberately avoid quoting specific seat numbers or cutoff percentiles here, since these shift from year to year and vary by category and state quota — candidates should always check current NBEMS and counselling body data directly rather than relying on previous years' figures.&lt;/p&gt;
+&lt;p&gt;The UKMLA works on a fundamentally different logic. There is no fixed number of "passes" issued per sitting, and no ranking of candidates against one another. If you demonstrate, through the AKT and CPSA, that you meet the GMC's defined standard for safe practice, you pass — full stop. This does not mean the UKMLA is undemanding; the standard itself is rigorous and requires genuine clinical competence across a broad content map, and a meaningful proportion of candidates do not clear it on a given attempt. But the nature of the difficulty is different: it is about closing personal knowledge and skills gaps against a defined syllabus, not about out-competing thousands of equally prepared peers for a scarce resource. This is also why the UKMLA is sometimes seen as more "controllable" by candidates — your outcome depends almost entirely on your own preparation quality, not on how well everyone else in your cohort happens to perform that year.&lt;/p&gt;
+&lt;p&gt;It is worth being honest that this does not make the UK route "easier" in an absolute sense. Passing the AKT and CPSA to a genuinely safe clinical standard, in a system and clinical context that may be unfamiliar, is a serious undertaking, and IMGs must also independently meet &lt;a href="/eligibility"&gt;UKMLA eligibility criteria&lt;/a&gt; around primary qualifications, internship completion, and English language proficiency before they can even book the exam. What can honestly be said is that the two exams measure different things: NEET PG measures your knowledge relative to a very large, high-achieving national cohort competing for scarce seats, while the UKMLA measures your knowledge and skills against a fixed external bar. Candidates who dislike the psychological weight of a zero-sum ranking system often find the UKMLA's threshold model less stressful in this specific respect, even though the underlying study workload is comparable.&lt;/p&gt;
+&lt;p&gt;There is a second, less discussed dimension to competition worth naming explicitly: NEET PG competition is largely fixed in scale — a candidate cannot meaningfully change how many other people sit the exam or how many seats exist that year, only their own preparation. UKMLA "competition," such as it is, works differently, because the constraint is not a shared scarce resource but each individual candidate's own readiness against the standard. This means a well-prepared UKMLA candidate is not disadvantaged by a stronger-than-usual cohort sitting alongside them in the way a NEET PG candidate can be pushed down the rank order by an unusually strong applicant year. For candidates who have already sat one or more attempts at NEET PG and are reassessing their options, this structural difference is often the single biggest factor that tips the decision towards exploring the UK route seriously.&lt;/p&gt;
+&lt;h2&gt;Cost Comparison&lt;/h2&gt;
+&lt;p&gt;Cost is rarely the deciding factor on its own, but it is a real constraint for most Indian MBBS families, and the two pathways differ in both the size and the shape of the expense.&lt;/p&gt;
+&lt;p&gt;The NEET PG exam fee itself is comparatively modest — a few thousand rupees to register and sit the test. However, the realistic total cost of the NEET PG route for most candidates is considerably higher than the headline exam fee suggests, because of the coaching culture that has grown up around it. A large proportion of NEET PG aspirants enrol in structured coaching programmes — whether in-person institutes, online question banks and test series, or both — and many candidates sit the exam more than once to improve their rank, each repeat attempt adding another exam fee plus another year (or more) of coaching, study material, and living costs during a "drop year." When these realistic repeat-attempt and coaching costs are added up, the effective total investment in the NEET PG route can run into several lakhs of rupees for candidates who need multiple attempts to secure a seat in their preferred specialty.&lt;/p&gt;
+&lt;p&gt;The UKMLA/PLAB route has a different cost structure: fewer individually large fees, paid over a shorter window, with less dependence on multi-year repeat-attempt culture (though &lt;a href="/appeals-and-resits"&gt;resit&lt;/a&gt;s do happen and carry their own cost). &lt;a href="/news#ukmla-fees-for-img-2026"&gt;The full IMG fee breakdown&lt;/a&gt; sets out each component in detail; the table below summarises the core figures.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Cost Item&lt;/th&gt;&lt;th&gt;Amount (GBP)&lt;/th&gt;&lt;th&gt;Approximate INR&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;AKT (Applied Knowledge Test) exam fee&lt;/td&gt;&lt;td&gt;£283&lt;/td&gt;&lt;td&gt;≈ ₹30,000&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;CPSA (Clinical and Professional Skills Assessment) exam fee&lt;/td&gt;&lt;td&gt;£1,036&lt;/td&gt;&lt;td&gt;≈ ₹1,10,000&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;GMC registration fee&lt;/td&gt;&lt;td&gt;£481&lt;/td&gt;&lt;td&gt;≈ ₹51,000&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Total (approximate)&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;≈ £1,800&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;strong&gt;≈ ₹1,90,000–₹2,00,000&lt;/strong&gt;&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;These INR conversions are approximate and will move with the exchange rate, so candidates should always check the current rate when budgeting. It is also worth noting that this UKMLA/PLAB total does not include travel to the UK for the CPSA (which, for PLAB candidates, is held at the GMC's Clinical Assessment Centre in Manchester), accommodation during the trip, English language test fees (IELTS or OET), or preparation resources such as question banks and courses — all of which add a further, variable cost on top of the core &lt;a href="/fees"&gt;exam fees&lt;/a&gt;. Even accounting for these additions, most candidates find the total UK route cost more predictable and front-loaded into a single, shorter window, compared with the open-ended, multi-year cost profile that a repeat-attempt NEET PG journey can involve. Candidates weighing this trade-off often also compare it against a third option; &lt;a href="/news#ukmla-vs-usmle-comparison"&gt;how the UKMLA route compares to the US's USMLE&lt;/a&gt; is a useful reference point if the US is also on your shortlist, since USMLE Steps carry their own separate fee structure again.&lt;/p&gt;
+&lt;h2&gt;Career Outcomes: MD/MS in India vs NHS Practice in the UK&lt;/h2&gt;
+&lt;p&gt;Passing either exam is a milestone, not a destination — what happens afterwards is what actually shapes your career, so it deserves equal weight in this comparison.&lt;/p&gt;
+&lt;p&gt;Success in NEET PG leads to a seat in an MD, MS, or postgraduate diploma programme in India, typically a three-year residency-style training programme in your allocated specialty. This is the recognised route to becoming a specialist within the Indian healthcare system, whether in government hospitals, academic medical colleges, or the private sector. Career progression after MD/MS in India is well understood domestically: many graduates move into hospital consultant roles, private practice, or academic medicine, and the postgraduate degree is a prerequisite for most senior clinical and teaching positions in the country. Earning potential varies enormously by specialty, city, and whether a doctor works in government service, a corporate hospital chain, or independent private practice, and lifestyle factors — working hours, on-call burden, and geographic flexibility — likewise vary by specialty and sector rather than being fixed by the qualification itself.&lt;/p&gt;
+&lt;p&gt;Passing the UKMLA (via PLAB, for most Indian IMGs) makes you eligible for GMC registration and, from there, eligible to apply for clinical posts within the NHS. Most IMGs enter through IMG-specific placement routes into NHS trust posts, often starting at Foundation Year or early specialty training grade equivalent roles, before applying into formal specialty training programmes through the standard NHS recruitment rounds — a process that runs in parallel to, and is separate from, the UK medical graduate route described in &lt;a href="/news#how-to-become-a-doctor-in-uk-from-india"&gt;the complete step-by-step route from India&lt;/a&gt;. From there, career progression follows the NHS specialty training structure: core training, followed by higher specialty training, leading to a Certificate of Completion of Training (CCT) and eligibility for consultant or GP posts. This structure is nationally standardised in a way that Indian postgraduate training, spread across many universities and boards, is not — which some candidates find reassuring and others find rigid compared with the relative flexibility of private practice routes in India.&lt;/p&gt;
+&lt;p&gt;On earning potential and lifestyle, the honest, factual position is that both systems offer a credible, respected medical career, and direct comparisons are complicated by currency differences, cost of living, tax regimes, and the very different structures of private versus public practice in each country. NHS pay is nationally banded and relatively transparent at each training grade, with additional income possible through locum work; Indian earning potential is more sector-dependent, with private practice and corporate hospital roles often paying considerably more than government service, particularly for established specialists. Rather than treating either system as objectively "better paid," candidates are better served by researching current NHS pay scales and current Indian specialty-specific earning data directly, since both change over time and vary significantly by specialty, location, and sector.&lt;/p&gt;
+&lt;p&gt;Timeline to becoming a fully independent specialist is another factor worth weighing honestly, since it differs meaningfully between the two systems. In India, the path from MBBS to becoming a recognised specialist typically runs through a three-year MD/MS programme, sometimes followed by a further super-specialisation (DM/MCh) for those pursuing narrower fields — a well-defined but often lengthy sequence, made longer for candidates who need one or more additional years to clear NEET PG at a competitive rank first. In the UK, after GMC registration an IMG typically spends a period gaining NHS clinical experience before entering formal specialty training, with core and higher specialty training together generally taking a broadly comparable number of years to reach CCT, though exact duration depends heavily on specialty choice, training pathway, and how competitive entry into that specialty's training numbers is in a given recruitment round. Neither system is reliably "faster" in every specialty, and candidates should treat any claim to the contrary with caution unless it is specific to the exact specialty they are considering.&lt;/p&gt;
+&lt;p&gt;Regulatory and professional recognition is a further consideration many candidates underweight early on. GMC registration is a globally recognised medical regulatory credential, which can matter to doctors who anticipate wanting to work in more than one country during their career, or who value the portability that comes with a UK licensing history. An MD/MS from a recognised Indian university carries strong domestic recognition and is generally required for senior clinical, teaching, and many private-sector leadership roles within India, but the process of having it separately recognised for practice in other countries varies by destination and is not automatic. Doctors should research the specific recognition pathway for any country they might want to work in eventually, rather than assuming either qualification transfers seamlessly elsewhere.&lt;/p&gt;
+&lt;h2&gt;Can You Prepare for Both at the Same Time?&lt;/h2&gt;
+&lt;p&gt;A significant number of candidates, understandably reluctant to close off either option early, ask whether they can prepare for NEET PG and the UKMLA/PLAB route simultaneously. The realistic answer is: partially, and with clear trade-offs.&lt;/p&gt;
+&lt;p&gt;The good news is that there is genuine subject overlap between the two exams. Both draw on the same core MBBS clinical curriculum — medicine, surgery, &lt;a href="/news#obstetrics-gynaecology-ukmla-revision"&gt;obstetrics and gynaecology&lt;/a&gt;, &lt;a href="/news#paediatrics-ukmla-revision"&gt;paediatrics&lt;/a&gt;, and the major allied specialties — so time spent building a strong foundation in core clinical knowledge is not wasted, whichever exam you ultimately prioritise. A candidate with solid general clinical knowledge is starting from a reasonable position for either exam, and this shared foundation is why dual preparation is at least plausible as a strategy, unlike, say, trying to prepare for two completely unrelated professional exams at once.&lt;/p&gt;
+&lt;p&gt;The complication is that the exam styles diverge significantly once you move past that shared foundation, and this divergence grows the closer you get to your exam date. NEET PG rewards very high-speed, high-volume MCQ practice across an extremely broad syllabus, with particular attention to previous years' question patterns, high-yield topic prioritisation, and exam-taking speed under a strict single-sitting time limit — skills honed through dedicated NEET PG question banks and test series. The UKMLA's AKT similarly uses single-best-answer questions but is explicitly built around applied clinical reasoning mapped to the &lt;a href="/syllabus"&gt;MLA content map&lt;/a&gt; rather than the Indian PG curriculum's emphasis, and the CPSA adds an entirely separate skill set — structured clinical communication, examination technique, and &lt;a href="/news#clinical-examination-cpsa-guide"&gt;OSCE station&lt;/a&gt; performance — that NEET PG does not test at all and that requires dedicated, UK-context-specific practice.
+&lt;a href="/preparation"&gt;A complete UKMLA preparation guide&lt;/a&gt; sets out what that AKT- and CPSA-specific preparation actually looks like in practice, which is worth reviewing before assuming your NEET PG study plan will transfer directly.&lt;/p&gt;
+&lt;p&gt;In practice, most candidates who genuinely want to keep both doors open follow one of two realistic strategies. The first is sequential: build core clinical knowledge broadly during MBBS final year and internship, then make a decision point after internship about which exam-specific preparation to commit to fully, rather than trying to peak for both simultaneously. The second is a deliberate hedge, where a candidate prepares primarily for one exam but sits the other opportunistically with lighter, secondary preparation — for example, prioritising NEET PG while keeping AKT-relevant reading going in parallel, then committing fully to CPSA-specific OSCE practice only once a UK decision is firmer. What is rarely realistic is preparing for both at full intensity simultaneously in the final run-up to either exam — the volume of exam-specific practice each one demands in its last few months tends to require focused, undivided attention.&lt;/p&gt;
+&lt;h2&gt;Which Path Suits Which Kind of Candidate?&lt;/h2&gt;
+&lt;p&gt;Rather than framing this as a stereotype about which "type" of student goes where, it is more useful to look at what priorities tend to correlate with a stronger fit for each route, based on how the two systems are actually structured.&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Candidates who prioritise staying close to family and an established support network in India&lt;/strong&gt; often find the NEET PG to MD/MS route more compatible with their life plans, since it keeps training and early career entirely within India.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Candidates who want a predictable, standardised training structure with clearly defined stages&lt;/strong&gt; — core training, specialty training, CCT — may find the NHS's nationally structured pathway appealing, since it is more uniform across the country than India's more institution-by-institution postgraduate landscape.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Candidates who strongly prefer a pass/fail competency system over a ranked competition&lt;/strong&gt;, and who find the psychological pressure of relative ranking against a huge national cohort genuinely difficult to sustain over multiple attempts, often gravitate towards the UKMLA route precisely because of its threshold-based structure.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Candidates set on a specific, highly competitive Indian specialty&lt;/strong&gt; — where they are confident in their ability to rank competitively and have the resources for a possible drop year — may reasonably choose to commit fully to NEET PG rather than split focus.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Candidates prioritising earlier financial independence and a defined, shorter run-up to starting paid clinical work&lt;/strong&gt; sometimes favour the UK route, given its comparatively front-loaded and time-bound cost and preparation structure versus an open-ended multi-attempt NEET PG journey.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Candidates who value flexibility to eventually work in multiple countries&lt;/strong&gt; may lean towards the UKMLA/GMC route, since GMC registration is a well-recognised credential internationally, though this should not be the sole deciding factor for anyone not otherwise drawn to UK practice.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;None of these are hard rules, and many successful doctors have chosen against the "typical" fit for their stated priorities and done well regardless. The purpose of this list is to help you interrogate your own priorities honestly, not to sort candidates into fixed boxes.&lt;/p&gt;
+&lt;h2&gt;Frequently Asked Questions&lt;/h2&gt;
+&lt;h3&gt;Is UKMLA easier than NEET PG?&lt;/h3&gt;
+&lt;p&gt;Not in any simple sense — they measure different things. The UKMLA is a pass/fail competency threshold exam, so your outcome depends only on whether you meet the defined standard, not on how other candidates perform. NEET PG is a ranking exam, so even strong performance may not translate into your preferred outcome if enough other candidates rank higher. Many candidates find the UKMLA's threshold model less psychologically punishing, but the actual clinical knowledge and skills bar it sets is genuinely rigorous.&lt;/p&gt;
+&lt;h3&gt;Can I do NEET PG and UKMLA together?&lt;/h3&gt;
+&lt;p&gt;Partially. Both exams share a core MBBS clinical knowledge foundation, so general study in your final year and internship benefits both. However, exam-specific preparation — high-speed MCQ practice for NEET PG versus applied clinical reasoning and OSCE skills for the UKMLA's AKT and CPSA — diverges significantly closer to each exam date, so most candidates end up prioritising one in the final preparation phase rather than peaking for both at once.&lt;/p&gt;
+&lt;h3&gt;Which is cheaper, NEET PG or UKMLA/PLAB?&lt;/h3&gt;
+&lt;p&gt;The NEET PG exam fee itself is lower than the UKMLA/PLAB total of roughly &lt;strong&gt;£1,800 (≈ ₹1,90,000–₹2,00,000)&lt;/strong&gt;. However, when realistic coaching costs and the cost of repeat attempts common among NEET PG aspirants are factored in, the effective total cost of the NEET PG route can exceed the UK route for candidates who need multiple attempts to secure a seat.&lt;/p&gt;
+&lt;h3&gt;Do I need to pass NEET PG to sit the UKMLA?&lt;/h3&gt;
+&lt;p&gt;No. The two exams are entirely independent, run by different bodies for different jurisdictions. NEET PG is administered by the National Board of Examinations in Medical Sciences for Indian postgraduate admissions; the UKMLA is administered by the GMC for UK medical registration. Passing or failing one has no bearing on your eligibility for the other, though you must separately meet &lt;a href="/eligibility"&gt;UKMLA eligibility criteria&lt;/a&gt; such as primary qualification recognition, internship completion, and English language requirements before booking the UK exam.&lt;/p&gt;
+&lt;h3&gt;Is UKMLA recognised as equivalent to an MD in India?&lt;/h3&gt;
+&lt;p&gt;No. The UKMLA is a licensing assessment, not a postgraduate degree — passing it confirms you meet the standard for GMC registration and safe practice in the UK, similar in spirit to a licensing threshold rather than a specialty qualification. An MD/MS from NEET PG is a postgraduate degree conferring specialist status within the Indian system. A doctor who passes the UKMLA and later wants to return to India to practise would need to separately satisfy Indian regulatory requirements for that qualification's recognition, which candidates should confirm directly with the relevant Indian medical council rather than assuming automatic equivalence.&lt;/p&gt;
+&lt;h3&gt;What happens if I fail NEET PG or the UKMLA?&lt;/h3&gt;
+&lt;p&gt;Under NEET PG, a low rank does not necessarily mean failure in an absolute sense — it usually means missing out on your preferred specialty or college in that year's counselling, with many candidates re-attempting the following year to improve their rank. Under the UKMLA, failing the AKT or CPSA means not meeting the standard on that attempt; candidates can typically resit, though resit policies, fees, and any attempt limits should be confirmed directly against current GMC guidance, since these details can change.&lt;/p&gt;
+&lt;h3&gt;Is PLAB the same thing as the UKMLA for Indian doctors?&lt;/h3&gt;
+&lt;p&gt;Broadly, yes, and this is a common point of confusion worth clarifying separately from the NEET PG comparison. Since the 2024 transition, PLAB 1 is aligned with the UKMLA's AKT and PLAB 2 is aligned with the UKMLA's CPSA, so IMGs — including Indian MBBS graduates — who pass PLAB 1 and PLAB 2 have, in effect, met the UKMLA standard. For the mechanics of exactly how this alignment works, see &lt;a href="</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG India</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>/images/ukmla-vs-neet-pg-featured.webp</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG - Indian medical graduate comparing UK and India postgraduate exam pathways</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>5026</v>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>How to choose a UKMLA question bank, which free UKMLA mock tests are worth using, and how to structure practice questions into an effective AKT revision routine.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Preparation, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/education/medical-licensing-assessment/mla-content-map</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank: Best Practice Resources 2026</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA question bank guide: how to choose one, free UKMLA mock tests worth trying, and how to build an effective AKT practice routine for 2026.</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA question bank</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;A good &lt;strong&gt;UKMLA question bank&lt;/strong&gt; is the single most useful resource a candidate can build a revision plan around, yet most candidates choose one based on advertising rather than on any structured evaluation of what actually makes a question bank effective. With so many free and paid options now competing for attention, the practical question is not "which brand is best" but "which features actually predict better performance on exam day" — coverage of the full syllabus, the quality of explanations, realistic difficulty calibration, and genuine timed mock conditions. This guide sets out a framework for evaluating any UKMLA question bank you are considering, free or paid, and shows how to build those questions into a structured mock-exam routine.&lt;/p&gt;
+&lt;p&gt;Rather than recommending specific commercial products, this article focuses on the criteria that separate a genuinely useful UKMLA question bank from one that merely looks impressive. It covers why question practice is the highest-yield form of AKT preparation, what to check before committing time or money to any resource, the honest trade-offs between free and paid options, how to structure a mock-test routine across a revision timeline, and the volume of practice most candidates need at each stage. It closes with a detailed FAQ addressing the most common searches UKMLA candidates run when looking for practice material.&lt;/p&gt;
+&lt;p&gt;This is written for both UK final-year medical students sitting the UKMLA as part of their degree and &lt;a href="/eligibility"&gt;international medical graduates&lt;/a&gt; (IMGs) preparing for the AKT as a standalone qualifying exam. Both groups rely on the same underlying content map and the same exam format, so the evaluation framework below applies equally regardless of where you are sitting the exam or how you arrived at this stage of preparation.&lt;/p&gt;
+&lt;p&gt;It is worth being upfront about what this guide will not do. It will not tell you that one named product is superior to another, and it will not produce a ranked league table of commercial platforms. Search results for terms such as "best question bank for UKMLA" or "UKMLA AKT question bank free" are dominated by marketing pages and affiliate comparisons that reward whichever platform pays the highest commission, not whichever platform actually helps a candidate pass. What follows instead is a set of criteria you can apply yourself to any resource — including ones that do not exist yet — so that the evaluation remains useful for as long as the &lt;a href="/news#ukmla-akt-format-preparation"&gt;AKT format&lt;/a&gt; itself remains stable, rather than becoming outdated the moment a particular platform changes its pricing or shuts down.&lt;/p&gt;
+&lt;h2&gt;Why Question Banks Matter for the UKMLA AKT&lt;/h2&gt;
+&lt;p&gt;The &lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test&lt;/a&gt; is built entirely around the Single Best Answer (SBA) format: candidates are given a clinical vignette followed by a question stem and a list of options, of which only one is the best answer given the information provided. This format does not simply test whether you know a fact — it tests whether you can apply that fact correctly under time pressure, discriminate between several plausible-sounding options, and reach a decision within roughly 72 seconds per question across a 180-question, three-hour paper. Because the format itself is the challenge, not just the underlying medical knowledge, timed question practice using a well-built &lt;strong&gt;UKMLA question bank&lt;/strong&gt; is consistently the highest-yield preparation method available, ahead of passive reading, lecture-watching, or textbook review on its own.&lt;/p&gt;
+&lt;p&gt;Reading a chapter on acute coronary syndromes teaches you facts. Answering thirty SBA questions on acute coronary syndromes teaches you how those facts get disguised inside a clinical stem, how distractors are constructed to catch common misconceptions, and how to extract the single decisive piece of information from a paragraph of plausible-looking clinical noise. This is a distinct skill from knowledge recall, and it can only be trained through repeated exposure to real exam-style questions. A candidate who has memorised the entire &lt;a href="/syllabus"&gt;MLA syllabus&lt;/a&gt; but has never practised applying it inside the SBA format will typically underperform a candidate with slightly less raw knowledge but far more question experience.&lt;/p&gt;
+&lt;p&gt;UKMLA questions also train two skills that are easy to underestimate: reading the stem efficiently and managing time across a long paper. Both are addressed in more detail elsewhere on this site, including a dedicated guide to &lt;a href="/news#how-to-read-akt-stem"&gt;reading AKT question stems correctly&lt;/a&gt; and a walkthrough of &lt;a href="/news#time-management-akt-ukmla"&gt;managing your time during timed practice&lt;/a&gt;. A UKMLA question bank is the vehicle through which both skills are built, which is why the choice of question bank — and how it is used — deserves far more attention than most candidates give it.&lt;/p&gt;
+&lt;p&gt;There is also a psychological dimension to question practice that candidates frequently underestimate. Sitting hundreds of SBA questions over several months exposes you to the recurring "shapes" that AKT questions take — the vignette that mentions a red herring early on, the option that is technically correct but not the best answer given the clinical priority, the question that hinges on a single lab value buried in the middle of a paragraph. Recognising these patterns is a form of exam literacy that develops only through volume and variety of practice, and it is largely independent of raw clinical knowledge. Two candidates with identical textbook knowledge can produce very different AKT results depending on how much of this exam literacy they have built through a genuine UKMLA question bank, which is part of why question practice consistently outperforms passive revision methods in candidate feedback and why it is treated as the backbone of most structured preparation timelines rather than an optional supplement to them.&lt;/p&gt;
+&lt;h2&gt;What Makes a Good UKMLA Question Bank? Evaluation Criteria&lt;/h2&gt;
+&lt;p&gt;Not all question banks are built to the same standard, and the difference between a mediocre resource and an excellent one is rarely obvious from a homepage or a marketing email. Before committing significant revision time to any UKMLA question bank, free or paid, it is worth running it through a structured checklist covering seven criteria: content coverage, explanation quality, difficulty calibration, filtering capability, mock mode, progress tracking, and cost. A resource that performs well across all seven is worth prioritising; one that is weak on several is unlikely to serve you well as your primary revision tool, however large its advertised question count.&lt;/p&gt;
+&lt;h3&gt;Coverage of the Full MLA Content Map&lt;/h3&gt;
+&lt;p&gt;The most fundamental test of any UKMLA question bank is whether its questions actually map onto &lt;a href="https://www.gmc-uk.org/education/medical-licensing-assessment/mla-content-map"&gt;the official MLA content map published by the GMC&lt;/a&gt;, which defines the presentations, conditions, and clinical skills that the AKT is permitted to draw questions from. A question bank that is heavily weighted toward a handful of popular topics — &lt;a href="/news#cardiology-ukmla-akt-revision"&gt;cardiology&lt;/a&gt; and &lt;a href="/news#respiratory-medicine-ukmla-revision"&gt;respiratory medicine&lt;/a&gt;, for instance — while offering thin coverage of areas such as &lt;a href="/news#ophthalmology-ent-ukmla-revision"&gt;ophthalmology&lt;/a&gt;, &lt;a href="/news#dermatology-ukmla-revision"&gt;dermatology&lt;/a&gt;, or ethics and law will leave systematic gaps in your preparation regardless of how many total questions it contains. Before relying on any bank, check whether it organises content by the same domains used in the content map and whether question distribution across those domains is roughly proportionate to how the real AKT is structured, rather than skewed toward whichever topics were easiest for question writers to produce.&lt;/p&gt;
+&lt;h3&gt;Quality of Explanations&lt;/h3&gt;
+&lt;p&gt;A question with no explanation, or an explanation that simply restates the correct answer without reasoning, teaches almost nothing beyond whether you happened to guess correctly. The explanations attached to each question are arguably more valuable than the question itself, because they are where the actual learning happens. A high-quality explanation should state why the correct answer is right, explain why each plausible distractor is wrong, and ideally reference the underlying guideline or physiological principle involved. If you find yourself finishing a question set and still uncertain why an answer was correct despite reading the explanation, that is a strong signal the resource's explanation quality is inadequate for serious revision use.&lt;/p&gt;
+&lt;h3&gt;Difficulty Calibration Against the Real AKT Standard&lt;/h3&gt;
+&lt;p&gt;Some question banks are written to be deliberately harder than the real exam, in order to appear more rigorous; others drift toward easier, more clear-cut questions that are simpler to write and mark. Neither extreme serves you well. Questions that are artificially difficult, relying on obscure trivia rather than applied clinical reasoning, can undermine your confidence and waste revision time on content that will never appear in the real assessment. Questions that are too straightforward, offering an obviously correct answer with implausible distractors, fail to train the discrimination skill that the SBA format actually demands. The best available indicator of realistic calibration is whether a bank's practice questions resemble the style, length, and reasoning demand of the official sample materials released by the Medical Schools Council, which remain the closest public benchmark for what real AKT questions look like.&lt;/p&gt;
+&lt;h3&gt;Ability to Filter by System or Topic&lt;/h3&gt;
+&lt;p&gt;Early in a revision timeline, most candidates want to work through a question bank systematically, topic by topic, alongside their content review. Later in the timeline, the priority shifts to targeted practice on weak areas identified from previous mock performance. Both modes of use require a question bank that allows filtering by system, topic, or content-map domain, rather than only offering questions in one fixed, unfilterable sequence. A bank that cannot be filtered forces you to either work through irrelevant material to reach the topics you actually need, or abandon systematic practice altogether — both of which reduce the efficiency of your revision time.&lt;/p&gt;
+&lt;h3&gt;Timed Mock Mode&lt;/h3&gt;
+&lt;p&gt;Because the AKT is fundamentally a timed exam, any UKMLA question bank worth using seriously should offer a genuine timed mock mode: a mode that withholds feedback until the session ends, allows you to set a realistic question count and time limit, and ideally lets you flag questions and return to them, mirroring the functionality of the real assessment delivered through &lt;a href="https://www.pearsonvue.com/"&gt;Pearson VUE, which administers the AKT at test centres worldwide&lt;/a&gt;. A bank that only offers an untimed, feedback-after-every-question "learning mode" is useful for initial content coverage but cannot substitute for the pacing and endurance training that a full mock provides.&lt;/p&gt;
+&lt;h3&gt;Progress Tracking&lt;/h3&gt;
+&lt;p&gt;A UKMLA question bank without meaningful progress tracking forces you to guess where your weaknesses lie rather than measuring them directly. Useful tracking includes a breakdown of performance by topic or domain, a record of which questions you have already attempted, and ideally a distinction between questions answered correctly with confidence and those answered correctly by guesswork. Without this data, it is very difficult to direct revision time efficiently in the final weeks before the exam, when targeted practice on genuine weak areas produces far more improvement than continuing to practise topics you have already mastered.&lt;/p&gt;
+&lt;h3&gt;Cost&lt;/h3&gt;
+&lt;p&gt;Cost matters, particularly for IMGs who are already budgeting for registration, travel, and multiple &lt;a href="/fees"&gt;exam fees&lt;/a&gt; on top of revision resources. A question bank's price should be evaluated against the six criteria above, not in isolation — a free resource that covers the syllabus comprehensively, calibrates difficulty well, and offers genuine timed mocks may be entirely sufficient for many candidates, while an expensive resource that is weak on explanation quality or content coverage is a poor use of a limited budget. The next section addresses this trade-off directly.&lt;/p&gt;
+&lt;h3&gt;Question Format and Vignette Realism&lt;/h3&gt;
+&lt;p&gt;A subtler but still important criterion is whether questions are written as genuine clinical vignettes — a patient presenting with a history, examination findings, and relevant investigations — rather than as bare factual-recall prompts dressed up with a token clinical scenario. The AKT tests applied clinical reasoning, so a bank whose questions frequently reduce to "which drug treats condition X" without requiring the candidate to first work out what condition X actually is from the presenting information will not adequately train the skill the real exam demands. When trialling a new question bank, read through ten or fifteen questions specifically checking whether the vignette information is necessary to reach the answer, or merely decorative.&lt;/p&gt;
+&lt;h3&gt;Currency and Guideline Accuracy&lt;/h3&gt;
+&lt;p&gt;UK clinical guidelines change regularly, and a question bank that has not been reviewed or updated in several years can quietly teach outdated management, particularly in areas such as antimicrobial choice, cardiovascular risk thresholds, or first-line drug therapy where national guidance is periodically revised. Before relying heavily on any resource, check whether it states when its content was last reviewed and whether it references current guideline bodies. A bank that is otherwise strong on the other criteria but has not been updated recently should be treated with some caution, particularly on guideline-dependent topics.&lt;/p&gt;
+&lt;h2&gt;Free vs Paid UKMLA Question Banks: What's the Real Difference?&lt;/h2&gt;
+&lt;p&gt;The honest answer is that free and paid UKMLA question banks differ in degree rather than in kind, and the right choice depends heavily on where you are in your revision timeline and how much time you have available. Free resources — including sample questions released by official bodies, university-provided banks, and smaller independent platforms — typically offer smaller total question pools, narrower coverage of less common content-map topics, and simpler explanations that state the correct answer without extensive reasoning. A &lt;strong&gt;free UKMLA &lt;a href="/news#mock-exams-ukmla-preparation"&gt;mock test&lt;/a&gt;&lt;/strong&gt; built from these resources is genuinely useful, particularly early in revision or as a diagnostic tool, but it rarely offers the full 180-question, exam-length experience with proportionate domain weighting that a comprehensive paid resource can provide.&lt;/p&gt;
+&lt;p&gt;Paid question banks generally differentiate themselves in three areas: total question volume (often several thousand questions rather than several hundred), the availability of multiple full-length timed mock papers built to mirror real AKT proportions across all twelve domains, and more detailed analytics that track performance trends across weeks of use rather than a single session. Some paid resources also update their question pools periodically to reflect changes in national guidelines, which matters for a syllabus as guideline-dependent as UKMLA content.&lt;/p&gt;
+&lt;p&gt;Realistic advice on when free is enough: if you are more than twelve weeks from your exam date and still working through initial content review, a free UKMLA question bank or your medical school's own resources are usually sufficient, because the priority at this stage is building foundational familiarity with the SBA format across topics rather than exhaustive question volume. If you are within the final six to eight weeks, sitting the exam as a standalone qualifying assessment as an IMG, or have already exhausted the available free question pool without reaching a consistent, confident performance level, investing in a paid resource with a larger bank and full-length mock papers becomes considerably more worthwhile. The decision should be driven by where the gaps in the free evaluation criteria above actually sit for you, not by assuming that paying automatically solves a coverage or calibration problem that a specific resource has.&lt;/p&gt;
+&lt;p&gt;It is also worth noting that cost is not the only budget IMG candidates need to plan for. Question bank spending should be considered alongside registration, travel, and sitting fees as part of an overall plan for &lt;a href="/news#ukmla-fees-for-img-2026"&gt;budgeting for the full IMG exam pathway&lt;/a&gt;, so that resource spending on practice questions does not crowd out the funds needed for the exam itself.&lt;/p&gt;
+&lt;h2&gt;How to Get the Most Out of a Free UKMLA Mock Test&lt;/h2&gt;
+&lt;p&gt;A free UKMLA mock test delivers most of its value only if it is taken under conditions that genuinely replicate the real exam, and reviewed with the same rigour you would apply to paid material. The single biggest mistake candidates make with free mock tests is treating them casually — pausing partway through, checking a phone between questions, or skipping the review step — which wastes the one advantage a mock test actually offers: an honest, timed measurement of current performance.&lt;/p&gt;
+&lt;p&gt;Begin by simulating real exam timing as closely as the mock allows. Set a fixed time limit based on the standard AKT pacing of roughly 72 seconds per question, remove all notes and distractions from your workspace, and commit to completing the full set without pausing. If the free resource offers fewer than 180 questions, scale the time allowance proportionately rather than allowing yourself extra time per question, since the pacing pressure itself is part of what the mock is meant to train.&lt;/p&gt;
+&lt;p&gt;After finishing, review every question — not only the ones you got wrong. A question answered correctly through an educated guess or partial recall represents exactly the same underlying gap as a wrong answer; the only difference is that it did not cost you a mark this time. For each question, however you answered it, read the explanation fully and check it against your own reasoning, not just against the final answer. This is where &lt;a href="/news#ukmla-revision-notes-strategy"&gt;combining question practice with structured revision notes&lt;/a&gt; pays off, because a wrong or guessed answer becomes an entry point for targeted note review rather than a dead end.&lt;/p&gt;
+&lt;p&gt;Finally, track your weak topics against &lt;a href="/syllabus"&gt;the full MLA syllabus&lt;/a&gt; rather than relying on memory of which questions felt difficult. Keep a simple running log of which domains produced the most errors across each mock you sit, whether free or paid. Over several mocks, this log becomes far more informative than any single score, because it reveals whether specific domains are persistently weak or whether errors are scattered randomly across topics — two patterns that call for very different revision responses.&lt;/p&gt;
+&lt;h2&gt;How Many Practice Questions Do You Actually Need?&lt;/h2&gt;
+&lt;p&gt;There is no &lt;a href="/official-resources"&gt;official GMC&lt;/a&gt; figure for how many practice questions a candidate should complete before sitting the AKT, and any number quoted online should be treated as general guidance rather than a fixed target. That said, most structured revision timelines converge on a similar shape: a lower daily volume early on while content review is still underway, rising to a higher volume in the middle of the revision period once foundational knowledge is in place, and a shift toward full-length timed mocks rather than raw question volume in the final month. The table below sets out illustrative, reasonable ranges for each stage, based on the typical structure of a twelve-week revision plan.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Revision Stage&lt;/th&gt;&lt;th&gt;Typical Timeframe&lt;/th&gt;&lt;th&gt;Suggested Daily/Weekly Question Volume&lt;/th&gt;&lt;th&gt;Mock Frequency&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;Early revision&lt;/td&gt;&lt;td&gt;Weeks 1–4&lt;/td&gt;&lt;td&gt;20–30 questions per day, filtered by topic alongside content review&lt;/td&gt;&lt;td&gt;None yet, or one short diagnostic set&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Mid-revision&lt;/td&gt;&lt;td&gt;Weeks 5–8&lt;/td&gt;&lt;td&gt;40–60 questions per day, mixing topic-filtered sets with mixed-domain blocks&lt;/td&gt;&lt;td&gt;One full-length timed mock around week 8&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Final month&lt;/td&gt;&lt;td&gt;Weeks 9–11&lt;/td&gt;&lt;td&gt;30–50 questions per day, increasingly weighted toward weak topics identified from mocks&lt;/td&gt;&lt;td&gt;One further full mock around week 10–11, plus shorter targeted mocks&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Final week&lt;/td&gt;&lt;td&gt;Week 12&lt;/td&gt;&lt;td&gt;Lighter volume, focused review of previously flagged and incorrect questions rather than new material&lt;/td&gt;&lt;td&gt;Optional short mock early in the week only; no new full mocks in final 48 hours&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;Total cumulative volume across a full revision timeline commonly falls somewhere in the range of &lt;strong&gt;2,500 to 4,000 questions&lt;/strong&gt; for candidates using a single well-structured UKMLA question bank consistently, though candidates with strong existing clinical knowledge from recent placements may need fewer, and &lt;a href="/news#ukmla-preparation-for-imgs"&gt;IMGs preparing&lt;/a&gt; the AKT as a standalone assessment without concurrent clinical exposure often benefit from higher volumes at the upper end of that range. What matters more than hitting a specific number is consistency of practice combined with rigorous review, since a candidate who completes 1,500 questions with careful review of every explanation will typically outperform one who rushes through 5,000 questions without ever properly reviewing their errors.&lt;/p&gt;
+&lt;h2&gt;Building a UKMLA Mock Exam Routine&lt;/h2&gt;
+&lt;p&gt;A UKMLA question bank delivers its full value only when built into a deliberate mock-exam routine rather than used in an unstructured, ad hoc way. This means spacing mocks appropriately across your revision timeline, balancing full-length timed papers against shorter topic-focused blocks, and building in a consistent review process after every session.&lt;/p&gt;
+&lt;h3&gt;Spacing Mocks Across Your Revision Timeline&lt;/h3&gt;
+&lt;p&gt;Mocks should not be clustered at the very end of a revision period, however tempting that feels once exam anxiety builds. A common and effective pattern places the first full-length mock around the midpoint of a twelve-week plan — roughly week 8 — once initial content review and topic-based question practice are largely complete. A second full mock follows two to three weeks later, once the weak areas identified in the first mock have had time to be addressed. This spacing allows genuine improvement to be measured between mocks, which is one of the strongest indicators that your revision strategy is working, rather than sitting every mock too close together and measuring only random day-to-day variation in performance.&lt;/p&gt;
+&lt;h3&gt;Full-Length Timed Mocks vs Topic Blocks&lt;/h3&gt;
+&lt;p&gt;Full-length, 180-question timed mocks and shorter topic-focused question blocks serve different purposes and should not be treated as interchangeable. Full mocks train pacing, endurance, and the ability to switch cognitive gears rapidly between unrelated domains — a cardiology question immediately followed by a &lt;a href="/news#psychiatry-communication-cpsa-stations"&gt;psychiatry&lt;/a&gt; question followed by a &lt;a href="/news#rheumatology-ukmla-revision"&gt;musculoskeletal&lt;/a&gt; question — which is a realistic feature of the actual AKT that topic blocks cannot replicate. Topic blocks, by contrast, are better suited to consolidating a specific weak domain identified from mock performance data, since they allow concentrated repetition on one area without the dilution effect of mixing in dozens of unrelated questions. A balanced routine uses topic blocks for the bulk of weekly practice and reserves full-length mocks for periodic, deliberately spaced performance checkpoints.&lt;/p&gt;
+&lt;h3&gt;Reviewing Performance Data and Targeting Weak Areas&lt;/h3&gt;
+&lt;p&gt;Every mock, whether full-length or a shorter targeted block, should end with a structured review rather than simply noting the final score. Record your domain-level breakdown after each session and compare it against previous mocks to identify whether specific domains are persistently weak, improving, or static. Persistent weak domains — those still underperforming after two or more mocks despite targeted revision — deserve disproportionate attention in the following one to two weeks, since they represent genuine, stable knowledge gaps rather than one-off variation. This kind of data-driven targeting is only possible if your UKMLA question bank provides adequate progress tracking, which is why that criterion was included in the evaluation framework above.&lt;/p&gt;
+&lt;h2&gt;Common Mistakes When Using Question Banks&lt;/h2&gt;
+&lt;p&gt;Several recurring mistakes reduce the value candidates get from otherwise good question bank resources, regardless of how comprehensive or well-calibrated the bank itself is.&lt;/p&gt;
+&lt;p&gt;The most common is &lt;strong&gt;over-relying on recognising questions rather than understanding reasoning&lt;/strong&gt;. Candidates who repeat the same question bank multiple times can begin to recognise the correct answer from the shape or wording of the question rather than from applying clinical reasoning, which inflates apparent performance without building the transferable skill the real exam demands. If a repeated question is answered correctly, it is worth pausing to check whether you actually reasoned through it again or simply remembered the answer from last time.&lt;/p&gt;
+&lt;p&gt;A second common mistake is &lt;strong&gt;ignoring weak-topic data&lt;/strong&gt; once it has been generated. Many candidates dutifully complete mock after mock, generating detailed domain breakdowns, but never actually change their revision plan in response to what that data shows. Weak-topic data is only useful if it changes what you study next.&lt;/p&gt;
+&lt;p&gt;A third mistake is &lt;strong&gt;leaving all mocks to the final week&lt;/strong&gt;, which removes any opportunity to act on the results. A mock sat five days before the exam can reveal a serious gap in, for example, &lt;a href="/news#endocrinology-diabetes-ukmla-revision"&gt;endocrinology&lt;/a&gt;, but there is little time left to address it meaningfully. Mocks need to be spaced early enough in the timeline that their findings can actually be used.&lt;/p&gt;
+&lt;p&gt;A fourth mistake is &lt;strong&gt;not replicating real exam timing conditions&lt;/strong&gt; during practice, whether that means pausing mid-mock, checking answers between questions, or allowing extra time beyond the standard pacing. This undermines the two things a mock is specifically designed to train — pacing and endurance — and produces a false sense of security that does not transfer to the actual test-centre experience delivered through Pearson VUE.&lt;/p&gt;
+&lt;p&gt;A fifth mistake, less discussed than the others, is &lt;strong&gt;switching resources too frequently&lt;/strong&gt;. Candidates who feel anxious about their progress sometimes respond by abandoning one UKMLA question bank partway through and starting again on another, hoping a different resource will produce faster improvement. In practice, this usually resets progress tracking, discards accumulated performance data, and wastes the time already invested in working through the first bank's content systematically. Unless a resource has a clear, specific deficiency identified against the evaluation criteria above — persistently poor explanations or an obvious coverage gap, for instance — it is generally more productive to stay with one well-chosen bank for the bulk of a revision timeline and supplement it selectively rather than repeatedly switching platforms.&lt;/p&gt;
+&lt;p&gt;A sixth mistake is &lt;strong&gt;treating every question bank score as equally meaningful&lt;/strong&gt;. A single session of twenty questions on a topic you have just revised will naturally produce a higher score than a mixed, unseen 180-question mock sat cold. Comparing these two very different types of session as though they were interchangeable measures of readiness leads to false confidence. Scores from topic-filtered practice immediately after revision and scores from full, mixed-domain timed mocks should be tracked and interpreted separately.&lt;/p&gt;
+&lt;h2&gt;Frequently Asked Questions&lt;/h2&gt;
+&lt;h3&gt;Is there a free UKMLA mock test?&lt;/h3&gt;
+&lt;p&gt;Yes. Several free resources offer UKMLA-style practice questions and shorter mock sets, including official sample materials and university-provided banks, and these can be assembled into a self-timed mock by setting a fixed time limit based on standard AKT pacing. Free resources typically offer a smaller question pool and less comprehensive domain coverage than paid alternatives, so they are best used early in revision or as a diagnostic tool rather than as the sole basis for exam-readiness assessment in the final weeks.&lt;/p&gt;
+&lt;h3&gt;How many questions are in a good UKMLA question bank?&lt;/h3&gt;
+&lt;p&gt;There is no fixed official number, but question banks with only a few hundred questions typically cannot provide proportionate coverage across all twelve content-map domains. As a general guide, a UKMLA question bank intended to support a full revision timeline should offer enough volume and range to allow both systematic topic-by-topic practice and multiple full-length, 180-question mock papers without excessive question repetition.&lt;/p&gt;
+&lt;h3&gt;What is the best question bank for UKMLA preparation?&lt;/h3&gt;
+&lt;p&gt;Rather than a single "best" product, the better approach is to evaluate any candidate resource — free or paid — against the seven criteria set out above: content-map coverage, explanation quality, difficulty calibration, filtering capability, timed mock mode, progress tracking, and cost. A resource that performs strongly across all seven will serve most candidates well regardless of brand, and different candidates may reasonably reach different conclusions depending on their budget, timeline, and existing clinical knowledge.&lt;/p&gt;
+&lt;h3&gt;Do UK medical students need a separate question bank from their medical school's resources?&lt;/h3&gt;
+&lt;p&gt;Many &lt;a href="/news#uk-medical-schools-ukmla-implementation"&gt;UK medical school&lt;/a&gt;s provide their own bank of practice questions aligned to their curriculum, and for students whose school resources are comprehensive and well-calibrated to the AKT standard, this may be sufficient on its own. However, school-provided banks are sometimes narrower in scope than the full MLA content map or lighter on timed full-length mock functionality, so many students supplement with an additional UKMLA question bank, particularly in the final two to three months before the exam, to access larger question volumes and more robust mock-exam modes.&lt;/p&gt;
+&lt;h3&gt;How is a UKMLA question bank different for IMGs preparing from abroad?&lt;/h3&gt;
+&lt;p&gt;The underlying content and format are identical for UK final-year students and IMGs, since both groups sit the same AKT built from the same content map. The practical difference is that IMGs are usually preparing without the benefit of recent UK clinical placements or a medical school's bundled resources, which often means relying more heavily on a standalone question bank for both initial content coverage and mock practice. This applies to &lt;a href="/news#how-to-become-a-doctor-in-uk-from-india"&gt;IMGs preparing from India&lt;/a&gt;, &lt;a href="/news#ukmla-for-pakistani-doctors"&gt;Pakistani candidates preparing for the AKT&lt;/a&gt;, &lt;a href="/news#ukmla-for-nigerian-doctors"&gt;Nigerian candidates preparing for the AKT&lt;/a&gt;, and IMGs from any other country following the standalone route.&lt;/p&gt;
+&lt;h3&gt;Can question bank practice alone replace a structured revision plan?&lt;/h3&gt;
+&lt;p&gt;No. Question bank practice is most effective when it is combined with structured content review rather than used as a substitute for it, particularly for topics where a candidate has an underlying knowledge gap rather than simply a reasoning or exam-technique gap. The most effective approach pairs consistent question practice with &lt;a href="/news#ukmla-revision-notes-strategy"&gt;combining question practice with structured revision notes&lt;/a&gt;, using each wrong or guessed answer as a prompt to revisit and reinforce the underlying material rather than treating the question bank as a complete revision method by itself.&lt;/p&gt;
+&lt;h3&gt;How does UKMLA question bank practice compare with preparing for the USMLE or NEET PG?&lt;/h3&gt;
+&lt;p&gt;The underlying principle — that timed question practice is the highest-yield preparation method — holds across most major single-best-answer medical licensing assessments, but the specific conte</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA question bank mock test</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>/images/ukmla-question-bank-and-mock-tests-featured.webp</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank and Mock Tests</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA question bank and mock tests - medical student practising AKT questions on a laptop</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>5099</v>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>A complete 2026 breakdown of UKMLA exam fees for IMGs — every charge from EPIC verification to GMC registration, plus the total cost of the pathway by country.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Fees &amp; Funding</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Fees &amp; Funding, UKMLA, Medical Licensing</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gmc-uk.org/registration-and-licensing/managing-your-registration/fees-and-funding/fees-for-doctors</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for IMG: 2026 Full Cost Guide</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA exam fees for IMG in 2026: AKT, CPSA, GMC registration, EPIC verification and total pathway cost for international medical graduates.</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam fees for IMG</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;UKMLA exam fees for IMG&lt;/strong&gt; candidates rarely stop at the three headline charges most guides quote. The &lt;a href="/exam-pattern/akt"&gt;Applied Knowledge Test&lt;/a&gt;, the &lt;a href="/exam-pattern/cpsa"&gt;Clinical and Professional Skills Assessment&lt;/a&gt;, and initial GMC registration together come to roughly £1,800, but that figure is only the starting point of what an international medical graduate actually spends on the road to a UK licence. By the time you add primary source verification, an English language test, flights and accommodation for a CPSA sitting in Manchester, a preparation course or &lt;a href="/preparation"&gt;question bank&lt;/a&gt; subscription, and the first annual retention fee, the realistic total for most IMGs lands well above £3,000 — and for candidates travelling long-haul with no local support network, it can exceed £4,500.&lt;/p&gt;
+&lt;p&gt;This guide is built specifically to answer the question most fee pages skip: what does the whole pathway cost, end to end, once every unavoidable expense is included? We walk through the core GMC charges briefly (with a link to &lt;a href="/news#ukmla-fees-explained"&gt;the complete AKT, CPSA and registration fee breakdown&lt;/a&gt; for readers who only need the headline numbers), then go category by category through everything that happens before you even book the AKT, the real logistics cost of sitting the CPSA in Manchester, and what it costs to stay registered once you're through. A regional budget table gives illustrative totals for candidates travelling from South Asia, West Africa, the Middle East and Gulf, and Southeast Asia.&lt;/p&gt;
+&lt;p&gt;None of the figures below replace official guidance. Core GMC amounts are cited as such; everything else — flights, hotels, courses, question banks — is presented as an indicative planning range so you can build a realistic personal budget rather than being caught out by costs nobody mentioned until it was too late. You can always check &lt;a href="https://www.gmc-uk.org/registration-and-licensing/managing-your-registration/fees-and-funding/fees-for-doctors" target="_blank" rel="noopener"&gt;the GMC's official fees for doctors page&lt;/a&gt; for the current core charges before relying on any figure quoted here or elsewhere.&lt;/p&gt;
+&lt;p&gt;Why does this distinction matter so much? Because most IMGs plan their finances around the number they first encounter — usually the £283 AKT fee or the combined £1,800 core total — and only discover the rest of the spending piecemeal, at the exact moments they can least afford a surprise: an EPIC invoice a few weeks before a planned AKT booking, a language test result that has quietly expired, or a Manchester hotel search two weeks before a CPSA date when prices have already climbed. Building the full picture upfront, even as a rough range rather than an exact figure, converts several unpredictable shocks into one manageable, plannable total.&lt;/p&gt;
+&lt;h2&gt;UKMLA Exam Fees for IMG: The Core Charges&lt;/h2&gt;
+&lt;p&gt;Before adding up the wider pathway, it helps to restate the three charges every IMG pays directly to the GMC. The &lt;strong&gt;AKT costs £283 per attempt&lt;/strong&gt;, the &lt;strong&gt;CPSA costs £1,036 per attempt&lt;/strong&gt;, and &lt;strong&gt;initial GMC registration costs £481&lt;/strong&gt;, bringing the core total to approximately &lt;strong&gt;£1,800&lt;/strong&gt; for a candidate who passes both assessments first time. These are the same figures IMGs will have seen quoted elsewhere, and they are set out in full — including the tiered cancellation and refund policy, currency conversions, and historical fee changes — in &lt;a href="/news#ukmla-fees-explained"&gt;the complete AKT, CPSA and registration fee breakdown&lt;/a&gt;, so we won't repeat that detail here.&lt;/p&gt;
+&lt;p&gt;What matters for this guide is that these three charges are the floor, not the ceiling, of what the pathway costs. They assume a candidate who is already eligible to book (meaning primary qualification verification and English language requirements are already sorted), who passes both exams on the first attempt, and who lives close enough to a Pearson VUE centre and to Manchester that travel is negligible. For the large majority of IMGs, none of those three assumptions hold, which is why the categories below matter just as much as the headline fees. If you do need to resit either exam, &lt;a href="/news#ukmla-resits-rules-limits"&gt;the resit rules and repeat costs if you don't pass first time&lt;/a&gt; cover the financial and procedural implications in detail. Before booking anything, it's also worth checking &lt;a href="/eligibility"&gt;UKMLA eligibility requirements&lt;/a&gt; and &lt;a href="/key-dates"&gt;UKMLA key dates and booking windows&lt;/a&gt; so your spending lines up with a workable timeline.&lt;/p&gt;
+&lt;h2&gt;Costs Before You Even Book the AKT&lt;/h2&gt;
+&lt;p&gt;A significant share of total IMG spending happens before a single GMC exam fee is paid. Primary source verification, English language testing, and — for some candidates — document translation are all prerequisites to booking the AKT, and skipping or underestimating them is one of the most common budgeting mistakes IMGs make.&lt;/p&gt;
+&lt;h3&gt;Primary Source Verification and EPIC Fees&lt;/h3&gt;
+&lt;p&gt;The GMC requires independent verification that your primary medical qualification is genuine before it will accept you onto the UKMLA pathway. For most IMGs this is done through the Electronic Portfolio of International Credentials (EPIC), the verification service operated by the Educational Commission for Foreign Medical Graduates (ECFMG) on behalf of medical regulators worldwide, including the GMC. Setting up an EPIC account and submitting your primary medical qualification for verification typically costs in the region of &lt;strong&gt;£100–£140&lt;/strong&gt;, though the exact figure depends on your country of qualification and whether your &lt;a href="/news#uk-medical-schools-ukmla-implementation"&gt;medical school&lt;/a&gt; has previously used the system (schools already integrated into EPIC's verification network tend to process faster and sometimes more cheaply than first-time submissions).&lt;/p&gt;
+&lt;p&gt;Verification is not instantaneous. Depending on how quickly your medical school responds to EPIC's request to confirm your qualification, the process can take anywhere from a few weeks to several months. Candidates from medical schools with a track record of slow administrative response should budget both extra time and, in some cases, a follow-up fee if documents need to be resubmitted or a verification lapses and must be renewed. Because EPIC verification sits on the critical path to booking the AKT, delays here have a knock-on financial effect: a slipped exam booking window can mean losing a preferred test centre slot or having to wait for the next available cycle, both of which can add indirect cost through extended preparation time and, in some cases, additional question bank subscription months.&lt;/p&gt;
+&lt;p&gt;It is worth starting the EPIC process as early as possible relative to your intended AKT booking date, ideally as soon as you have decided to pursue the UK pathway rather than waiting until you are ready to sit the exam. Because EPIC verification does not expire quickly once completed, there is little downside to beginning it well in advance, and doing so removes one of the most common causes of avoidable delay — and avoidable cost — from the rest of your timeline. Candidates weighing up the UK route against other destinations may also want to check &lt;a href="/eligibility"&gt;UKMLA eligibility requirements&lt;/a&gt; at this stage, since primary qualification recognition rules differ by country of training and can affect whether EPIC verification proceeds smoothly or requires additional supporting evidence.&lt;/p&gt;
+&lt;h3&gt;English Language Test Fees&lt;/h3&gt;
+&lt;p&gt;Every IMG must demonstrate English language proficiency to the GMC's required standard, and this is one of the largest "hidden" costs in the whole pathway simply because it's easy to treat as a formality rather than a genuine budget line. The two accepted tests are IELTS Academic and OET, and their costs differ meaningfully:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;IELTS Academic&lt;/strong&gt; costs approximately &lt;strong&gt;£180–£200&lt;/strong&gt; per sitting in most countries, with the GMC requiring an overall score of 7.5 and no individual component below 7.0.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;OET (Occupational English Test)&lt;/strong&gt; costs approximately &lt;strong&gt;£500&lt;/strong&gt; per sitting, with a minimum Grade B required across all four sub-tests (Listening, Reading, Writing, Speaking).&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;OET is considerably more expensive per attempt, but many clinicians find its healthcare-specific format easier to pass on the first try, which can make it cheaper overall despite the higher headline price — a single failed IELTS attempt followed by a pass adds £180–£200, narrowing or eliminating the gap. Both test results are valid for two years from the test date, so timing matters: sitting your language test too early relative to the rest of your pathway risks the result expiring before you reach registration, forcing a costly repeat sitting purely due to a timeline mismatch rather than any change in your ability.&lt;/p&gt;
+&lt;p&gt;Beyond the test fee itself, most candidates also spend on preparation — practice books, mock speaking sessions, or short preparation courses specific to IELTS or OET, typically in the range of £20–£150 depending on how much structured support is used. Test centre availability also varies by country and city; candidates in smaller cities may need to travel to a regional hub to sit either test, adding a modest but real travel cost on top of the test fee itself. Because both tests require an in-person sitting (OET Speaking can sometimes be taken at a different time from the other components, but Listening, Reading and Writing are typically sat together), it is not possible to reduce this cost through remote or online-only test formats in the way some other English proficiency tests allow.&lt;/p&gt;
+&lt;h3&gt;Document Translation and Notarisation Costs&lt;/h3&gt;
+&lt;p&gt;&lt;a href="/news#ukmla-preparation-for-imgs"&gt;IMGs who&lt;/a&gt;se primary medical qualification, transcripts, or supporting documents were issued in a language other than English typically need certified translations before these documents will be accepted by EPIC or the GMC. Certified translation costs vary widely by country and document length but commonly fall in the range of &lt;strong&gt;£30–£80 per document&lt;/strong&gt;, and a full application file often includes three to six documents requiring translation (degree certificate, transcript, internship completion certificate, good standing certificate, and any name-change or identity documents). Some jurisdictions also require notarisation or apostille certification of original documents before submission, adding a further &lt;strong&gt;£20–£60 per document&lt;/strong&gt; depending on local notary fees. Candidates from countries where medical qualifications are issued bilingually, or where English-language transcripts are standard, can often avoid this cost entirely — it's worth checking with your medical school's registrar early, since a same-language original document is one of the easiest categories of cost to eliminate through advance planning.&lt;/p&gt;
+&lt;h2&gt;The Real Cost of Sitting the CPSA in Manchester&lt;/h2&gt;
+&lt;p&gt;Unlike the AKT, which can be sat at Pearson VUE centres in most IMG source countries, the CPSA is administered exclusively at the GMC's Clinical Assessment Centre in Manchester. This single fact turns the CPSA from a £1,036 exam fee into what is, for most IMGs, a multi-thousand-pound international trip once flights, accommodation, local transport, meals, and preparation are factored in. This section breaks down each component with indicative ranges by region.&lt;/p&gt;
+&lt;h3&gt;Flights to Manchester&lt;/h3&gt;
+&lt;p&gt;Flight costs vary substantially depending on your departure region, how far in advance you book, and whether you can travel on flexible dates outside peak periods. As indicative return fares:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;South Asia&lt;/strong&gt; (India, Pakistan, Bangladesh, Sri Lanka): approximately &lt;strong&gt;£450–£850&lt;/strong&gt; return, depending on city of departure and season.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;West Africa&lt;/strong&gt; (Nigeria, Ghana): approximately &lt;strong&gt;£550–£950&lt;/strong&gt; return, with Lagos and Accra typically at the lower end when booked well ahead.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Middle East and Gulf&lt;/strong&gt; (UAE, Saudi Arabia, Egypt, Jordan): approximately &lt;strong&gt;£350–£650&lt;/strong&gt; return, generally the cheapest of the major IMG source regions due to strong connectivity and competition among Gulf carriers.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Southeast Asia&lt;/strong&gt; (Philippines, Malaysia, Myanmar): approximately &lt;strong&gt;£600–£1,100&lt;/strong&gt; return, reflecting the greater distance and typically at least one connection.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;These are illustrative ranges only, not live fares — actual prices swing with fuel surcharges, season, and how far ahead you book. Booking six to twelve weeks in advance and remaining flexible on exact travel dates typically secures meaningfully lower fares than booking within two to three weeks of a CPSA date, particularly for departures from South Asia and West Africa where demand from other CPSA candidates can push up prices around popular exam &lt;a href="/news#ukmla-key-dates-sitting-schedule"&gt;sitting dates&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;Connecting flights add a further layer of cost variability worth planning around. Direct or one-stop routes from major Gulf and South Asian hub cities to Manchester are increasingly common, but candidates departing from smaller cities often need to first fly domestically or regionally to a major international hub before the long-haul leg, effectively splitting the journey into two separate fares. Where possible, checking connecting itineraries out of a nearby major hub — even if it means a short additional domestic flight or a longer ground journey to the departure airport — can sometimes beat the price of a single itinerary booked from a smaller regional airport, particularly for candidates in Southeast Asia and parts of West Africa where domestic and regional carrier competition is more limited.&lt;/p&gt;
+&lt;h3&gt;Accommodation for a One-to-Two-Week Stay&lt;/h3&gt;
+&lt;p&gt;Most IMGs do not fly in the day before their CPSA and fly out immediately after — the exam is demanding enough that most candidates build in several days to a couple of weeks locally beforehand to adjust to the time zone, complete a final round of practice, and reduce the risk of travel disruption affecting exam-day attendance. Accommodation options near the GMC Clinical Assessment Centre in Manchester range widely:&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Budget hotel or hostel:&lt;/strong&gt; approximately &lt;strong&gt;£40–£70 per night&lt;/strong&gt;.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Mid-range hotel or serviced apartment:&lt;/strong&gt; approximately &lt;strong&gt;£70–£120 per night&lt;/strong&gt;.&lt;/li&gt;
+&lt;li&gt;&lt;strong&gt;Shared candidate accommodation&lt;/strong&gt; (rooms or flats split with other CPSA candidates, commonly arranged through preparation course cohorts or online candidate groups): approximately &lt;strong&gt;£25–£45 per person per night&lt;/strong&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;Over a one-week stay, this translates to roughly £280–£840 depending on accommodation type; over a two-week stay, roughly £560–£1,680. Sharing accommodation with other candidates preparing for the same sitting is consistently the single biggest lever IMGs have over this cost category, often cutting it by 40–50% compared with a solo mid-range hotel booking.&lt;/p&gt;
+&lt;h3&gt;Local Transport and Meals&lt;/h3&gt;
+&lt;p&gt;Local transport in Manchester — buses, trams, and occasional taxis to and from the Clinical Assessment Centre — typically adds &lt;strong&gt;£30–£60&lt;/strong&gt; for a one- to two-week stay if using public transport for most journeys. Meals, allowing for a mix of self-catering and eating out, typically run &lt;strong&gt;£15–£30 per day&lt;/strong&gt;, or roughly £105–£420 across a one- to two-week visit. Candidates staying in serviced apartments or shared accommodation with kitchen access can bring this down considerably by cooking rather than relying on restaurants throughout the stay.&lt;/p&gt;
+&lt;h3&gt;CPSA Preparation Courses&lt;/h3&gt;
+&lt;p&gt;Many IMGs supplement self-study with a structured CPSA/OSCE preparation course, either in person in the UK or online. In-person, multi-day intensive courses typically cost &lt;strong&gt;£500–£1,500&lt;/strong&gt;, often scheduled in the days immediately before the exam so candidates can combine travel for the course and the exam into a single trip — a sensible way to consolidate travel costs rather than making two separate journeys. Online preparation packages, including video content, mock stations, and feedback, typically cost &lt;strong&gt;£100–£400&lt;/strong&gt; and can be started well in advance of travel, reducing time pressure during the in-person stay. Preparation course spend is optional rather than mandatory, but for candidates without access to a UK-based clinical mentor or peer practice group, a structured course is often the most efficient way to close specific skill gaps before a £1,036 exam attempt.&lt;/p&gt;
+&lt;h2&gt;Total Estimated Budget by Region&lt;/h2&gt;
+&lt;p&gt;Bringing every category together, the table below sets out an illustrative total pathway cost by IMG source region. These figures combine the core GMC fees (assuming first-attempt passes), EPIC verification plus one English language test sitting, and CPSA-related travel and accommodation for a one- to two-week Manchester stay. They exclude optional preparation courses, question bank subscriptions, and any visa costs, which are covered separately below. All regional figures are indicative estimates for planning purposes only — not official GMC or third-party pricing — and individual circumstances will vary considerably.&lt;/p&gt;
+&lt;table class="post-table"&gt;
+&lt;thead&gt;
+&lt;tr&gt;&lt;th&gt;Region&lt;/th&gt;&lt;th&gt;Core GMC Fees&lt;/th&gt;&lt;th&gt;EPIC + English Test&lt;/th&gt;&lt;th&gt;Travel/Accommodation for CPSA&lt;/th&gt;&lt;th&gt;Estimated Total&lt;/th&gt;&lt;/tr&gt;
+&lt;/thead&gt;
+&lt;tbody&gt;
+&lt;tr&gt;&lt;td&gt;South Asia (India, Pakistan, Bangladesh, Sri Lanka)&lt;/td&gt;&lt;td&gt;£1,800&lt;/td&gt;&lt;td&gt;£280–£340&lt;/td&gt;&lt;td&gt;£730–£1,690&lt;/td&gt;&lt;td&gt;£2,810–£3,830&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;West Africa (Nigeria, Ghana)&lt;/td&gt;&lt;td&gt;£1,800&lt;/td&gt;&lt;td&gt;£280–£340&lt;/td&gt;&lt;td&gt;£830–£1,790&lt;/td&gt;&lt;td&gt;£2,910–£3,930&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Middle East and Gulf (UAE, Saudi Arabia, Egypt, Jordan)&lt;/td&gt;&lt;td&gt;£1,800&lt;/td&gt;&lt;td&gt;£280–£340&lt;/td&gt;&lt;td&gt;£630–£1,490&lt;/td&gt;&lt;td&gt;£2,710–£3,630&lt;/td&gt;&lt;/tr&gt;
+&lt;tr&gt;&lt;td&gt;Southeast Asia (Philippines, Malaysia, Myanmar)&lt;/td&gt;&lt;td&gt;£1,800&lt;/td&gt;&lt;td&gt;£280–£340&lt;/td&gt;&lt;td&gt;£880–£1,940&lt;/td&gt;&lt;td&gt;£2,960–£4,080&lt;/td&gt;&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;
+&lt;p&gt;Every region clusters in a broadly similar £2,700–£4,100 range for a first-attempt pathway, with the spread driven mainly by flight distance and accommodation choices rather than by fundamental differences in the process itself. Adding a preparation course (£100–£1,500), a comprehensive question bank subscription (£40–£200), or a single resit of either exam (£283 for AKT, £1,036 for CPSA) pushes the realistic upper end of most candidates' total spend towards £4,500–£5,500. Candidates from Southeast Asia and West Africa, who tend to face the highest flight costs, benefit most from early booking and shared accommodation strategies, since travel and lodging make up a proportionally larger share of their total budget than for candidates travelling from the Gulf.&lt;/p&gt;
+&lt;p&gt;It is also worth noting what this table deliberately excludes, since candidates sometimes mistake a regional estimate for a complete personal budget. None of the figures above include a CPSA preparation course, a question bank subscription used during AKT preparation, visa costs where applicable, document translation or notarisation, or any resit fees. They also assume a single one- to two-week Manchester visit covering only the CPSA itself, rather than a longer stay for in-person preparation or informal clinical exposure beforehand. Candidates who plan for any of these additional elements should treat the table as a floor for their region rather than a ceiling, and add the relevant category from the sections above onto their personal total.&lt;/p&gt;
+&lt;p&gt;Currency movement is a further factor the table cannot fully capture. Because all four regions convert from a home currency into pounds sterling to make GMC and UK-based payments, a shift in the exchange rate between the time a candidate starts saving and the time they actually pay each fee can meaningfully change the local-currency cost of the pathway, even though the pound figure stays fixed. Candidates with a long runway between deciding to pursue the UK route and actually booking exams may want to monitor exchange rate trends and, where practical, convert and hold funds in pounds sterling ahead of major payment dates to avoid a late, unfavourable conversion at the point of booking.&lt;/p&gt;
+&lt;h2&gt;Ongoing Costs After Registration: The Annual Retention Fee&lt;/h2&gt;
+&lt;p&gt;Passing the CPSA and being granted registration is not the end of GMC-related costs. Every doctor on the UK medical register, whether trained in the UK or abroad, pays an &lt;strong&gt;annual retention fee of £431&lt;/strong&gt; to remain registered and licensed to practise. This fee is billed each January and funds the GMC's ongoing regulatory functions: maintaining the medical register, running revalidation, investigating fitness-to-practise concerns, and operating the standard-setting and quality assurance processes that underpin the MLA framework itself.&lt;/p&gt;
+&lt;p&gt;The retention fee is typically collected by direct debit, set up when you first register, and is a legal requirement to remain on the register — non-payment can result in removal from the register and loss of your licence to practise, so it is not a fee that can be deferred or skipped. Newly registered doctors in their first partial year sometimes pay a pro-rated amount depending on when in the registration cycle they joined, with the full £431 applying from the following January onward. Over the course of a career, this is a substantial cumulative cost: at the current rate, thirty years of registration totals roughly £12,930, and forty years roughly £17,240, though the GMC reviews and periodically adjusts this fee, so actual lifetime totals will differ. This is worth factoring into long-term financial planning even though it falls well outside the upfront pathway budget most candidates focus on.&lt;/p&gt;
+&lt;p&gt;For newly arrived IMGs beginning work in the NHS, the retention fee is worth budgeting for separately from the upfront pathway costs covered elsewhere in this guide, since it is easy to treat registration as the finish line and forget that a recurring annual charge follows immediately behind it. Doctors who move between different types of registration status, take a career break, or temporarily leave the register and later reapply should also be aware that reinstatement can carry its own fee, separate from the standard annual retention charge, so maintaining continuous registration where possible is usually the more cost-effective path if a temporary pause is not strictly necessary. Completing &lt;a href="/registration-guide"&gt;the GMC registration process&lt;/a&gt; correctly the first time, with the retention fee direct debit set up promptly, avoids the administrative complications — and potential late fees — that can arise from a missed or failed payment.&lt;/p&gt;
+&lt;h2&gt;How to Budget and Reduce Your Total IMG Pathway Cost&lt;/h2&gt;
+&lt;p&gt;Given that total pathway costs commonly reach £3,000–£4,500 or more, deliberate cost management makes a real difference, particularly for candidates converting from currencies where the pound has significant purchasing power. The following strategies address the largest cost levers identified throughout this guide.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Pass on the first attempt wherever possible.&lt;/strong&gt; This is the single highest-leverage cost-saving strategy available. A failed AKT adds £283 to &lt;a href="/appeals-and-resits"&gt;re-sit&lt;/a&gt;; a failed CPSA adds £1,036, plus a second round of flights and accommodation to Manchester that can easily exceed £1,000 on its own. A candidate who needs a second CPSA attempt is not just paying £1,036 twice — they are effectively duplicating their entire travel budget. Thorough preparation, realistic mock assessments, and honest self-assessment of readiness before booking are worth far more than their time cost in avoided resit expenses. For full detail on how resits work procedurally and what they cost, see &lt;a href="/news#ukmla-resits-rules-limits"&gt;the resit rules and repeat costs if you don't pass first time&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Book CPSA travel early.&lt;/strong&gt; Flights and accommodation both get more expensive, and availability tighter, the closer you get to a popular exam sitting date. Booking flights six to twelve weeks ahead and accommodation as soon as your CPSA date is confirmed typically saves 20–40% compared with booking in the final two to three weeks before travel.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Share accommodation where possible.&lt;/strong&gt; Splitting a room or flat with one or two other CPSA candidates — often arranged through preparation course cohorts, university alumni networks, or online IMG candidate communities — is consistently the most effective way to cut the accommodation line of the budget, frequently by close to half compared with a solo hotel stay.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Time your English test validity against the rest of your timeline.&lt;/strong&gt; Both IELTS and OET results are valid for two years. Sitting your language test too far ahead of your planned AKT and CPSA dates risks the result lapsing before you reach registration, which means paying for and sitting the test again purely due to poor sequencing rather than any change in ability. Map out your expected timeline across &lt;a href="/key-dates"&gt;UKMLA key dates and booking windows&lt;/a&gt; before committing to a language test date, so the two-year window comfortably covers your realistic path through to registration.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Budget deliberately for question banks and &lt;a href="/news#mock-exams-ukmla-preparation"&gt;mock test&lt;/a&gt;s rather than over-subscribing.&lt;/strong&gt; Many candidates subscribe to multiple overlapping AKT question banks out of anxiety rather than genuine need, which can add hundreds of pounds without proportionate benefit. A focused approach — one comprehensive question bank used systematically through the full &lt;a href="/syllabus"&gt;MLA content map&lt;/a&gt;, supplemented by timed mock papers closer to the exam date — is usually both cheaper and more effective than subscribing broadly. For a fuller look at what's worth paying for, see the guidance on &lt;a href="/news#ukmla-question-bank-and-mock-tests"&gt;budgeting for question banks and mock tests&lt;/a&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Factor in visa costs if relevant to your travel.&lt;/strong&gt; Depending on your nationality, a short-term visit visa may be required to travel to the UK for the CPSA. Visa application fees, biometric appointment costs, and any associated travel to a visa application centre in your home country should be added to your personal budget where applicable, as these are separate from and additional to any GMC or exam-related charge.&lt;/p&gt;
+&lt;h2&gt;Financial Support and Concessions for IMGs&lt;/h2&gt;
+&lt;p&gt;The GMC operates one formal fee concession scheme relevant to IMGs: the refugee doctor assistance programme. Under this scheme, doctors with recognised refugee status, or a pending asylum application accepted by the relevant national authority, can sit their first two AKT (&lt;a href="/ukmla-vs-plab"&gt;PLAB 1&lt;/a&gt;) attempts free of charge, and their first two CPSA (PLAB 2) attempts at 50% of the standard fee, meaning roughly £518 per sitting rather than £1,036. To access the concession, evidence of refugee or asylum-seeker status must be submitted to and accepted by the GMC before the discounted booking is applied — it is not retrospective, so candidates who may qualify should establish their eligibility before booking rather than after paying full price.&lt;/p&gt;
+&lt;p&gt;Outside this specific scheme, there is currently &lt;strong&gt;no general income-based hardship fund&lt;/strong&gt; available to IMGs. Candidates from lower-income countries, where the pound cost of the pathway represents a proportionally much larger sum relative to local earnings, do not have access to a sliding-scale fee structure or GMC-administered bursary. In practice, most IMGs fund the pathway through personal savings, family contribution, or, in some cases, informal interest-free loans arranged through diaspora professional networks and alumni associations. Some professional bodies and diaspora medical associations in source countries offer small grants or loan schemes specifically for licensing exam costs, though availability and terms vary significantly and should be verified directly with the relevant organisation rather than assumed. As with the core exam fees, it's worth reiterating that &lt;strong&gt;no agent or intermediary can legitimately facilitate or discount GMC payments&lt;/strong&gt; — any service claiming to arrange reduced-fee GMC bookings, expedited registration for a fee, or "guaranteed" concessionary rates outside the official refugee doctor scheme should be treated as a red flag, and all fee payments should be made directly through your own GMC Online account.&lt;/p&gt;
+&lt;h2&gt;Frequently Asked Questions&lt;/h2&gt;
+&lt;h3&gt;How much does the full UKMLA pathway cost for an IMG?&lt;/h3&gt;
+&lt;p&gt;Including the core GMC fees, primary source verification, an English language test, and CPSA-related travel and accommodation, most IMGs should budget between &lt;strong&gt;£2,700 and £4,100&lt;/strong&gt; for a first-attempt pathway, depending on their departure region. Adding a preparation course, question bank subscriptions, or any resit pushes many candidates' realistic total towards £4,500–£5,500. These are planning estimates, not fixed costs, and individual circumstances vary considerably.&lt;/p&gt;
+&lt;h3&gt;Are there fee discounts for IMGs from low-income countries?&lt;/h3&gt;
+&lt;p&gt;No general discount exists based on country of origin or income level. The only formal GMC concession is the refugee doctor assistance scheme, which offers free AKT attempts and half-price CPSA attempts to doctors with recognised refugee or pending asylum status. IMGs from lower-income countries who do not qualify for this scheme pay the same standard fees as all other IMGs.&lt;/p&gt;
+&lt;h3&gt;What is the cost of UKMLA exam for IMG 2026 compared with previous years?&lt;/h3&gt;
+&lt;p&gt;Core fees have risen over the past decade, with PLAB 1 and PLAB 2 fees (now the AKT and CPSA) increasing from roughly £225 and £665 respectively in 2015 to £283 and £1,036 in 2026. Full detail on year-by-year changes is available via &lt;a href="https://www.gmc-uk.org/registration-and-licensing/managing-your-registration/fees-and-funding/how-our-fees-have-changed" target="_blank" rel="noopener"&gt;how GMC fees have changed over time&lt;/a&gt;. The GMC reviews its fee schedule periodically; always verify current charges on the &lt;a href="/official-resources"&gt;GMC website&lt;/a&gt; before booking.&lt;/p&gt;
+&lt;h3&gt;Do EPIC verification and English test fees count towards the "official" UKMLA fee?&lt;/h3&gt;
+&lt;p&gt;No. EPIC/primary source verification and English language test fees (IELTS or OET) are paid to separate organisations, not to the GMC, and are not part of the official AKT/CPSA/registration fee schedule. They are, however, mandatory prerequisites for most IMGs and should be included in any realistic total budget, which is why this guide treats them as core pathway costs even though they don't appear on the GMC's own fee page.&lt;/p&gt;
+&lt;h3&gt;Is it cheaper to prepare for the CPSA in my home country or in the UK?&lt;/h3&gt;
+&lt;p&gt;Preparing primarily in your home country using online resources and question banks, then travelling to the UK only for a short, focused period immediately before the CPSA, is generally the cheaper approach, since it minimises UK accommodation and living costs. Some candidates choose a longer UK stay to attend an in-person preparation course or gain informal clinical exposure, which raises costs but may improve first-attempt pass chances — a trade-off worth weighing against the roughly £1,036 cost of a resit.&lt;/p&gt;
+&lt;h3&gt;How does the UKMLA pathway cost compare to alternatives like the USMLE or staying in India for NEET PG?&lt;/h3&gt;
+&lt;p&gt;The UKMLA pathway is generally less expensive upfront than the USMLE route, where total US exam fees alone exceed $3,500 before travel — see &lt;a href="/news#ukmla-vs-usmle-comparison"&gt;how these costs compare to the US's USMLE route&lt;/a&gt; for a full breakdown. For Indian doctors specifically weighing UK registration against pursuing postgraduate training domestically, &lt;a href="/news#ukmla-vs-neet-pg"&gt;how this compares to staying in India for NEET PG&lt;/a&gt; covers the cost and career trade-offs in detail.&lt;/p&gt;
+&lt;h3&gt;Do visa costs need to be added to the IMG pathway budget?&lt;/h3&gt;
+&lt;p&gt;If your nationality requires a visa to enter the UK for the CPSA, yes — visa application fees, biometric appointment costs, and any related travel to a visa centre are additional to e</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fees IMG cost guide</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>/images/ukmla-fees-for-img-2026-featured.webp</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam fees for IMG - international medical graduate calculating total UKMLA and GMC registration costs</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>5006</v>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>No active links</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
